--- a/src/assets/data/Grupos_66.xlsx
+++ b/src/assets/data/Grupos_66.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Santiago Castro\Documents\github\agenda-jfd-69-cue\src\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A35591-704C-44BA-8F37-A91A275616F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B0B851-06AB-4F7A-B9A9-EBE4B93E40AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10709,7 +10709,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I562"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10751,7 +10750,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -10780,7 +10779,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -10838,7 +10837,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -10867,7 +10866,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -10896,7 +10895,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
@@ -10925,7 +10924,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -10954,7 +10953,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>39</v>
       </c>
@@ -10983,7 +10982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
@@ -11012,7 +11011,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>46</v>
       </c>
@@ -11041,7 +11040,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>49</v>
       </c>
@@ -11070,7 +11069,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>52</v>
       </c>
@@ -11099,7 +11098,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>55</v>
       </c>
@@ -11128,7 +11127,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>58</v>
       </c>
@@ -11157,7 +11156,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>62</v>
       </c>
@@ -11186,7 +11185,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>65</v>
       </c>
@@ -11215,7 +11214,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>68</v>
       </c>
@@ -11244,7 +11243,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>71</v>
       </c>
@@ -11273,7 +11272,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>75</v>
       </c>
@@ -11302,7 +11301,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>78</v>
       </c>
@@ -11331,7 +11330,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>81</v>
       </c>
@@ -11360,7 +11359,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>84</v>
       </c>
@@ -11389,7 +11388,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>87</v>
       </c>
@@ -11418,7 +11417,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>90</v>
       </c>
@@ -11447,7 +11446,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>93</v>
       </c>
@@ -11505,7 +11504,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>100</v>
       </c>
@@ -11534,7 +11533,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>103</v>
       </c>
@@ -11563,7 +11562,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>106</v>
       </c>
@@ -11592,7 +11591,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>109</v>
       </c>
@@ -11621,7 +11620,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>112</v>
       </c>
@@ -11650,7 +11649,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>115</v>
       </c>
@@ -11679,7 +11678,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>119</v>
       </c>
@@ -11708,7 +11707,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>122</v>
       </c>
@@ -11737,7 +11736,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>125</v>
       </c>
@@ -11766,7 +11765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>128</v>
       </c>
@@ -11795,7 +11794,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>131</v>
       </c>
@@ -11824,7 +11823,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>134</v>
       </c>
@@ -11853,7 +11852,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>137</v>
       </c>
@@ -11882,7 +11881,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>141</v>
       </c>
@@ -11911,7 +11910,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>144</v>
       </c>
@@ -11940,7 +11939,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>147</v>
       </c>
@@ -11969,7 +11968,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>150</v>
       </c>
@@ -11998,7 +11997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>153</v>
       </c>
@@ -12027,7 +12026,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>156</v>
       </c>
@@ -12056,7 +12055,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>159</v>
       </c>
@@ -12085,7 +12084,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>162</v>
       </c>
@@ -12114,7 +12113,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>165</v>
       </c>
@@ -12143,7 +12142,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>168</v>
       </c>
@@ -12172,7 +12171,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>171</v>
       </c>
@@ -12201,7 +12200,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>174</v>
       </c>
@@ -12230,7 +12229,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>177</v>
       </c>
@@ -12259,7 +12258,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>180</v>
       </c>
@@ -12288,7 +12287,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>183</v>
       </c>
@@ -12317,7 +12316,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>186</v>
       </c>
@@ -12346,7 +12345,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>189</v>
       </c>
@@ -12375,7 +12374,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>192</v>
       </c>
@@ -12433,7 +12432,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>198</v>
       </c>
@@ -12462,7 +12461,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>201</v>
       </c>
@@ -12491,7 +12490,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>204</v>
       </c>
@@ -12520,7 +12519,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>207</v>
       </c>
@@ -12549,7 +12548,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>210</v>
       </c>
@@ -12578,7 +12577,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>213</v>
       </c>
@@ -12607,7 +12606,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>216</v>
       </c>
@@ -12636,7 +12635,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>219</v>
       </c>
@@ -12665,7 +12664,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>222</v>
       </c>
@@ -12694,7 +12693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>225</v>
       </c>
@@ -12752,7 +12751,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>231</v>
       </c>
@@ -12810,7 +12809,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>237</v>
       </c>
@@ -12839,7 +12838,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>240</v>
       </c>
@@ -12868,7 +12867,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>243</v>
       </c>
@@ -12897,7 +12896,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>246</v>
       </c>
@@ -12926,7 +12925,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>249</v>
       </c>
@@ -12955,7 +12954,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>252</v>
       </c>
@@ -12984,7 +12983,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>255</v>
       </c>
@@ -13013,7 +13012,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>258</v>
       </c>
@@ -13042,7 +13041,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>261</v>
       </c>
@@ -13071,7 +13070,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>264</v>
       </c>
@@ -13100,7 +13099,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>267</v>
       </c>
@@ -13129,7 +13128,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>270</v>
       </c>
@@ -13158,7 +13157,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>273</v>
       </c>
@@ -13187,7 +13186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>276</v>
       </c>
@@ -13216,7 +13215,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>279</v>
       </c>
@@ -13245,7 +13244,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>282</v>
       </c>
@@ -13274,7 +13273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>285</v>
       </c>
@@ -13303,7 +13302,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>288</v>
       </c>
@@ -13332,7 +13331,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>291</v>
       </c>
@@ -13361,7 +13360,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>294</v>
       </c>
@@ -13390,7 +13389,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>297</v>
       </c>
@@ -13419,7 +13418,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>300</v>
       </c>
@@ -13477,7 +13476,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>306</v>
       </c>
@@ -13506,7 +13505,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>309</v>
       </c>
@@ -13535,7 +13534,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>312</v>
       </c>
@@ -13564,7 +13563,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>315</v>
       </c>
@@ -13593,7 +13592,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>318</v>
       </c>
@@ -13622,7 +13621,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>321</v>
       </c>
@@ -13651,7 +13650,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>324</v>
       </c>
@@ -13680,7 +13679,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>327</v>
       </c>
@@ -13709,7 +13708,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>330</v>
       </c>
@@ -13738,7 +13737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>333</v>
       </c>
@@ -13767,7 +13766,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>336</v>
       </c>
@@ -13796,7 +13795,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>339</v>
       </c>
@@ -13825,7 +13824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>342</v>
       </c>
@@ -13854,7 +13853,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>345</v>
       </c>
@@ -13883,7 +13882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>348</v>
       </c>
@@ -13912,7 +13911,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>351</v>
       </c>
@@ -13941,7 +13940,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>354</v>
       </c>
@@ -13970,7 +13969,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>357</v>
       </c>
@@ -13999,7 +13998,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>360</v>
       </c>
@@ -14028,7 +14027,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>363</v>
       </c>
@@ -14057,7 +14056,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>366</v>
       </c>
@@ -14086,7 +14085,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>369</v>
       </c>
@@ -14115,7 +14114,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>372</v>
       </c>
@@ -14144,7 +14143,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>375</v>
       </c>
@@ -14173,7 +14172,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>378</v>
       </c>
@@ -14231,7 +14230,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>384</v>
       </c>
@@ -14260,7 +14259,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>387</v>
       </c>
@@ -14289,7 +14288,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>390</v>
       </c>
@@ -14318,7 +14317,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>393</v>
       </c>
@@ -14347,7 +14346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>396</v>
       </c>
@@ -14376,7 +14375,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>399</v>
       </c>
@@ -14405,7 +14404,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>402</v>
       </c>
@@ -14434,7 +14433,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>405</v>
       </c>
@@ -14463,7 +14462,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>408</v>
       </c>
@@ -14492,7 +14491,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>411</v>
       </c>
@@ -14521,7 +14520,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>414</v>
       </c>
@@ -14550,7 +14549,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>417</v>
       </c>
@@ -14579,7 +14578,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>420</v>
       </c>
@@ -14608,7 +14607,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>423</v>
       </c>
@@ -14637,7 +14636,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>426</v>
       </c>
@@ -14666,7 +14665,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>429</v>
       </c>
@@ -14695,7 +14694,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>432</v>
       </c>
@@ -14724,7 +14723,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>435</v>
       </c>
@@ -14753,7 +14752,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>438</v>
       </c>
@@ -14782,7 +14781,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>441</v>
       </c>
@@ -14811,7 +14810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>444</v>
       </c>
@@ -14840,7 +14839,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>447</v>
       </c>
@@ -14869,7 +14868,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>450</v>
       </c>
@@ -14898,7 +14897,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>453</v>
       </c>
@@ -14927,7 +14926,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>456</v>
       </c>
@@ -14956,7 +14955,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>459</v>
       </c>
@@ -14985,7 +14984,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>462</v>
       </c>
@@ -15014,7 +15013,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>465</v>
       </c>
@@ -15043,7 +15042,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>468</v>
       </c>
@@ -15072,7 +15071,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>471</v>
       </c>
@@ -15101,7 +15100,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>474</v>
       </c>
@@ -15130,7 +15129,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>477</v>
       </c>
@@ -15159,7 +15158,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>480</v>
       </c>
@@ -15217,7 +15216,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>486</v>
       </c>
@@ -15246,7 +15245,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>489</v>
       </c>
@@ -15275,7 +15274,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>492</v>
       </c>
@@ -15304,7 +15303,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>495</v>
       </c>
@@ -15333,7 +15332,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>498</v>
       </c>
@@ -15362,7 +15361,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>501</v>
       </c>
@@ -15391,7 +15390,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>504</v>
       </c>
@@ -15420,7 +15419,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>507</v>
       </c>
@@ -15449,7 +15448,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>510</v>
       </c>
@@ -15478,7 +15477,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>513</v>
       </c>
@@ -15507,7 +15506,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>516</v>
       </c>
@@ -15536,7 +15535,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>519</v>
       </c>
@@ -15565,7 +15564,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>522</v>
       </c>
@@ -15594,7 +15593,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>525</v>
       </c>
@@ -15623,7 +15622,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>528</v>
       </c>
@@ -15652,7 +15651,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>531</v>
       </c>
@@ -15681,7 +15680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>534</v>
       </c>
@@ -15710,7 +15709,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>537</v>
       </c>
@@ -15739,7 +15738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>540</v>
       </c>
@@ -15768,7 +15767,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>543</v>
       </c>
@@ -15797,7 +15796,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>546</v>
       </c>
@@ -15826,7 +15825,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>549</v>
       </c>
@@ -15855,7 +15854,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>552</v>
       </c>
@@ -15884,7 +15883,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>555</v>
       </c>
@@ -15913,7 +15912,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>558</v>
       </c>
@@ -15942,7 +15941,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>561</v>
       </c>
@@ -16029,7 +16028,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>570</v>
       </c>
@@ -16058,7 +16057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>573</v>
       </c>
@@ -16087,7 +16086,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>576</v>
       </c>
@@ -16116,7 +16115,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>579</v>
       </c>
@@ -16145,7 +16144,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>582</v>
       </c>
@@ -16174,7 +16173,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>585</v>
       </c>
@@ -16203,7 +16202,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>588</v>
       </c>
@@ -16232,7 +16231,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>591</v>
       </c>
@@ -16261,7 +16260,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>594</v>
       </c>
@@ -16290,7 +16289,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>597</v>
       </c>
@@ -16319,7 +16318,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>600</v>
       </c>
@@ -16348,7 +16347,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>603</v>
       </c>
@@ -16377,7 +16376,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>606</v>
       </c>
@@ -16406,7 +16405,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>609</v>
       </c>
@@ -16435,7 +16434,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>612</v>
       </c>
@@ -16464,7 +16463,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>615</v>
       </c>
@@ -16493,7 +16492,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>618</v>
       </c>
@@ -16522,7 +16521,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>621</v>
       </c>
@@ -16551,7 +16550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>624</v>
       </c>
@@ -16580,7 +16579,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>627</v>
       </c>
@@ -16609,7 +16608,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>630</v>
       </c>
@@ -16638,7 +16637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>633</v>
       </c>
@@ -16667,7 +16666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>636</v>
       </c>
@@ -16696,7 +16695,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>639</v>
       </c>
@@ -16725,7 +16724,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>642</v>
       </c>
@@ -16754,7 +16753,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>645</v>
       </c>
@@ -16783,7 +16782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>648</v>
       </c>
@@ -16812,7 +16811,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>651</v>
       </c>
@@ -16841,7 +16840,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>654</v>
       </c>
@@ -16870,7 +16869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>657</v>
       </c>
@@ -16899,7 +16898,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>660</v>
       </c>
@@ -16928,7 +16927,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>663</v>
       </c>
@@ -16957,7 +16956,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>666</v>
       </c>
@@ -16986,7 +16985,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>669</v>
       </c>
@@ -17015,7 +17014,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>672</v>
       </c>
@@ -17044,7 +17043,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>675</v>
       </c>
@@ -17073,7 +17072,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>678</v>
       </c>
@@ -17102,7 +17101,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>681</v>
       </c>
@@ -17131,7 +17130,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>684</v>
       </c>
@@ -17160,7 +17159,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>687</v>
       </c>
@@ -17189,7 +17188,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>690</v>
       </c>
@@ -17218,7 +17217,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>693</v>
       </c>
@@ -17247,7 +17246,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>696</v>
       </c>
@@ -17276,7 +17275,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>699</v>
       </c>
@@ -17305,7 +17304,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>702</v>
       </c>
@@ -17334,7 +17333,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>705</v>
       </c>
@@ -17363,7 +17362,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>708</v>
       </c>
@@ -17392,7 +17391,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>711</v>
       </c>
@@ -17421,7 +17420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>714</v>
       </c>
@@ -17450,7 +17449,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>717</v>
       </c>
@@ -17479,7 +17478,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>720</v>
       </c>
@@ -17508,7 +17507,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>723</v>
       </c>
@@ -17537,7 +17536,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>726</v>
       </c>
@@ -17566,7 +17565,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>729</v>
       </c>
@@ -17595,7 +17594,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>732</v>
       </c>
@@ -17624,7 +17623,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>735</v>
       </c>
@@ -17653,7 +17652,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>738</v>
       </c>
@@ -17682,7 +17681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>741</v>
       </c>
@@ -17711,7 +17710,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>744</v>
       </c>
@@ -17740,7 +17739,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>747</v>
       </c>
@@ -17769,7 +17768,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>750</v>
       </c>
@@ -17798,7 +17797,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>753</v>
       </c>
@@ -17827,7 +17826,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>756</v>
       </c>
@@ -17856,7 +17855,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>759</v>
       </c>
@@ -17885,7 +17884,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>762</v>
       </c>
@@ -17914,7 +17913,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>765</v>
       </c>
@@ -17943,7 +17942,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>768</v>
       </c>
@@ -18001,7 +18000,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>774</v>
       </c>
@@ -18030,7 +18029,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>777</v>
       </c>
@@ -18088,7 +18087,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>783</v>
       </c>
@@ -18117,7 +18116,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>786</v>
       </c>
@@ -18146,7 +18145,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>789</v>
       </c>
@@ -18175,7 +18174,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>792</v>
       </c>
@@ -18204,7 +18203,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>795</v>
       </c>
@@ -18233,7 +18232,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>798</v>
       </c>
@@ -18262,7 +18261,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>801</v>
       </c>
@@ -18291,7 +18290,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>804</v>
       </c>
@@ -18320,7 +18319,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>807</v>
       </c>
@@ -18349,7 +18348,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>810</v>
       </c>
@@ -18378,7 +18377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>813</v>
       </c>
@@ -18407,7 +18406,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>816</v>
       </c>
@@ -18436,7 +18435,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>819</v>
       </c>
@@ -18465,7 +18464,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>822</v>
       </c>
@@ -18523,7 +18522,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>828</v>
       </c>
@@ -18552,7 +18551,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>831</v>
       </c>
@@ -18581,7 +18580,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>834</v>
       </c>
@@ -18610,7 +18609,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>837</v>
       </c>
@@ -18639,7 +18638,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>840</v>
       </c>
@@ -18668,7 +18667,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>843</v>
       </c>
@@ -18726,7 +18725,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>849</v>
       </c>
@@ -18755,7 +18754,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>852</v>
       </c>
@@ -18784,7 +18783,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>855</v>
       </c>
@@ -18813,7 +18812,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>858</v>
       </c>
@@ -18842,7 +18841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>861</v>
       </c>
@@ -18871,7 +18870,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>864</v>
       </c>
@@ -18900,7 +18899,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>867</v>
       </c>
@@ -18929,7 +18928,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>870</v>
       </c>
@@ -18958,7 +18957,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
         <v>873</v>
       </c>
@@ -18987,7 +18986,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
         <v>876</v>
       </c>
@@ -19016,7 +19015,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>879</v>
       </c>
@@ -19045,7 +19044,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>882</v>
       </c>
@@ -19074,7 +19073,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>885</v>
       </c>
@@ -19103,7 +19102,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>888</v>
       </c>
@@ -19132,7 +19131,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
         <v>891</v>
       </c>
@@ -19161,7 +19160,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
         <v>894</v>
       </c>
@@ -19219,7 +19218,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
         <v>900</v>
       </c>
@@ -19248,7 +19247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
         <v>903</v>
       </c>
@@ -19277,7 +19276,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>906</v>
       </c>
@@ -19306,7 +19305,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
         <v>909</v>
       </c>
@@ -19364,7 +19363,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
         <v>915</v>
       </c>
@@ -19393,7 +19392,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
         <v>918</v>
       </c>
@@ -19422,7 +19421,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>921</v>
       </c>
@@ -19451,7 +19450,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
         <v>924</v>
       </c>
@@ -19480,7 +19479,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
         <v>927</v>
       </c>
@@ -19509,7 +19508,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
         <v>930</v>
       </c>
@@ -19538,7 +19537,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
         <v>933</v>
       </c>
@@ -19567,7 +19566,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
         <v>936</v>
       </c>
@@ -19596,7 +19595,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
         <v>939</v>
       </c>
@@ -19625,7 +19624,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
         <v>942</v>
       </c>
@@ -19654,7 +19653,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
         <v>945</v>
       </c>
@@ -19683,7 +19682,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
         <v>948</v>
       </c>
@@ -19712,7 +19711,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
         <v>951</v>
       </c>
@@ -19741,7 +19740,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
         <v>954</v>
       </c>
@@ -19770,7 +19769,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
         <v>957</v>
       </c>
@@ -19799,7 +19798,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
         <v>960</v>
       </c>
@@ -19828,7 +19827,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
         <v>963</v>
       </c>
@@ -19857,7 +19856,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
         <v>966</v>
       </c>
@@ -19886,7 +19885,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>969</v>
       </c>
@@ -19915,7 +19914,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>972</v>
       </c>
@@ -19944,7 +19943,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>975</v>
       </c>
@@ -19973,7 +19972,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>978</v>
       </c>
@@ -20002,7 +20001,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>981</v>
       </c>
@@ -20031,7 +20030,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
         <v>984</v>
       </c>
@@ -20060,7 +20059,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
         <v>987</v>
       </c>
@@ -20089,7 +20088,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>990</v>
       </c>
@@ -20118,7 +20117,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
         <v>993</v>
       </c>
@@ -20147,7 +20146,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
         <v>996</v>
       </c>
@@ -20176,7 +20175,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
         <v>999</v>
       </c>
@@ -20205,7 +20204,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
         <v>1002</v>
       </c>
@@ -20234,7 +20233,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
         <v>1005</v>
       </c>
@@ -20263,7 +20262,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>1008</v>
       </c>
@@ -20292,7 +20291,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>1011</v>
       </c>
@@ -20321,7 +20320,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>1014</v>
       </c>
@@ -20350,7 +20349,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>1017</v>
       </c>
@@ -20379,7 +20378,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>1020</v>
       </c>
@@ -20408,7 +20407,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>1023</v>
       </c>
@@ -20437,7 +20436,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
         <v>1026</v>
       </c>
@@ -20466,7 +20465,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>1029</v>
       </c>
@@ -20495,7 +20494,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>1032</v>
       </c>
@@ -20524,7 +20523,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
         <v>1035</v>
       </c>
@@ -20553,7 +20552,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
         <v>1038</v>
       </c>
@@ -20611,7 +20610,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
         <v>1044</v>
       </c>
@@ -20669,7 +20668,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
         <v>1050</v>
       </c>
@@ -20698,7 +20697,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
         <v>1053</v>
       </c>
@@ -20727,7 +20726,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
         <v>1056</v>
       </c>
@@ -20756,7 +20755,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
         <v>1059</v>
       </c>
@@ -20785,7 +20784,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
         <v>1062</v>
       </c>
@@ -20843,7 +20842,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
         <v>1068</v>
       </c>
@@ -20901,7 +20900,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
         <v>1074</v>
       </c>
@@ -20930,7 +20929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
         <v>1077</v>
       </c>
@@ -20959,7 +20958,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
         <v>1080</v>
       </c>
@@ -20988,7 +20987,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
         <v>1083</v>
       </c>
@@ -21017,7 +21016,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
         <v>1086</v>
       </c>
@@ -21046,7 +21045,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
         <v>1089</v>
       </c>
@@ -21075,7 +21074,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
         <v>1092</v>
       </c>
@@ -21104,7 +21103,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
         <v>1095</v>
       </c>
@@ -21133,7 +21132,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
         <v>1098</v>
       </c>
@@ -21162,7 +21161,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
         <v>1101</v>
       </c>
@@ -21191,7 +21190,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
         <v>1104</v>
       </c>
@@ -21220,7 +21219,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
         <v>1107</v>
       </c>
@@ -21249,7 +21248,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
         <v>1110</v>
       </c>
@@ -21278,7 +21277,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
         <v>1113</v>
       </c>
@@ -21307,7 +21306,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
         <v>1116</v>
       </c>
@@ -21336,7 +21335,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
         <v>1119</v>
       </c>
@@ -21365,7 +21364,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
         <v>1122</v>
       </c>
@@ -21394,7 +21393,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
         <v>1125</v>
       </c>
@@ -21423,7 +21422,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
         <v>1128</v>
       </c>
@@ -21452,7 +21451,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
         <v>1131</v>
       </c>
@@ -21510,7 +21509,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
         <v>1137</v>
       </c>
@@ -21539,7 +21538,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
         <v>1140</v>
       </c>
@@ -21568,7 +21567,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
         <v>1143</v>
       </c>
@@ -21597,7 +21596,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
         <v>1146</v>
       </c>
@@ -21626,7 +21625,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
         <v>1149</v>
       </c>
@@ -21655,7 +21654,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
         <v>1152</v>
       </c>
@@ -21684,7 +21683,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
         <v>1155</v>
       </c>
@@ -21713,7 +21712,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
         <v>1158</v>
       </c>
@@ -21742,7 +21741,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
         <v>1161</v>
       </c>
@@ -21771,7 +21770,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
         <v>1164</v>
       </c>
@@ -21800,7 +21799,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
         <v>1167</v>
       </c>
@@ -21829,7 +21828,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
         <v>1170</v>
       </c>
@@ -21858,7 +21857,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
         <v>1173</v>
       </c>
@@ -21887,7 +21886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
         <v>1176</v>
       </c>
@@ -21916,7 +21915,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
         <v>1179</v>
       </c>
@@ -21945,7 +21944,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
         <v>1182</v>
       </c>
@@ -21974,7 +21973,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
         <v>1185</v>
       </c>
@@ -22003,7 +22002,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
         <v>1188</v>
       </c>
@@ -22061,7 +22060,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
         <v>1194</v>
       </c>
@@ -22090,7 +22089,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
         <v>1197</v>
       </c>
@@ -22119,7 +22118,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
         <v>1200</v>
       </c>
@@ -22148,7 +22147,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
         <v>1203</v>
       </c>
@@ -22177,7 +22176,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
         <v>1206</v>
       </c>
@@ -22206,7 +22205,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
         <v>1209</v>
       </c>
@@ -22235,7 +22234,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
         <v>1212</v>
       </c>
@@ -22264,7 +22263,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
         <v>1215</v>
       </c>
@@ -22293,7 +22292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
         <v>1218</v>
       </c>
@@ -22322,7 +22321,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
         <v>1221</v>
       </c>
@@ -22351,7 +22350,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
         <v>1224</v>
       </c>
@@ -22380,7 +22379,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
         <v>1227</v>
       </c>
@@ -22438,7 +22437,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
         <v>1233</v>
       </c>
@@ -22467,7 +22466,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
         <v>1236</v>
       </c>
@@ -22496,7 +22495,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
         <v>1239</v>
       </c>
@@ -22525,7 +22524,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
         <v>1242</v>
       </c>
@@ -22554,7 +22553,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
         <v>1245</v>
       </c>
@@ -22583,7 +22582,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
         <v>1248</v>
       </c>
@@ -22612,7 +22611,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
         <v>1251</v>
       </c>
@@ -22641,7 +22640,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
         <v>1254</v>
       </c>
@@ -22670,7 +22669,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
         <v>1257</v>
       </c>
@@ -22699,7 +22698,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
         <v>1260</v>
       </c>
@@ -22728,7 +22727,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
         <v>1263</v>
       </c>
@@ -22757,7 +22756,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
         <v>1266</v>
       </c>
@@ -22786,7 +22785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
         <v>1269</v>
       </c>
@@ -22815,7 +22814,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
         <v>1272</v>
       </c>
@@ -22844,7 +22843,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
         <v>1275</v>
       </c>
@@ -22873,7 +22872,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
         <v>1278</v>
       </c>
@@ -22902,7 +22901,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
         <v>1281</v>
       </c>
@@ -22960,7 +22959,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
         <v>1287</v>
       </c>
@@ -22989,7 +22988,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
         <v>1290</v>
       </c>
@@ -23018,7 +23017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
         <v>1293</v>
       </c>
@@ -23047,7 +23046,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
         <v>1296</v>
       </c>
@@ -23076,7 +23075,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
         <v>1299</v>
       </c>
@@ -23105,7 +23104,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
         <v>1302</v>
       </c>
@@ -23134,7 +23133,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
         <v>1305</v>
       </c>
@@ -23163,7 +23162,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
         <v>1308</v>
       </c>
@@ -23192,7 +23191,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
         <v>1311</v>
       </c>
@@ -23221,7 +23220,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
         <v>1314</v>
       </c>
@@ -23250,7 +23249,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
         <v>1317</v>
       </c>
@@ -23279,7 +23278,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
         <v>1320</v>
       </c>
@@ -23308,7 +23307,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
         <v>1323</v>
       </c>
@@ -23337,7 +23336,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
         <v>1326</v>
       </c>
@@ -23366,7 +23365,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
         <v>1329</v>
       </c>
@@ -23395,7 +23394,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
         <v>1332</v>
       </c>
@@ -23424,7 +23423,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
         <v>1335</v>
       </c>
@@ -23453,7 +23452,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
         <v>1338</v>
       </c>
@@ -23482,7 +23481,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
         <v>1341</v>
       </c>
@@ -23511,7 +23510,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
         <v>1344</v>
       </c>
@@ -23540,7 +23539,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
         <v>1347</v>
       </c>
@@ -23569,7 +23568,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
         <v>1350</v>
       </c>
@@ -23598,7 +23597,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
         <v>1353</v>
       </c>
@@ -23627,7 +23626,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
         <v>1356</v>
       </c>
@@ -23656,7 +23655,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
         <v>1359</v>
       </c>
@@ -23714,7 +23713,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
         <v>1365</v>
       </c>
@@ -23743,7 +23742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="s">
         <v>1368</v>
       </c>
@@ -23772,7 +23771,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
         <v>1371</v>
       </c>
@@ -23801,7 +23800,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
         <v>1374</v>
       </c>
@@ -23830,7 +23829,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
         <v>1377</v>
       </c>
@@ -23859,7 +23858,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
         <v>1380</v>
       </c>
@@ -23888,7 +23887,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="s">
         <v>1383</v>
       </c>
@@ -23917,7 +23916,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="s">
         <v>1386</v>
       </c>
@@ -23946,7 +23945,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="s">
         <v>1389</v>
       </c>
@@ -24004,7 +24003,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="s">
         <v>1395</v>
       </c>
@@ -24033,7 +24032,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A460" s="2" t="s">
         <v>1398</v>
       </c>
@@ -24062,7 +24061,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
         <v>1401</v>
       </c>
@@ -24091,7 +24090,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
         <v>1404</v>
       </c>
@@ -24120,7 +24119,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
         <v>1407</v>
       </c>
@@ -24149,7 +24148,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A464" s="2" t="s">
         <v>1410</v>
       </c>
@@ -24178,7 +24177,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
         <v>1413</v>
       </c>
@@ -24207,7 +24206,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
         <v>1416</v>
       </c>
@@ -24236,7 +24235,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
         <v>1419</v>
       </c>
@@ -24265,7 +24264,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
         <v>1422</v>
       </c>
@@ -24294,7 +24293,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A469" s="2" t="s">
         <v>1425</v>
       </c>
@@ -24323,7 +24322,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A470" s="2" t="s">
         <v>1428</v>
       </c>
@@ -24352,7 +24351,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A471" s="2" t="s">
         <v>1431</v>
       </c>
@@ -24381,7 +24380,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="472" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A472" s="2" t="s">
         <v>1434</v>
       </c>
@@ -24410,7 +24409,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="473" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A473" s="2" t="s">
         <v>1437</v>
       </c>
@@ -24439,7 +24438,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
         <v>1440</v>
       </c>
@@ -24497,7 +24496,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A476" s="2" t="s">
         <v>1446</v>
       </c>
@@ -24526,7 +24525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A477" s="2" t="s">
         <v>1449</v>
       </c>
@@ -24555,7 +24554,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A478" s="2" t="s">
         <v>1452</v>
       </c>
@@ -24584,7 +24583,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A479" s="2" t="s">
         <v>1455</v>
       </c>
@@ -24613,7 +24612,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A480" s="2" t="s">
         <v>1458</v>
       </c>
@@ -24642,7 +24641,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A481" s="2" t="s">
         <v>1461</v>
       </c>
@@ -24671,7 +24670,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A482" s="2" t="s">
         <v>1464</v>
       </c>
@@ -24700,7 +24699,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
         <v>1467</v>
       </c>
@@ -24729,7 +24728,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A484" s="2" t="s">
         <v>1470</v>
       </c>
@@ -24758,7 +24757,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="485" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A485" s="2" t="s">
         <v>1473</v>
       </c>
@@ -24787,7 +24786,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A486" s="2" t="s">
         <v>1476</v>
       </c>
@@ -24816,7 +24815,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A487" s="2" t="s">
         <v>1479</v>
       </c>
@@ -24845,7 +24844,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="488" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A488" s="2" t="s">
         <v>1482</v>
       </c>
@@ -24874,7 +24873,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A489" s="2" t="s">
         <v>1485</v>
       </c>
@@ -24903,7 +24902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A490" s="2" t="s">
         <v>1488</v>
       </c>
@@ -24932,7 +24931,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A491" s="2" t="s">
         <v>1491</v>
       </c>
@@ -24990,7 +24989,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A493" s="2" t="s">
         <v>1497</v>
       </c>
@@ -25019,7 +25018,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="494" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A494" s="2" t="s">
         <v>1500</v>
       </c>
@@ -25048,7 +25047,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="495" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A495" s="2" t="s">
         <v>1503</v>
       </c>
@@ -25077,7 +25076,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A496" s="2" t="s">
         <v>1506</v>
       </c>
@@ -25106,7 +25105,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A497" s="2" t="s">
         <v>1509</v>
       </c>
@@ -25135,7 +25134,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="498" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A498" s="2" t="s">
         <v>1512</v>
       </c>
@@ -25164,7 +25163,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A499" s="2" t="s">
         <v>1515</v>
       </c>
@@ -25193,7 +25192,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A500" s="2" t="s">
         <v>1518</v>
       </c>
@@ -25222,7 +25221,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="501" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A501" s="2" t="s">
         <v>1521</v>
       </c>
@@ -25251,7 +25250,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="502" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A502" s="2" t="s">
         <v>1524</v>
       </c>
@@ -25280,7 +25279,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A503" s="2" t="s">
         <v>1527</v>
       </c>
@@ -25309,7 +25308,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A504" s="2" t="s">
         <v>1530</v>
       </c>
@@ -25338,7 +25337,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A505" s="2" t="s">
         <v>1533</v>
       </c>
@@ -25367,7 +25366,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A506" s="2" t="s">
         <v>1536</v>
       </c>
@@ -25396,7 +25395,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A507" s="2" t="s">
         <v>1539</v>
       </c>
@@ -25425,7 +25424,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A508" s="2" t="s">
         <v>1542</v>
       </c>
@@ -25454,7 +25453,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A509" s="2" t="s">
         <v>1545</v>
       </c>
@@ -25483,7 +25482,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A510" s="2" t="s">
         <v>1548</v>
       </c>
@@ -25512,7 +25511,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A511" s="2" t="s">
         <v>1551</v>
       </c>
@@ -25541,7 +25540,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A512" s="2" t="s">
         <v>1554</v>
       </c>
@@ -25570,7 +25569,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A513" s="2" t="s">
         <v>1557</v>
       </c>
@@ -25599,7 +25598,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A514" s="2" t="s">
         <v>1560</v>
       </c>
@@ -25628,7 +25627,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A515" s="2" t="s">
         <v>1563</v>
       </c>
@@ -25657,7 +25656,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A516" s="2" t="s">
         <v>1566</v>
       </c>
@@ -25686,7 +25685,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A517" s="2" t="s">
         <v>1569</v>
       </c>
@@ -25715,7 +25714,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A518" s="2" t="s">
         <v>1572</v>
       </c>
@@ -25744,7 +25743,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A519" s="2" t="s">
         <v>1575</v>
       </c>
@@ -25773,7 +25772,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A520" s="2" t="s">
         <v>1578</v>
       </c>
@@ -25802,7 +25801,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A521" s="2" t="s">
         <v>1581</v>
       </c>
@@ -25860,7 +25859,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A523" s="2" t="s">
         <v>1587</v>
       </c>
@@ -25889,7 +25888,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A524" s="2" t="s">
         <v>1590</v>
       </c>
@@ -25918,7 +25917,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A525" s="2" t="s">
         <v>1593</v>
       </c>
@@ -25947,7 +25946,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A526" s="2" t="s">
         <v>1596</v>
       </c>
@@ -25976,7 +25975,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A527" s="2" t="s">
         <v>1599</v>
       </c>
@@ -26005,7 +26004,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A528" s="2" t="s">
         <v>1602</v>
       </c>
@@ -26034,7 +26033,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A529" s="2" t="s">
         <v>1605</v>
       </c>
@@ -26063,7 +26062,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A530" s="2" t="s">
         <v>1608</v>
       </c>
@@ -26092,7 +26091,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A531" s="2" t="s">
         <v>1611</v>
       </c>
@@ -26121,7 +26120,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A532" s="2" t="s">
         <v>1614</v>
       </c>
@@ -26150,7 +26149,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A533" s="2" t="s">
         <v>1617</v>
       </c>
@@ -26179,7 +26178,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A534" s="2" t="s">
         <v>1620</v>
       </c>
@@ -26208,7 +26207,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A535" s="2" t="s">
         <v>1623</v>
       </c>
@@ -26237,7 +26236,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A536" s="2" t="s">
         <v>1626</v>
       </c>
@@ -26266,7 +26265,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A537" s="2" t="s">
         <v>1629</v>
       </c>
@@ -26295,7 +26294,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A538" s="2" t="s">
         <v>1632</v>
       </c>
@@ -26324,7 +26323,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A539" s="2" t="s">
         <v>1635</v>
       </c>
@@ -26353,7 +26352,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A540" s="2" t="s">
         <v>1638</v>
       </c>
@@ -26382,7 +26381,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A541" s="2" t="s">
         <v>1641</v>
       </c>
@@ -26469,7 +26468,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A544" s="2" t="s">
         <v>1650</v>
       </c>
@@ -26498,7 +26497,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A545" s="2" t="s">
         <v>1653</v>
       </c>
@@ -26527,7 +26526,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A546" s="2" t="s">
         <v>1656</v>
       </c>
@@ -26556,7 +26555,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A547" s="2" t="s">
         <v>1659</v>
       </c>
@@ -26585,7 +26584,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A548" s="2" t="s">
         <v>1662</v>
       </c>
@@ -26614,7 +26613,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A549" s="2" t="s">
         <v>1665</v>
       </c>
@@ -26643,7 +26642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A550" s="2" t="s">
         <v>1668</v>
       </c>
@@ -26672,7 +26671,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A551" s="2" t="s">
         <v>1671</v>
       </c>
@@ -26730,7 +26729,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A553" s="2" t="s">
         <v>1677</v>
       </c>
@@ -26759,7 +26758,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A554" s="2" t="s">
         <v>1680</v>
       </c>
@@ -26788,7 +26787,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A555" s="2" t="s">
         <v>1683</v>
       </c>
@@ -26817,7 +26816,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A556" s="2" t="s">
         <v>1686</v>
       </c>
@@ -26846,7 +26845,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A557" s="2" t="s">
         <v>1689</v>
       </c>
@@ -26875,7 +26874,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A558" s="2" t="s">
         <v>1692</v>
       </c>
@@ -26904,7 +26903,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A559" s="2" t="s">
         <v>1695</v>
       </c>
@@ -26933,7 +26932,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A560" s="2" t="s">
         <v>1698</v>
       </c>
@@ -26962,7 +26961,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A561" s="2" t="s">
         <v>1701</v>
       </c>
@@ -26991,7 +26990,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A562" s="2" t="s">
         <v>1704</v>
       </c>
@@ -27021,13 +27020,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I562" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="Grupo 5 - Aula A8"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I562" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/assets/data/Grupos_66.xlsx
+++ b/src/assets/data/Grupos_66.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Santiago Castro\Documents\github\agenda-jfd-69-cue\src\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B0B851-06AB-4F7A-B9A9-EBE4B93E40AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0919AC58-FA97-4267-8BC2-043DCE744983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18667,7 +18667,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>843</v>
       </c>
@@ -18693,7 +18693,7 @@
         <v>37</v>
       </c>
       <c r="I275" s="18" t="s">
-        <v>37</v>
+        <v>3391</v>
       </c>
     </row>
     <row r="276" spans="1:9" ht="24" x14ac:dyDescent="0.3">

--- a/src/assets/data/Grupos_66.xlsx
+++ b/src/assets/data/Grupos_66.xlsx
@@ -2,38 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convocatoria" sheetId="1" r:id="R7bcb7bb410114b07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mié-Jue detalle" sheetId="2" r:id="R939b64cd8bfa4c1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="3" r:id="R5890896995bf460a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Resumen" sheetId="4" r:id="Rfc1ce6e2872c418d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 1" sheetId="5" r:id="R40576c7a13d94b01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 2" sheetId="6" r:id="R53a56163f63f4cf8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 3" sheetId="7" r:id="R880deb3562784f78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 4" sheetId="8" r:id="R48cfe34834f34ba7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 5" sheetId="9" r:id="Re51b4f8597604d9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 6" sheetId="10" r:id="R3014a14e24e6479d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 7" sheetId="11" r:id="Rcbf2eb6461cd42fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 8" sheetId="12" r:id="Rec8558e225074ce4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Pendientes" sheetId="13" r:id="R6b9ae463d6224feb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Resumen" sheetId="14" r:id="R084736dd986d45e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 1" sheetId="15" r:id="Rccb189f7d37d44b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 2" sheetId="16" r:id="R515ab5381f0843a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 3" sheetId="17" r:id="R8b1361c464144737"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 4" sheetId="18" r:id="Rc3ca7ea3cef043cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 5" sheetId="19" r:id="R6743f49dfaad4be4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 6" sheetId="20" r:id="Rf522d67c4739431d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 7" sheetId="21" r:id="R091c5f338d584c61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 1" sheetId="22" r:id="Rc36ce1f7363f4f86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 2" sheetId="23" r:id="Re9e86a5de2b54d07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 3" sheetId="24" r:id="Re5df4edb1fae45be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 4" sheetId="25" r:id="R89f700816a424289"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 5" sheetId="26" r:id="R8d1aac19e96b4a74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 6" sheetId="27" r:id="R69f16679de9e4c5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 7" sheetId="28" r:id="R84d313bcf1da40aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 8" sheetId="29" r:id="Rcb54fdfe5a4847b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 9" sheetId="30" r:id="Rfcdc38c627f344bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T6 Resumen" sheetId="31" r:id="R1f5f09fa7d94414b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inactivos fuente" sheetId="32" r:id="R11e15c5f5ed34816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convocatoria" sheetId="1" r:id="Rb3d0eb2910574fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mié-Jue detalle" sheetId="2" r:id="R1016835159844824"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="3" r:id="R674f938606914ecd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Resumen" sheetId="4" r:id="R535eb3b20ba64efc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 1" sheetId="5" r:id="Rc5dfc4c125364462"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 2" sheetId="6" r:id="R9643fe5c361442e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 3" sheetId="7" r:id="Rd108cbf436724495"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 4" sheetId="8" r:id="R90c49f6bb3e6431c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 5" sheetId="9" r:id="R5babb0d64ccc4ea9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 6" sheetId="10" r:id="R4a149e4c06e04984"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 7" sheetId="11" r:id="Rd453f7e65fa945a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Grupo 8" sheetId="12" r:id="R4f196153fcf947f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Pendientes" sheetId="13" r:id="R56dfd56284364159"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Resumen" sheetId="14" r:id="R9fff48390c4b4b57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 1" sheetId="15" r:id="R10d8735b7ae24073"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 2" sheetId="16" r:id="R1cdbaf18027f405e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 3" sheetId="17" r:id="R2a8529eda46f41a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 4" sheetId="18" r:id="Rf5f1fcd7f190495b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 5" sheetId="19" r:id="R60afc4e2aab14c14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 6" sheetId="20" r:id="R9831159632b843a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 7" sheetId="21" r:id="R605d657b762e499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 1" sheetId="22" r:id="R66cda48a3c9a4aa1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 2" sheetId="23" r:id="Reb89be6d77814128"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 3" sheetId="24" r:id="Rd0dda00388bb43c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 4" sheetId="25" r:id="Racb6cbd770a349f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 5" sheetId="26" r:id="R56d7f54ac0b14117"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 6" sheetId="27" r:id="Re13dd5ffc1ba461a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 7" sheetId="28" r:id="R53c0e8c88f1c42c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 8" sheetId="29" r:id="Ree8c34c610e94148"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 9" sheetId="30" r:id="Raf9e5c7e2b9e4a03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T6 Resumen" sheetId="31" r:id="R1178a8cb4f584df0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inactivos fuente" sheetId="32" r:id="Rcedec69e245a4df6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Directores carrera" sheetId="33" r:id="R14963adc5d46412b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -209,7 +210,17 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="1">
+  <x:dxfs count="2">
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
     <x:dxf>
       <x:font>
         <x:color rgb="FF9C6500"/>
@@ -1222,10 +1233,10 @@
         <x:v>Grupo 5 - Aula D204</x:v>
       </x:c>
       <x:c r="H27" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 5 - Aula D204</x:v>
       </x:c>
       <x:c r="I27" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 5 - Aula D204</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="65" customHeight="1">
@@ -2121,10 +2132,10 @@
         <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="H58" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="I58" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="65" customHeight="1">
@@ -2295,10 +2306,10 @@
         <x:v>Grupo 5 - Aula D204</x:v>
       </x:c>
       <x:c r="H64" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 5 - Aula D204</x:v>
       </x:c>
       <x:c r="I64" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 5 - Aula D204</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="65" customHeight="1">
@@ -3194,10 +3205,10 @@
         <x:v>Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="H95" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="I95" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 2 - Aula D201</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="65" customHeight="1">
@@ -3368,10 +3379,10 @@
         <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="H101" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="I101" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="65" customHeight="1">
@@ -3455,10 +3466,10 @@
         <x:v>Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="H104" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="I104" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 4 - Aula D203</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="65" customHeight="1">
@@ -5079,10 +5090,10 @@
         <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="H160" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="I160" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="65" customHeight="1">
@@ -6384,10 +6395,10 @@
         <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="H205" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="I205" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="65" customHeight="1">
@@ -6471,10 +6482,10 @@
         <x:v>Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="H208" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="I208" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 4 - Aula D203</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="65" customHeight="1">
@@ -7747,10 +7758,10 @@
         <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="H252" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="I252" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
     </x:row>
     <x:row r="253" ht="65" customHeight="1">
@@ -8615,10 +8626,10 @@
         <x:v>Grupo 1 - Aula D200</x:v>
       </x:c>
       <x:c r="H282" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 1 - Aula D200</x:v>
       </x:c>
       <x:c r="I282" s="9" t="str">
-        <x:v>No Convocado</x:v>
+        <x:v>Grupo 1 - Aula D200</x:v>
       </x:c>
     </x:row>
     <x:row r="283" ht="65" customHeight="1">
@@ -10626,7 +10637,7 @@
       </x:c>
       <x:c r="D3" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$H$2:$H$299,A3)</x:f>
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
         <x:v>ADMINISTRACIÓN Y ECONOMÍA</x:v>
@@ -10645,7 +10656,7 @@
       </x:c>
       <x:c r="D4" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$H$2:$H$299,A4)</x:f>
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
         <x:v>CCSS Y DEL COMPORTAMIENTO HUMANO, HUMANIDADES</x:v>
@@ -10660,11 +10671,11 @@
 CORDOVA LEON JOSE RENATO (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
-        <x:v>BIOMEDICINA, ELECTRICIDAD, ELECTRONICA Y AUTOMATIZACION, INGENIERIA AUTOMOTRIZ, MECATRONICA, TELECOMUNICACIONES</x:v>
+        <x:v>BIOMEDICINA, ELECTRICIDAD, ELECTRONICA Y AUTOMATIZACION, INGENIERIA AUTOMOTRIZ, INGENIERIA INDUSTRIAL, MECATRONICA, TELECOMUNICACIONES</x:v>
       </x:c>
       <x:c r="D5" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$H$2:$H$299,A5)</x:f>
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
         <x:v>CIENCIA Y TECNOLOGÍA | CIENCIAS EXACTAS</x:v>
@@ -10679,11 +10690,11 @@
 PEÑA MONTOYA PEDRO GERARDO (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="C6" s="4" t="str">
-        <x:v>ARQUITECTURA, COMPUTACION, INGENIERIA CIVIL, INGENIERIA ELECTRICA, INGENIERIA INDUSTRIAL, MAESTRIA EN ANALITICA DE DATOS, MAESTRÍA EN SEGURIDAD, SALUD E HIGIENE INDUSTRIAL, SEGURIDAD DE LA INFORMACION-LINEA, TECNOLOGIA ELECTRICIDAD INDUSTRIAL, TECNOLOGIA MECANICA INDUSTRIAL</x:v>
+        <x:v>ARQUITECTURA, COMPUTACION, INGENIERIA AUTOMOTRIZ, INGENIERIA CIVIL, INGENIERIA ELECTRICA, INGENIERIA INDUSTRIAL, MAESTRIA EN ANALITICA DE DATOS, MAESTRÍA EN SEGURIDAD, SALUD E HIGIENE INDUSTRIAL, SEGURIDAD DE LA INFORMACION-LINEA, TECNOLOGIA ELECTRICIDAD INDUSTRIAL, TECNOLOGIA MECANICA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="D6" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$H$2:$H$299,A6)</x:f>
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
         <x:v>CIENCIA Y TECNOLOGÍA | CIENCIAS EXACTAS</x:v>
@@ -10702,7 +10713,7 @@
       </x:c>
       <x:c r="D7" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$H$2:$H$299,A7)</x:f>
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
         <x:v>CIENCIAS DE LA VIDA | SALUD</x:v>
@@ -10721,7 +10732,7 @@
       </x:c>
       <x:c r="D8" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$H$2:$H$299,A8)</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
         <x:v>EDUCACIÓN</x:v>
@@ -10754,7 +10765,7 @@
       <x:c r="C10" s="25"/>
       <x:c r="D10" s="26" t="n">
         <x:f>SUM(D3:D9)</x:f>
-        <x:v>168</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E10" s="25"/>
     </x:row>
@@ -10766,7 +10777,7 @@
       <x:c r="C11" s="4"/>
       <x:c r="D11" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$H$2:$H$299,A11)</x:f>
-        <x:v>130</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E11" s="4"/>
     </x:row>
@@ -11626,19 +11637,19 @@
         <x:v>Aula D200</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
+        <x:v>ECONOMIA</x:v>
       </x:c>
       <x:c r="F28" s="8" t="str">
-        <x:v>0924287097</x:v>
+        <x:v>0917770778</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>VERA SANTISTEVAN</x:v>
+        <x:v>VALLEJO LEON</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>VICTOR PATRICIO</x:v>
+        <x:v>KARINA ROXANA</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>vvera@ups.edu.ec</x:v>
+        <x:v>kvallejo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="92" customHeight="1">
@@ -11656,19 +11667,19 @@
         <x:v>Aula D200</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>NEGOCIOS DIGITALES</x:v>
+        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>1204142937</x:v>
+        <x:v>0924287097</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>VILLACRES BELTRAN</x:v>
+        <x:v>VERA SANTISTEVAN</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>FABIAN ISAAC</x:v>
+        <x:v>VICTOR PATRICIO</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>fvillacres@ups.edu.ec</x:v>
+        <x:v>vvera@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="92" customHeight="1">
@@ -11689,16 +11700,16 @@
         <x:v>NEGOCIOS DIGITALES</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>1103515902</x:v>
+        <x:v>1204142937</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>YAGUANA HERRERA</x:v>
+        <x:v>VILLACRES BELTRAN</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>TANIA GUADALUPE</x:v>
+        <x:v>FABIAN ISAAC</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>tyaguana@ups.edu.ec</x:v>
+        <x:v>fvillacres@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="92" customHeight="1">
@@ -11716,19 +11727,19 @@
         <x:v>Aula D200</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
+        <x:v>NEGOCIOS DIGITALES</x:v>
       </x:c>
       <x:c r="F31" s="8" t="str">
-        <x:v>0917360554</x:v>
+        <x:v>1103515902</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>ZAMBRANO PARRALES</x:v>
+        <x:v>YAGUANA HERRERA</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>FLORA ANGELICA</x:v>
+        <x:v>TANIA GUADALUPE</x:v>
       </x:c>
       <x:c r="I31" s="4" t="str">
-        <x:v>fzambrano@ups.edu.ec</x:v>
+        <x:v>tyaguana@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="92" customHeight="1">
@@ -11749,16 +11760,16 @@
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
       </x:c>
       <x:c r="F32" s="8" t="str">
-        <x:v>0923726772</x:v>
+        <x:v>0917360554</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
-        <x:v>ZEA VILLACIS</x:v>
+        <x:v>ZAMBRANO PARRALES</x:v>
       </x:c>
       <x:c r="H32" s="4" t="str">
-        <x:v>NORMA MARGARITA</x:v>
+        <x:v>FLORA ANGELICA</x:v>
       </x:c>
       <x:c r="I32" s="4" t="str">
-        <x:v>nzea@ups.edu.ec</x:v>
+        <x:v>fzambrano@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="92" customHeight="1">
@@ -11779,15 +11790,45 @@
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
       </x:c>
       <x:c r="F33" s="8" t="str">
+        <x:v>0923726772</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>ZEA VILLACIS</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>NORMA MARGARITA</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>nzea@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="92" customHeight="1">
+      <x:c r="A34" s="9" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="str">
+        <x:v>FABIÁN LEONARDO CUESTA ASTUDILLO (DIRECTOR NACIONAL)
+ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
+      </x:c>
+      <x:c r="D34" s="4" t="str">
+        <x:v>Aula D200</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="str">
+        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
+      </x:c>
+      <x:c r="F34" s="8" t="str">
         <x:v>0917375537</x:v>
       </x:c>
-      <x:c r="G33" s="4" t="str">
+      <x:c r="G34" s="4" t="str">
         <x:v>ZUÑIGA ALVARADO</x:v>
       </x:c>
-      <x:c r="H33" s="4" t="str">
+      <x:c r="H34" s="4" t="str">
         <x:v>MARIA ALEJANDRA</x:v>
       </x:c>
-      <x:c r="I33" s="4" t="str">
+      <x:c r="I34" s="4" t="str">
         <x:v>mzunigaa@ups.edu.ec</x:v>
       </x:c>
     </x:row>
@@ -12024,19 +12065,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
-        <x:v>DISEÑO MULTIMEDIA</x:v>
+        <x:v>COMUNICACION SOCIAL</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str">
-        <x:v>0919098681</x:v>
+        <x:v>1202606404</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
-        <x:v>FIALLOS VARGAS</x:v>
+        <x:v>ESCOBAR TERAN</x:v>
       </x:c>
       <x:c r="H8" s="4" t="str">
-        <x:v>INGRID VERONICA</x:v>
+        <x:v>SUSAN CATHERINE</x:v>
       </x:c>
       <x:c r="I8" s="4" t="str">
-        <x:v>ifiallos@ups.edu.ec</x:v>
+        <x:v>sescobar@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="92" customHeight="1">
@@ -12054,19 +12095,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>COMUNICACION SOCIAL</x:v>
+        <x:v>DISEÑO MULTIMEDIA</x:v>
       </x:c>
       <x:c r="F9" s="8" t="str">
-        <x:v>1205726456</x:v>
+        <x:v>0919098681</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
-        <x:v>FLORES PERALTA</x:v>
+        <x:v>FIALLOS VARGAS</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>JUANA KATIUSCA</x:v>
+        <x:v>INGRID VERONICA</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
-        <x:v>jfloresp@ups.edu.ec</x:v>
+        <x:v>ifiallos@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="92" customHeight="1">
@@ -12084,19 +12125,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>DISEÑO MULTIMEDIA</x:v>
+        <x:v>COMUNICACION SOCIAL</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str">
-        <x:v>0927400747</x:v>
+        <x:v>1205726456</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
-        <x:v>LOPEZ RUIZ</x:v>
+        <x:v>FLORES PERALTA</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>GILDA NOELIA</x:v>
+        <x:v>JUANA KATIUSCA</x:v>
       </x:c>
       <x:c r="I10" s="4" t="str">
-        <x:v>glopez@ups.edu.ec</x:v>
+        <x:v>jfloresp@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="92" customHeight="1">
@@ -12114,19 +12155,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>DERECHO</x:v>
+        <x:v>DISEÑO MULTIMEDIA</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>0911023406</x:v>
+        <x:v>0927400747</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>MOREIRA ARGUDO</x:v>
+        <x:v>LOPEZ RUIZ</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>MARCOS FRANCISCO</x:v>
+        <x:v>GILDA NOELIA</x:v>
       </x:c>
       <x:c r="I11" s="4" t="str">
-        <x:v>mmoreiraa@ups.edu.ec</x:v>
+        <x:v>glopez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="92" customHeight="1">
@@ -12147,16 +12188,16 @@
         <x:v>DERECHO</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>0927079673</x:v>
+        <x:v>0911023406</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>NAVARRETE SANTANA</x:v>
+        <x:v>MOREIRA ARGUDO</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>ALEX MICHAELL</x:v>
+        <x:v>MARCOS FRANCISCO</x:v>
       </x:c>
       <x:c r="I12" s="4" t="str">
-        <x:v>anavarretes@ups.edu.ec</x:v>
+        <x:v>mmoreiraa@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="92" customHeight="1">
@@ -12174,19 +12215,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>DISEÑO MULTIMEDIA</x:v>
+        <x:v>DERECHO</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>0927230631</x:v>
+        <x:v>0927079673</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>PAREDES ESTRELLA</x:v>
+        <x:v>NAVARRETE SANTANA</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>GUILLERMO XAVIER</x:v>
+        <x:v>ALEX MICHAELL</x:v>
       </x:c>
       <x:c r="I13" s="4" t="str">
-        <x:v>gparedes@ups.edu.ec</x:v>
+        <x:v>anavarretes@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="92" customHeight="1">
@@ -12207,16 +12248,16 @@
         <x:v>DISEÑO MULTIMEDIA</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>0926631573</x:v>
+        <x:v>0927230631</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>PORTUGAL GOROZABEL</x:v>
+        <x:v>PAREDES ESTRELLA</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>JONATAN ANDRES</x:v>
+        <x:v>GUILLERMO XAVIER</x:v>
       </x:c>
       <x:c r="I14" s="4" t="str">
-        <x:v>jportugal@ups.edu.ec</x:v>
+        <x:v>gparedes@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="92" customHeight="1">
@@ -12234,19 +12275,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>DERECHO</x:v>
+        <x:v>DISEÑO MULTIMEDIA</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>0929557916</x:v>
+        <x:v>0926631573</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>QUITO MEGO</x:v>
+        <x:v>PORTUGAL GOROZABEL</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>ROSSMERY ASHLEY</x:v>
+        <x:v>JONATAN ANDRES</x:v>
       </x:c>
       <x:c r="I15" s="4" t="str">
-        <x:v>rquitom@ups.edu.ec</x:v>
+        <x:v>jportugal@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="92" customHeight="1">
@@ -12264,19 +12305,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>DISEÑO MULTIMEDIA</x:v>
+        <x:v>DERECHO</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>0918508573</x:v>
+        <x:v>0929557916</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>TOLEDO HERRERA</x:v>
+        <x:v>QUITO MEGO</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>LINDA JOHANIE</x:v>
+        <x:v>ROSSMERY ASHLEY</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>ltoledo@ups.edu.ec</x:v>
+        <x:v>rquitom@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="92" customHeight="1">
@@ -12297,15 +12338,45 @@
         <x:v>DISEÑO MULTIMEDIA</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
+        <x:v>0918508573</x:v>
+      </x:c>
+      <x:c r="G17" s="4" t="str">
+        <x:v>TOLEDO HERRERA</x:v>
+      </x:c>
+      <x:c r="H17" s="4" t="str">
+        <x:v>LINDA JOHANIE</x:v>
+      </x:c>
+      <x:c r="I17" s="4" t="str">
+        <x:v>ltoledo@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="92" customHeight="1">
+      <x:c r="A18" s="9" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B18" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C18" s="4" t="str">
+        <x:v>FLORALBA DEL ROCIO AGUILAR GORDON (DIRECTOR NACIONAL)
+PORTUGAL GOROZABEL JONATAN ANDRES (RESPONSABLE SEDE)</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="str">
+        <x:v>Aula D201</x:v>
+      </x:c>
+      <x:c r="E18" s="4" t="str">
+        <x:v>DISEÑO MULTIMEDIA</x:v>
+      </x:c>
+      <x:c r="F18" s="8" t="str">
         <x:v>0916155112</x:v>
       </x:c>
-      <x:c r="G17" s="4" t="str">
+      <x:c r="G18" s="4" t="str">
         <x:v>VELOZ ARCE</x:v>
       </x:c>
-      <x:c r="H17" s="4" t="str">
+      <x:c r="H18" s="4" t="str">
         <x:v>ALONSO EDUARDO</x:v>
       </x:c>
-      <x:c r="I17" s="4" t="str">
+      <x:c r="I18" s="4" t="str">
         <x:v>aveloz@ups.edu.ec</x:v>
       </x:c>
     </x:row>
@@ -12902,19 +12973,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>0923328629</x:v>
+        <x:v>0914335484</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>FRANCO REINA</x:v>
+        <x:v>FARIÑO CEDEÑO</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>RAFAEL CHRISTIAN</x:v>
+        <x:v>JORGE BLADIMIR</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>rfranco@ups.edu.ec</x:v>
+        <x:v>jfarino@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="92" customHeight="1">
@@ -12935,16 +13006,16 @@
         <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F21" s="8" t="str">
-        <x:v>0922357702</x:v>
+        <x:v>0923328629</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>GARCIA FLOR</x:v>
+        <x:v>FRANCO REINA</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>GEOVANNY XAVIER</x:v>
+        <x:v>RAFAEL CHRISTIAN</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>ggarciaf1@ups.edu.ec</x:v>
+        <x:v>rfranco@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="92" customHeight="1">
@@ -12962,19 +13033,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>MECATRONICA</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F22" s="8" t="str">
-        <x:v>0920256500</x:v>
+        <x:v>0922357702</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>GARCIA VASQUEZ</x:v>
+        <x:v>GARCIA FLOR</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>GABRIEL SANTIAGO</x:v>
+        <x:v>GEOVANNY XAVIER</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>ggarciav@ups.edu.ec</x:v>
+        <x:v>ggarciaf1@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="92" customHeight="1">
@@ -12995,16 +13066,16 @@
         <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>1802792646</x:v>
+        <x:v>0920256500</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>GAVILANEZ GAMBOA</x:v>
+        <x:v>GARCIA VASQUEZ</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>TOMAS SANTIAGO</x:v>
+        <x:v>GABRIEL SANTIAGO</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>tgavilanez@ups.edu.ec</x:v>
+        <x:v>ggarciav@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="92" customHeight="1">
@@ -13022,19 +13093,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>BIOMEDICINA</x:v>
+        <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F24" s="8" t="str">
-        <x:v>0912439486</x:v>
+        <x:v>1802792646</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>GRUNAUER ESPINOZA</x:v>
+        <x:v>GAVILANEZ GAMBOA</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>CECILIA CATALINA</x:v>
+        <x:v>TOMAS SANTIAGO</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>cgrunauer@ups.edu.ec</x:v>
+        <x:v>tgavilanez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="92" customHeight="1">
@@ -13052,19 +13123,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>MECATRONICA</x:v>
+        <x:v>BIOMEDICINA</x:v>
       </x:c>
       <x:c r="F25" s="8" t="str">
-        <x:v>0909627432</x:v>
+        <x:v>0912439486</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>KUONQUI GAINZA</x:v>
+        <x:v>GRUNAUER ESPINOZA</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>FRANKLIN ILLICH</x:v>
+        <x:v>CECILIA CATALINA</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>fkuonqui@ups.edu.ec</x:v>
+        <x:v>cgrunauer@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="92" customHeight="1">
@@ -13082,19 +13153,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F26" s="8" t="str">
-        <x:v>0923270136</x:v>
+        <x:v>0909627432</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>LARCO TORRES</x:v>
+        <x:v>KUONQUI GAINZA</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>VICTOR DAVID</x:v>
+        <x:v>FRANKLIN ILLICH</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>vlarco@ups.edu.ec</x:v>
+        <x:v>fkuonqui@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="92" customHeight="1">
@@ -13112,19 +13183,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>ELECTRICIDAD</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F27" s="8" t="str">
-        <x:v>0301791893</x:v>
+        <x:v>0923270136</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>LATA GARCIA</x:v>
+        <x:v>LARCO TORRES</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>JUAN CARLOS</x:v>
+        <x:v>VICTOR DAVID</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>jlatag@ups.edu.ec</x:v>
+        <x:v>vlarco@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="92" customHeight="1">
@@ -13142,19 +13213,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>ELECTRICIDAD</x:v>
       </x:c>
       <x:c r="F28" s="8" t="str">
-        <x:v>0909020679</x:v>
+        <x:v>0301791893</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>LLAGUNO VERA</x:v>
+        <x:v>LATA GARCIA</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>JORGE GREGORIO</x:v>
+        <x:v>JUAN CARLOS</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>jllaguno@ups.edu.ec</x:v>
+        <x:v>jlatag@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="92" customHeight="1">
@@ -13172,19 +13243,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>1105738395</x:v>
+        <x:v>0909020679</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>MALDONADO ORTEGA</x:v>
+        <x:v>LLAGUNO VERA</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>JOSE LUIS</x:v>
+        <x:v>JORGE GREGORIO</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>jmaldonadoo@ups.edu.ec</x:v>
+        <x:v>jllaguno@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="92" customHeight="1">
@@ -13202,19 +13273,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>0913608147</x:v>
+        <x:v>0912034790</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>MILLAN TRAVERSO</x:v>
+        <x:v>LOPEZ VARGAS</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>MARCOS EFRAIN</x:v>
+        <x:v>ARMANDO FABRIZZIO</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>mmillan@ups.edu.ec</x:v>
+        <x:v>alopez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="92" customHeight="1">
@@ -13232,19 +13303,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F31" s="8" t="str">
-        <x:v>0912419611</x:v>
+        <x:v>1105738395</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>NEGRETE PEÑA</x:v>
+        <x:v>MALDONADO ORTEGA</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>TEDDY JHENNSE</x:v>
+        <x:v>JOSE LUIS</x:v>
       </x:c>
       <x:c r="I31" s="4" t="str">
-        <x:v>tnegrete@ups.edu.ec</x:v>
+        <x:v>jmaldonadoo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="92" customHeight="1">
@@ -13265,16 +13336,16 @@
         <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F32" s="8" t="str">
-        <x:v>0916850274</x:v>
+        <x:v>0913608147</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
-        <x:v>NG ROBLES</x:v>
+        <x:v>MILLAN TRAVERSO</x:v>
       </x:c>
       <x:c r="H32" s="4" t="str">
-        <x:v>THOMAS LANHEN</x:v>
+        <x:v>MARCOS EFRAIN</x:v>
       </x:c>
       <x:c r="I32" s="4" t="str">
-        <x:v>tng@ups.edu.ec</x:v>
+        <x:v>mmillan@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="92" customHeight="1">
@@ -13292,19 +13363,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
-        <x:v>MECATRONICA</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F33" s="8" t="str">
-        <x:v>0923348890</x:v>
+        <x:v>0912419611</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
-        <x:v>RAMIREZ FARFAN</x:v>
+        <x:v>NEGRETE PEÑA</x:v>
       </x:c>
       <x:c r="H33" s="4" t="str">
-        <x:v>ALBERTO SANTIAGO</x:v>
+        <x:v>TEDDY JHENNSE</x:v>
       </x:c>
       <x:c r="I33" s="4" t="str">
-        <x:v>aramirezf@ups.edu.ec</x:v>
+        <x:v>tnegrete@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="92" customHeight="1">
@@ -13322,19 +13393,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E34" s="4" t="str">
-        <x:v>MECATRONICA</x:v>
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F34" s="8" t="str">
-        <x:v>0923848691</x:v>
+        <x:v>0916850274</x:v>
       </x:c>
       <x:c r="G34" s="4" t="str">
-        <x:v>REYES LOPEZ</x:v>
+        <x:v>NG ROBLES</x:v>
       </x:c>
       <x:c r="H34" s="4" t="str">
-        <x:v>CHRISTOPHER RUBEN</x:v>
+        <x:v>THOMAS LANHEN</x:v>
       </x:c>
       <x:c r="I34" s="4" t="str">
-        <x:v>creyesl@ups.edu.ec</x:v>
+        <x:v>tng@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="92" customHeight="1">
@@ -13352,19 +13423,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E35" s="4" t="str">
-        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F35" s="8" t="str">
-        <x:v>0104025838</x:v>
+        <x:v>0916113426</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
-        <x:v>ROCHE INTRIAGO</x:v>
+        <x:v>PEÑARANDA IDROVO</x:v>
       </x:c>
       <x:c r="H35" s="4" t="str">
-        <x:v>CARLOS WLADIMIR</x:v>
+        <x:v>VICENTE AVELINO</x:v>
       </x:c>
       <x:c r="I35" s="4" t="str">
-        <x:v>croche@ups.edu.ec</x:v>
+        <x:v>vpenaranda@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="92" customHeight="1">
@@ -13382,19 +13453,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E36" s="4" t="str">
-        <x:v>BIOMEDICINA</x:v>
+        <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F36" s="8" t="str">
-        <x:v>1206442616</x:v>
+        <x:v>0923348890</x:v>
       </x:c>
       <x:c r="G36" s="4" t="str">
-        <x:v>ROMERO SANTISTEVAN</x:v>
+        <x:v>RAMIREZ FARFAN</x:v>
       </x:c>
       <x:c r="H36" s="4" t="str">
-        <x:v>DARIO XAVIER</x:v>
+        <x:v>ALBERTO SANTIAGO</x:v>
       </x:c>
       <x:c r="I36" s="4" t="str">
-        <x:v>dromeros@ups.edu.ec</x:v>
+        <x:v>aramirezf@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="92" customHeight="1">
@@ -13412,19 +13483,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E37" s="4" t="str">
-        <x:v>ELECTRICIDAD</x:v>
+        <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F37" s="8" t="str">
-        <x:v>0923481915</x:v>
+        <x:v>0923848691</x:v>
       </x:c>
       <x:c r="G37" s="4" t="str">
-        <x:v>SOLANO VILLEGAS</x:v>
+        <x:v>REYES LOPEZ</x:v>
       </x:c>
       <x:c r="H37" s="4" t="str">
-        <x:v>ERVIN GEOVANNY</x:v>
+        <x:v>CHRISTOPHER RUBEN</x:v>
       </x:c>
       <x:c r="I37" s="4" t="str">
-        <x:v>esolano@ups.edu.ec</x:v>
+        <x:v>creyesl@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="92" customHeight="1">
@@ -13445,16 +13516,16 @@
         <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F38" s="8" t="str">
-        <x:v>1722909395</x:v>
+        <x:v>0104025838</x:v>
       </x:c>
       <x:c r="G38" s="4" t="str">
-        <x:v>TOTOY MONTERO</x:v>
+        <x:v>ROCHE INTRIAGO</x:v>
       </x:c>
       <x:c r="H38" s="4" t="str">
-        <x:v>PAUL HERNAN</x:v>
+        <x:v>CARLOS WLADIMIR</x:v>
       </x:c>
       <x:c r="I38" s="4" t="str">
-        <x:v>ptotoy@ups.edu.ec</x:v>
+        <x:v>croche@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="92" customHeight="1">
@@ -13472,18 +13543,138 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E39" s="4" t="str">
+        <x:v>BIOMEDICINA</x:v>
+      </x:c>
+      <x:c r="F39" s="8" t="str">
+        <x:v>1206442616</x:v>
+      </x:c>
+      <x:c r="G39" s="4" t="str">
+        <x:v>ROMERO SANTISTEVAN</x:v>
+      </x:c>
+      <x:c r="H39" s="4" t="str">
+        <x:v>DARIO XAVIER</x:v>
+      </x:c>
+      <x:c r="I39" s="4" t="str">
+        <x:v>dromeros@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="92" customHeight="1">
+      <x:c r="A40" s="9" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B40" s="9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C40" s="4" t="str">
+        <x:v>ROMEL EDUARDO RODAS ORELLANA (DIRECTOR NACIONAL)
+CORDOVA LEON JOSE RENATO (RESPONSABLE SEDE)</x:v>
+      </x:c>
+      <x:c r="D40" s="4" t="str">
+        <x:v>Aula D202</x:v>
+      </x:c>
+      <x:c r="E40" s="4" t="str">
+        <x:v>ELECTRICIDAD</x:v>
+      </x:c>
+      <x:c r="F40" s="8" t="str">
+        <x:v>0916303134</x:v>
+      </x:c>
+      <x:c r="G40" s="4" t="str">
+        <x:v>SANTILLAN CARRANZA</x:v>
+      </x:c>
+      <x:c r="H40" s="4" t="str">
+        <x:v>HOLGER JORGE</x:v>
+      </x:c>
+      <x:c r="I40" s="4" t="str">
+        <x:v>hsantillan@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="92" customHeight="1">
+      <x:c r="A41" s="9" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B41" s="9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C41" s="4" t="str">
+        <x:v>ROMEL EDUARDO RODAS ORELLANA (DIRECTOR NACIONAL)
+CORDOVA LEON JOSE RENATO (RESPONSABLE SEDE)</x:v>
+      </x:c>
+      <x:c r="D41" s="4" t="str">
+        <x:v>Aula D202</x:v>
+      </x:c>
+      <x:c r="E41" s="4" t="str">
+        <x:v>ELECTRICIDAD</x:v>
+      </x:c>
+      <x:c r="F41" s="8" t="str">
+        <x:v>0923481915</x:v>
+      </x:c>
+      <x:c r="G41" s="4" t="str">
+        <x:v>SOLANO VILLEGAS</x:v>
+      </x:c>
+      <x:c r="H41" s="4" t="str">
+        <x:v>ERVIN GEOVANNY</x:v>
+      </x:c>
+      <x:c r="I41" s="4" t="str">
+        <x:v>esolano@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="92" customHeight="1">
+      <x:c r="A42" s="9" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B42" s="9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C42" s="4" t="str">
+        <x:v>ROMEL EDUARDO RODAS ORELLANA (DIRECTOR NACIONAL)
+CORDOVA LEON JOSE RENATO (RESPONSABLE SEDE)</x:v>
+      </x:c>
+      <x:c r="D42" s="4" t="str">
+        <x:v>Aula D202</x:v>
+      </x:c>
+      <x:c r="E42" s="4" t="str">
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+      </x:c>
+      <x:c r="F42" s="8" t="str">
+        <x:v>1722909395</x:v>
+      </x:c>
+      <x:c r="G42" s="4" t="str">
+        <x:v>TOTOY MONTERO</x:v>
+      </x:c>
+      <x:c r="H42" s="4" t="str">
+        <x:v>PAUL HERNAN</x:v>
+      </x:c>
+      <x:c r="I42" s="4" t="str">
+        <x:v>ptotoy@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="92" customHeight="1">
+      <x:c r="A43" s="9" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B43" s="9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C43" s="4" t="str">
+        <x:v>ROMEL EDUARDO RODAS ORELLANA (DIRECTOR NACIONAL)
+CORDOVA LEON JOSE RENATO (RESPONSABLE SEDE)</x:v>
+      </x:c>
+      <x:c r="D43" s="4" t="str">
+        <x:v>Aula D202</x:v>
+      </x:c>
+      <x:c r="E43" s="4" t="str">
         <x:v>MECATRONICA</x:v>
       </x:c>
-      <x:c r="F39" s="8" t="str">
+      <x:c r="F43" s="8" t="str">
         <x:v>0801602160</x:v>
       </x:c>
-      <x:c r="G39" s="4" t="str">
+      <x:c r="G43" s="4" t="str">
         <x:v>VEGA URETA</x:v>
       </x:c>
-      <x:c r="H39" s="4" t="str">
+      <x:c r="H43" s="4" t="str">
         <x:v>NINO TELLO</x:v>
       </x:c>
-      <x:c r="I39" s="4" t="str">
+      <x:c r="I43" s="4" t="str">
         <x:v>nvega@ups.edu.ec</x:v>
       </x:c>
     </x:row>
@@ -13810,19 +14001,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>INGENIERIA CIVIL</x:v>
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>0919008201</x:v>
+        <x:v>1103588578</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>FONSECA MOTA</x:v>
+        <x:v>FIERRO JIMENEZ</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>EDUARDO SANTIAGO</x:v>
+        <x:v>PABLO RENATO</x:v>
       </x:c>
       <x:c r="I11" s="4" t="str">
-        <x:v>efonseca@ups.edu.ec</x:v>
+        <x:v>pfierro@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="92" customHeight="1">
@@ -13840,19 +14031,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>INGENIERIA CIVIL</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>0918123605</x:v>
+        <x:v>0919008201</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>GARCIA PEREZ</x:v>
+        <x:v>FONSECA MOTA</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>ALEX GUILLERMO</x:v>
+        <x:v>EDUARDO SANTIAGO</x:v>
       </x:c>
       <x:c r="I12" s="4" t="str">
-        <x:v>agarciap@ups.edu.ec</x:v>
+        <x:v>efonseca@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="92" customHeight="1">
@@ -13873,16 +14064,16 @@
         <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>0911019529</x:v>
+        <x:v>0918123605</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>GONZALEZ VASQUEZ</x:v>
+        <x:v>GARCIA PEREZ</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>ANGEL EDUARDO</x:v>
+        <x:v>ALEX GUILLERMO</x:v>
       </x:c>
       <x:c r="I13" s="4" t="str">
-        <x:v>agonzalez@ups.edu.ec</x:v>
+        <x:v>agarciap@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="92" customHeight="1">
@@ -13900,19 +14091,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>SEGURIDAD DE LA INFORMACION-LINEA</x:v>
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>0920375177</x:v>
+        <x:v>0911019529</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>HUILCAPI SUBIA</x:v>
+        <x:v>GONZALEZ VASQUEZ</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>DARIO FERNANDO</x:v>
+        <x:v>ANGEL EDUARDO</x:v>
       </x:c>
       <x:c r="I14" s="4" t="str">
-        <x:v>dhuilcapi@ups.edu.ec</x:v>
+        <x:v>agonzalez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="92" customHeight="1">
@@ -13930,19 +14121,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>SEGURIDAD DE LA INFORMACION-LINEA</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>0911047058</x:v>
+        <x:v>0920375177</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>LEON VEAS</x:v>
+        <x:v>HUILCAPI SUBIA</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>JOFFRE LUIS</x:v>
+        <x:v>DARIO FERNANDO</x:v>
       </x:c>
       <x:c r="I15" s="4" t="str">
-        <x:v>jleon@ups.edu.ec</x:v>
+        <x:v>dhuilcapi@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="92" customHeight="1">
@@ -13963,16 +14154,16 @@
         <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>0909257800</x:v>
+        <x:v>0911047058</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>MORA SALTOS</x:v>
+        <x:v>LEON VEAS</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>NELSON SALOMON</x:v>
+        <x:v>JOFFRE LUIS</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>nmora@ups.edu.ec</x:v>
+        <x:v>jleon@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="92" customHeight="1">
@@ -13990,19 +14181,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>INGENIERIA CIVIL</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>1310835457</x:v>
+        <x:v>0909257800</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>MOYA CHAVEZ</x:v>
+        <x:v>MORA SALTOS</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>LUIS EDUARDO</x:v>
+        <x:v>NELSON SALOMON</x:v>
       </x:c>
       <x:c r="I17" s="4" t="str">
-        <x:v>lmoya@ups.edu.ec</x:v>
+        <x:v>nmora@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="92" customHeight="1">
@@ -14020,19 +14211,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>INGENIERIA CIVIL</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
-        <x:v>0912380474</x:v>
+        <x:v>1310835457</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>NARANJO SANCHEZ</x:v>
+        <x:v>MOYA CHAVEZ</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>BERTHA ALICE</x:v>
+        <x:v>LUIS EDUARDO</x:v>
       </x:c>
       <x:c r="I18" s="4" t="str">
-        <x:v>bnaranjo@ups.edu.ec</x:v>
+        <x:v>lmoya@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="92" customHeight="1">
@@ -14053,16 +14244,16 @@
         <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>0916883093</x:v>
+        <x:v>0912380474</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
         <x:v>NARANJO SANCHEZ</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>RICARDO ALFREDO</x:v>
+        <x:v>BERTHA ALICE</x:v>
       </x:c>
       <x:c r="I19" s="4" t="str">
-        <x:v>rnaranjo@ups.edu.ec</x:v>
+        <x:v>bnaranjo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="92" customHeight="1">
@@ -14083,16 +14274,16 @@
         <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>0916522444</x:v>
+        <x:v>0916883093</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>ORTIZ ROJAS</x:v>
+        <x:v>NARANJO SANCHEZ</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>JAVIER GONZALO</x:v>
+        <x:v>RICARDO ALFREDO</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>jortiz@ups.edu.ec</x:v>
+        <x:v>rnaranjo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="92" customHeight="1">
@@ -14110,19 +14301,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>TECNOLOGIA ELECTRICIDAD INDUSTRIAL</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F21" s="8" t="str">
-        <x:v>0930313614</x:v>
+        <x:v>0916522444</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>PEÑA MARISCAL</x:v>
+        <x:v>ORTIZ ROJAS</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>NILO ANDRES</x:v>
+        <x:v>JAVIER GONZALO</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>npena@ups.edu.ec</x:v>
+        <x:v>jortiz@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="92" customHeight="1">
@@ -14140,19 +14331,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>INGENIERIA CIVIL</x:v>
+        <x:v>TECNOLOGIA ELECTRICIDAD INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F22" s="8" t="str">
-        <x:v>0914565148</x:v>
+        <x:v>0930313614</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>PEÑA MONTOYA</x:v>
+        <x:v>PEÑA MARISCAL</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>PEDRO GERARDO</x:v>
+        <x:v>NILO ANDRES</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>ppena@ups.edu.ec</x:v>
+        <x:v>npena@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="92" customHeight="1">
@@ -14170,19 +14361,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>INGENIERIA CIVIL</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>0920565066</x:v>
+        <x:v>0914565148</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>PIZARRO VASQUEZ</x:v>
+        <x:v>PEÑA MONTOYA</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>GUILLERMO OMAR</x:v>
+        <x:v>PEDRO GERARDO</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>gpizarro@ups.edu.ec</x:v>
+        <x:v>ppena@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="92" customHeight="1">
@@ -14200,19 +14391,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F24" s="8" t="str">
-        <x:v>1757049075</x:v>
+        <x:v>0920565066</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>PRECIADO VELASQUEZ</x:v>
+        <x:v>PIZARRO VASQUEZ</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>OSCAR EDUARDO</x:v>
+        <x:v>GUILLERMO OMAR</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>opreciadov@ups.edu.ec</x:v>
+        <x:v>gpizarro@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="92" customHeight="1">
@@ -14230,19 +14421,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>INGENIERIA CIVIL</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F25" s="8" t="str">
-        <x:v>1205363326</x:v>
+        <x:v>0920382785</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>PROAÑO VISCARRA</x:v>
+        <x:v>PLUA MORAN</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>KEVIN RICARDO</x:v>
+        <x:v>DANIEL HUMBERTO</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>kproano@ups.edu.ec</x:v>
+        <x:v>dplua@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="92" customHeight="1">
@@ -14260,19 +14451,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>MAESTRIA EN ANALITICA DE DATOS</x:v>
+        <x:v>ARQUITECTURA</x:v>
       </x:c>
       <x:c r="F26" s="8" t="str">
-        <x:v>0922799655</x:v>
+        <x:v>1757049075</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>QUIROZ MARTINEZ</x:v>
+        <x:v>PRECIADO VELASQUEZ</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>MIGUEL ANGEL</x:v>
+        <x:v>OSCAR EDUARDO</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>mquiroz@ups.edu.ec</x:v>
+        <x:v>opreciadov@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="92" customHeight="1">
@@ -14290,19 +14481,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
+        <x:v>INGENIERIA CIVIL</x:v>
       </x:c>
       <x:c r="F27" s="8" t="str">
-        <x:v>0924613334</x:v>
+        <x:v>1205363326</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>REYES SANCHEZ</x:v>
+        <x:v>PROAÑO VISCARRA</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>JORGE ANDRES</x:v>
+        <x:v>KEVIN RICARDO</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>jreyess@ups.edu.ec</x:v>
+        <x:v>kproano@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="92" customHeight="1">
@@ -14320,19 +14511,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>MAESTRÍA EN SEGURIDAD, SALUD E HIGIENE INDUSTRIAL</x:v>
+        <x:v>MAESTRIA EN ANALITICA DE DATOS</x:v>
       </x:c>
       <x:c r="F28" s="8" t="str">
-        <x:v>0919958363</x:v>
+        <x:v>0922799655</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>ROJAS PARRAGA</x:v>
+        <x:v>QUIROZ MARTINEZ</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>TANIA CATALINA</x:v>
+        <x:v>MIGUEL ANGEL</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>trojas@ups.edu.ec</x:v>
+        <x:v>mquiroz@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="92" customHeight="1">
@@ -14353,16 +14544,16 @@
         <x:v>ARQUITECTURA</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>0912805827</x:v>
+        <x:v>0924613334</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>SOTOMAYOR NAVARRO</x:v>
+        <x:v>REYES SANCHEZ</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>MARIA CAROLINA</x:v>
+        <x:v>JORGE ANDRES</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>msotomayorn@ups.edu.ec</x:v>
+        <x:v>jreyess@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="92" customHeight="1">
@@ -14380,19 +14571,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
+        <x:v>MAESTRÍA EN SEGURIDAD, SALUD E HIGIENE INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>1203815277</x:v>
+        <x:v>0919958363</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>TAMAYO MENDOZA</x:v>
+        <x:v>ROJAS PARRAGA</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>MARIA DE LOURDES</x:v>
+        <x:v>TANIA CATALINA</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>mtamayom@ups.edu.ec</x:v>
+        <x:v>trojas@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="92" customHeight="1">
@@ -14410,19 +14601,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>ARQUITECTURA</x:v>
       </x:c>
       <x:c r="F31" s="8" t="str">
-        <x:v>0914759576</x:v>
+        <x:v>0912805827</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>TEJADA ESCOBAR</x:v>
+        <x:v>SOTOMAYOR NAVARRO</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>FREDDY JAVIER</x:v>
+        <x:v>MARIA CAROLINA</x:v>
       </x:c>
       <x:c r="I31" s="4" t="str">
-        <x:v>ftejada@ups.edu.ec</x:v>
+        <x:v>msotomayorn@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="92" customHeight="1">
@@ -14440,19 +14631,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>ARQUITECTURA</x:v>
       </x:c>
       <x:c r="F32" s="8" t="str">
-        <x:v>0917242448</x:v>
+        <x:v>1203815277</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
-        <x:v>TERAN ALVARADO</x:v>
+        <x:v>TAMAYO MENDOZA</x:v>
       </x:c>
       <x:c r="H32" s="4" t="str">
-        <x:v>ANA FABIOLA</x:v>
+        <x:v>MARIA DE LOURDES</x:v>
       </x:c>
       <x:c r="I32" s="4" t="str">
-        <x:v>ateran@ups.edu.ec</x:v>
+        <x:v>mtamayom@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="92" customHeight="1">
@@ -14470,19 +14661,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F33" s="8" t="str">
-        <x:v>0926416298</x:v>
+        <x:v>0914759576</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
-        <x:v>TRUJILLO MOLINA</x:v>
+        <x:v>TEJADA ESCOBAR</x:v>
       </x:c>
       <x:c r="H33" s="4" t="str">
-        <x:v>ERICK SANTIAGO</x:v>
+        <x:v>FREDDY JAVIER</x:v>
       </x:c>
       <x:c r="I33" s="4" t="str">
-        <x:v>etrujillom@ups.edu.ec</x:v>
+        <x:v>ftejada@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="92" customHeight="1">
@@ -14500,19 +14691,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E34" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F34" s="8" t="str">
-        <x:v>0926416280</x:v>
+        <x:v>0917242448</x:v>
       </x:c>
       <x:c r="G34" s="4" t="str">
-        <x:v>TRUJILLO MOLINA</x:v>
+        <x:v>TERAN ALVARADO</x:v>
       </x:c>
       <x:c r="H34" s="4" t="str">
-        <x:v>JOEL DAVID</x:v>
+        <x:v>ANA FABIOLA</x:v>
       </x:c>
       <x:c r="I34" s="4" t="str">
-        <x:v>jtrujillom@ups.edu.ec</x:v>
+        <x:v>ateran@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="92" customHeight="1">
@@ -14530,19 +14721,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E35" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>ARQUITECTURA</x:v>
       </x:c>
       <x:c r="F35" s="8" t="str">
-        <x:v>0918552233</x:v>
+        <x:v>0926416298</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
-        <x:v>UGALDE VELASQUEZ</x:v>
+        <x:v>TRUJILLO MOLINA</x:v>
       </x:c>
       <x:c r="H35" s="4" t="str">
-        <x:v>LELYS ANDRES</x:v>
+        <x:v>ERICK SANTIAGO</x:v>
       </x:c>
       <x:c r="I35" s="4" t="str">
-        <x:v>lugalde@ups.edu.ec</x:v>
+        <x:v>etrujillom@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="92" customHeight="1">
@@ -14560,19 +14751,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E36" s="4" t="str">
-        <x:v>INGENIERIA CIVIL</x:v>
+        <x:v>ARQUITECTURA</x:v>
       </x:c>
       <x:c r="F36" s="8" t="str">
-        <x:v>0925766461</x:v>
+        <x:v>0926416280</x:v>
       </x:c>
       <x:c r="G36" s="4" t="str">
-        <x:v>VALERO FAJARDO</x:v>
+        <x:v>TRUJILLO MOLINA</x:v>
       </x:c>
       <x:c r="H36" s="4" t="str">
-        <x:v>CARLOS LUIS</x:v>
+        <x:v>JOEL DAVID</x:v>
       </x:c>
       <x:c r="I36" s="4" t="str">
-        <x:v>cvalero@ups.edu.ec</x:v>
+        <x:v>jtrujillom@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="92" customHeight="1">
@@ -14590,19 +14781,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E37" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F37" s="8" t="str">
-        <x:v>1705290128</x:v>
+        <x:v>0918552233</x:v>
       </x:c>
       <x:c r="G37" s="4" t="str">
-        <x:v>VALLADARES CARRILLO</x:v>
+        <x:v>UGALDE VELASQUEZ</x:v>
       </x:c>
       <x:c r="H37" s="4" t="str">
-        <x:v>ALVARO MANUEL</x:v>
+        <x:v>LELYS ANDRES</x:v>
       </x:c>
       <x:c r="I37" s="4" t="str">
-        <x:v>avalladares@ups.edu.ec</x:v>
+        <x:v>lugalde@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="92" customHeight="1">
@@ -14620,19 +14811,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E38" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>INGENIERIA CIVIL</x:v>
       </x:c>
       <x:c r="F38" s="8" t="str">
-        <x:v>0912511532</x:v>
+        <x:v>0925766461</x:v>
       </x:c>
       <x:c r="G38" s="4" t="str">
-        <x:v>VALVERDE LANDIVAR</x:v>
+        <x:v>VALERO FAJARDO</x:v>
       </x:c>
       <x:c r="H38" s="4" t="str">
-        <x:v>GALO ENRIQUE</x:v>
+        <x:v>CARLOS LUIS</x:v>
       </x:c>
       <x:c r="I38" s="4" t="str">
-        <x:v>gvalverde@ups.edu.ec</x:v>
+        <x:v>cvalero@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="92" customHeight="1">
@@ -14650,19 +14841,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E39" s="4" t="str">
-        <x:v>TECNOLOGIA MECANICA INDUSTRIAL</x:v>
+        <x:v>ARQUITECTURA</x:v>
       </x:c>
       <x:c r="F39" s="8" t="str">
-        <x:v>0923622476</x:v>
+        <x:v>1705290128</x:v>
       </x:c>
       <x:c r="G39" s="4" t="str">
-        <x:v>VILLAMARIN PINO</x:v>
+        <x:v>VALLADARES CARRILLO</x:v>
       </x:c>
       <x:c r="H39" s="4" t="str">
-        <x:v>JORGE ALFREDO</x:v>
+        <x:v>ALVARO MANUEL</x:v>
       </x:c>
       <x:c r="I39" s="4" t="str">
-        <x:v>jvillamarinp@ups.edu.ec</x:v>
+        <x:v>avalladares@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="92" customHeight="1">
@@ -14680,18 +14871,78 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E40" s="4" t="str">
+        <x:v>COMPUTACION</x:v>
+      </x:c>
+      <x:c r="F40" s="8" t="str">
+        <x:v>0912511532</x:v>
+      </x:c>
+      <x:c r="G40" s="4" t="str">
+        <x:v>VALVERDE LANDIVAR</x:v>
+      </x:c>
+      <x:c r="H40" s="4" t="str">
+        <x:v>GALO ENRIQUE</x:v>
+      </x:c>
+      <x:c r="I40" s="4" t="str">
+        <x:v>gvalverde@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="92" customHeight="1">
+      <x:c r="A41" s="9" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B41" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="4" t="str">
+        <x:v>SHEILA SERRANO VINCENTI (DIRECTOR NACIONAL)
+PEÑA MONTOYA PEDRO GERARDO (RESPONSABLE SEDE)</x:v>
+      </x:c>
+      <x:c r="D41" s="4" t="str">
+        <x:v>Aula D203</x:v>
+      </x:c>
+      <x:c r="E41" s="4" t="str">
+        <x:v>TECNOLOGIA MECANICA INDUSTRIAL</x:v>
+      </x:c>
+      <x:c r="F41" s="8" t="str">
+        <x:v>0923622476</x:v>
+      </x:c>
+      <x:c r="G41" s="4" t="str">
+        <x:v>VILLAMARIN PINO</x:v>
+      </x:c>
+      <x:c r="H41" s="4" t="str">
+        <x:v>JORGE ALFREDO</x:v>
+      </x:c>
+      <x:c r="I41" s="4" t="str">
+        <x:v>jvillamarinp@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="92" customHeight="1">
+      <x:c r="A42" s="9" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B42" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="4" t="str">
+        <x:v>SHEILA SERRANO VINCENTI (DIRECTOR NACIONAL)
+PEÑA MONTOYA PEDRO GERARDO (RESPONSABLE SEDE)</x:v>
+      </x:c>
+      <x:c r="D42" s="4" t="str">
+        <x:v>Aula D203</x:v>
+      </x:c>
+      <x:c r="E42" s="4" t="str">
         <x:v>ARQUITECTURA</x:v>
       </x:c>
-      <x:c r="F40" s="8" t="str">
+      <x:c r="F42" s="8" t="str">
         <x:v>0910867407</x:v>
       </x:c>
-      <x:c r="G40" s="4" t="str">
+      <x:c r="G42" s="4" t="str">
         <x:v>VITERI PALOMEQUE</x:v>
       </x:c>
-      <x:c r="H40" s="4" t="str">
+      <x:c r="H42" s="4" t="str">
         <x:v>MARIA FERNANDA</x:v>
       </x:c>
-      <x:c r="I40" s="4" t="str">
+      <x:c r="I42" s="4" t="str">
         <x:v>mviterip@ups.edu.ec</x:v>
       </x:c>
     </x:row>
@@ -14868,19 +15119,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
-        <x:v>INGENIERIA AMBIENTAL</x:v>
+        <x:v>BIOQUIMICA Y FARMACIA</x:v>
       </x:c>
       <x:c r="F6" s="8" t="str">
-        <x:v>0914078290</x:v>
+        <x:v>1714838123</x:v>
       </x:c>
       <x:c r="G6" s="4" t="str">
-        <x:v>BERRONES RIVERA</x:v>
+        <x:v>BALLESTEROS LARA</x:v>
       </x:c>
       <x:c r="H6" s="4" t="str">
-        <x:v>NESTOR MARCELO</x:v>
+        <x:v>JOSE LUIS</x:v>
       </x:c>
       <x:c r="I6" s="4" t="str">
-        <x:v>nberrones@ups.edu.ec</x:v>
+        <x:v>jballesterosl@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="92" customHeight="1">
@@ -14898,19 +15149,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>INGENIERIA AMBIENTAL</x:v>
       </x:c>
       <x:c r="F7" s="8" t="str">
-        <x:v>0917215956</x:v>
+        <x:v>0914078290</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
-        <x:v>BUSTAMANTE RUIZ</x:v>
+        <x:v>BERRONES RIVERA</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>ORLANDO FERNANDO</x:v>
+        <x:v>NESTOR MARCELO</x:v>
       </x:c>
       <x:c r="I7" s="4" t="str">
-        <x:v>obustamante@ups.edu.ec</x:v>
+        <x:v>nberrones@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="92" customHeight="1">
@@ -14928,19 +15179,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
-        <x:v>BIOQUIMICA Y FARMACIA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str">
-        <x:v>0931057756</x:v>
+        <x:v>0917215956</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
-        <x:v>CEDEÑO VINCES</x:v>
+        <x:v>BUSTAMANTE RUIZ</x:v>
       </x:c>
       <x:c r="H8" s="4" t="str">
-        <x:v>KEVIN GABRIEL</x:v>
+        <x:v>ORLANDO FERNANDO</x:v>
       </x:c>
       <x:c r="I8" s="4" t="str">
-        <x:v>kcedeno@ups.edu.ec</x:v>
+        <x:v>obustamante@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="92" customHeight="1">
@@ -14958,19 +15209,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>BIOTECNOLOGIA</x:v>
+        <x:v>BIOQUIMICA Y FARMACIA</x:v>
       </x:c>
       <x:c r="F9" s="8" t="str">
-        <x:v>1724832900</x:v>
+        <x:v>0931057756</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
-        <x:v>CRUZ MORENO</x:v>
+        <x:v>CEDEÑO VINCES</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>RAI SEBASTIAN</x:v>
+        <x:v>KEVIN GABRIEL</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
-        <x:v>rcruz@ups.edu.ec</x:v>
+        <x:v>kcedeno@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="92" customHeight="1">
@@ -14988,19 +15239,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>BIOTECNOLOGIA</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str">
-        <x:v>1003233689</x:v>
+        <x:v>0930971593</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
-        <x:v>DE LA CRUZ MORA</x:v>
+        <x:v>CHAVEZ GONZALEZ</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>MARIA ALEJANDRA</x:v>
+        <x:v>KAROL LEONOR</x:v>
       </x:c>
       <x:c r="I10" s="4" t="str">
-        <x:v>mde@ups.edu.ec</x:v>
+        <x:v>kchavezg@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="92" customHeight="1">
@@ -15018,19 +15269,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>ENFERMERIA</x:v>
+        <x:v>BIOTECNOLOGIA</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>1207725597</x:v>
+        <x:v>1724832900</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>DIAZ ARAUJO</x:v>
+        <x:v>CRUZ MORENO</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>PAULA JACQUELINE</x:v>
+        <x:v>RAI SEBASTIAN</x:v>
       </x:c>
       <x:c r="I11" s="4" t="str">
-        <x:v>pdiaz@ups.edu.ec</x:v>
+        <x:v>rcruz@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="92" customHeight="1">
@@ -15048,19 +15299,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>BIOTECNOLOGIA</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>0918581596</x:v>
+        <x:v>1003233689</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>FUENTES MIRANDA</x:v>
+        <x:v>DE LA CRUZ MORA</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>RAFAEL FRANCISCO</x:v>
+        <x:v>MARIA ALEJANDRA</x:v>
       </x:c>
       <x:c r="I12" s="4" t="str">
-        <x:v>rfuentes@ups.edu.ec</x:v>
+        <x:v>mde@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="92" customHeight="1">
@@ -15078,19 +15329,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>ENFERMERIA</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>0916525959</x:v>
+        <x:v>1207725597</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>GOMEZ PITA</x:v>
+        <x:v>DIAZ ARAUJO</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>ARACELY JOSEFINA</x:v>
+        <x:v>PAULA JACQUELINE</x:v>
       </x:c>
       <x:c r="I13" s="4" t="str">
-        <x:v>agomez@ups.edu.ec</x:v>
+        <x:v>pdiaz@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="92" customHeight="1">
@@ -15108,19 +15359,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>BIOTECNOLOGIA</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>1718061144</x:v>
+        <x:v>0918581596</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>GRIJALVA BORJA</x:v>
+        <x:v>FUENTES MIRANDA</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>NICOLAS ALEJANDRO</x:v>
+        <x:v>RAFAEL FRANCISCO</x:v>
       </x:c>
       <x:c r="I14" s="4" t="str">
-        <x:v>ngrijalva@ups.edu.ec</x:v>
+        <x:v>rfuentes@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="92" customHeight="1">
@@ -15138,19 +15389,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>PSICOLOGIA</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>1205707894</x:v>
+        <x:v>0916525959</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>HIDALGO SOTOMAYOR</x:v>
+        <x:v>GOMEZ PITA</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>DARWIN ANDRES</x:v>
+        <x:v>ARACELY JOSEFINA</x:v>
       </x:c>
       <x:c r="I15" s="4" t="str">
-        <x:v>dhidalgo@ups.edu.ec</x:v>
+        <x:v>agomez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="92" customHeight="1">
@@ -15168,19 +15419,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>BIOTECNOLOGIA</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>0930941646</x:v>
+        <x:v>1718061144</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>IPIALES VASCONEZ</x:v>
+        <x:v>GRIJALVA BORJA</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>MARLYS LISBETH</x:v>
+        <x:v>NICOLAS ALEJANDRO</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>mipiales@ups.edu.ec</x:v>
+        <x:v>ngrijalva@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="92" customHeight="1">
@@ -15198,19 +15449,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>BIOQUIMICA Y FARMACIA</x:v>
+        <x:v>PSICOLOGIA</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>1207482108</x:v>
+        <x:v>1205707894</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>JAIME CARVAJAL</x:v>
+        <x:v>HIDALGO SOTOMAYOR</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>JAIRO JOEL</x:v>
+        <x:v>DARWIN ANDRES</x:v>
       </x:c>
       <x:c r="I17" s="4" t="str">
-        <x:v>jjaimec@ups.edu.ec</x:v>
+        <x:v>dhidalgo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="92" customHeight="1">
@@ -15231,16 +15482,16 @@
         <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
-        <x:v>0706623923</x:v>
+        <x:v>0930941646</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>LOAYZA TORO</x:v>
+        <x:v>IPIALES VASCONEZ</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>MARIA ISABEL</x:v>
+        <x:v>MARLYS LISBETH</x:v>
       </x:c>
       <x:c r="I18" s="4" t="str">
-        <x:v>mloayzat@ups.edu.ec</x:v>
+        <x:v>mipiales@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="92" customHeight="1">
@@ -15258,19 +15509,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>BIOTECNOLOGIA</x:v>
+        <x:v>BIOQUIMICA Y FARMACIA</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>0960450922</x:v>
+        <x:v>1207482108</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>LOPEZ ULLOA</x:v>
+        <x:v>JAIME CARVAJAL</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>BRENDA PATRICIA</x:v>
+        <x:v>JAIRO JOEL</x:v>
       </x:c>
       <x:c r="I19" s="4" t="str">
-        <x:v>blopez@ups.edu.ec</x:v>
+        <x:v>jjaimec@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="92" customHeight="1">
@@ -15288,19 +15539,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>0503202475</x:v>
+        <x:v>0706623923</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>MENA GALLEGOS</x:v>
+        <x:v>LOAYZA TORO</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>CYNTHIA LORENA</x:v>
+        <x:v>MARIA ISABEL</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>cmenag@ups.edu.ec</x:v>
+        <x:v>mloayzat@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="92" customHeight="1">
@@ -15321,16 +15572,16 @@
         <x:v>BIOTECNOLOGIA</x:v>
       </x:c>
       <x:c r="F21" s="8" t="str">
-        <x:v>0927155226</x:v>
+        <x:v>0960450922</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>NARANJO MORAN</x:v>
+        <x:v>LOPEZ ULLOA</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>JAIME ALBERTO</x:v>
+        <x:v>BRENDA PATRICIA</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>jnaranjo@ups.edu.ec</x:v>
+        <x:v>blopez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="92" customHeight="1">
@@ -15348,19 +15599,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>INGENIERIA AMBIENTAL</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F22" s="8" t="str">
-        <x:v>0909780850</x:v>
+        <x:v>0503202475</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>ORDOÑEZ RAMIREZ</x:v>
+        <x:v>MENA GALLEGOS</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>VIRGILIO ALONSO</x:v>
+        <x:v>CYNTHIA LORENA</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>vordonezr@ups.edu.ec</x:v>
+        <x:v>cmenag@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="92" customHeight="1">
@@ -15378,19 +15629,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>BIOTECNOLOGIA</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>1311942971</x:v>
+        <x:v>0927155226</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>ORLANDO SANTANA</x:v>
+        <x:v>NARANJO MORAN</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>MISHEL DENISSE</x:v>
+        <x:v>JAIME ALBERTO</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>morlando@ups.edu.ec</x:v>
+        <x:v>jnaranjo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="92" customHeight="1">
@@ -15408,19 +15659,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>BIOTECNOLOGIA</x:v>
+        <x:v>INGENIERIA AMBIENTAL</x:v>
       </x:c>
       <x:c r="F24" s="8" t="str">
-        <x:v>0930726112</x:v>
+        <x:v>0909780850</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>PACHECO FLORES DE VALGAZ</x:v>
+        <x:v>ORDOÑEZ RAMIREZ</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>ANGELA VANESSA</x:v>
+        <x:v>VIRGILIO ALONSO</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>apachecof@ups.edu.ec</x:v>
+        <x:v>vordonezr@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="92" customHeight="1">
@@ -15438,19 +15689,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F25" s="8" t="str">
-        <x:v>0940441082</x:v>
+        <x:v>1311942971</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>PALMA DIAZ</x:v>
+        <x:v>ORLANDO SANTANA</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>BRYAN CARLOS</x:v>
+        <x:v>MISHEL DENISSE</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>bpalma@ups.edu.ec</x:v>
+        <x:v>morlando@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="92" customHeight="1">
@@ -15468,19 +15719,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>BIOTECNOLOGIA</x:v>
       </x:c>
       <x:c r="F26" s="8" t="str">
-        <x:v>0920160371</x:v>
+        <x:v>0930726112</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>PRECIADO MAILA</x:v>
+        <x:v>PACHECO FLORES DE VALGAZ</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>OLGA LISET</x:v>
+        <x:v>ANGELA VANESSA</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>opreciado@ups.edu.ec</x:v>
+        <x:v>apachecof@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="92" customHeight="1">
@@ -15498,19 +15749,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F27" s="8" t="str">
-        <x:v>0917494890</x:v>
+        <x:v>0940441082</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>RIVAS ORDOÑEZ</x:v>
+        <x:v>PALMA DIAZ</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>VIVIANA MARIA</x:v>
+        <x:v>BRYAN CARLOS</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>vrivaso@ups.edu.ec</x:v>
+        <x:v>bpalma@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="92" customHeight="1">
@@ -15528,19 +15779,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F28" s="8" t="str">
-        <x:v>1315506590</x:v>
+        <x:v>0920160371</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>RUIZ FARFAN</x:v>
+        <x:v>PRECIADO MAILA</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>MARIA ALEJANDRA</x:v>
+        <x:v>OLGA LISET</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>mruizf1@ups.edu.ec</x:v>
+        <x:v>opreciado@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="92" customHeight="1">
@@ -15558,19 +15809,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>0912520475</x:v>
+        <x:v>0917494890</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>SAMANIEGO BRIONES</x:v>
+        <x:v>RIVAS ORDOÑEZ</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>PAOLA MERCEDES</x:v>
+        <x:v>VIVIANA MARIA</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>psamaniego@ups.edu.ec</x:v>
+        <x:v>vrivaso@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="92" customHeight="1">
@@ -15591,16 +15842,16 @@
         <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>0966185225</x:v>
+        <x:v>1315506590</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>SANCHEZ ALMARAZ</x:v>
+        <x:v>RUIZ FARFAN</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>FRANCISCO</x:v>
+        <x:v>MARIA ALEJANDRA</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>fsanchez@ups.edu.ec</x:v>
+        <x:v>mruizf1@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="92" customHeight="1">
@@ -15618,19 +15869,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>FISIOTERAPIA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F31" s="8" t="str">
-        <x:v>1719094540</x:v>
+        <x:v>0912520475</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>SANCHEZ ZARSOSA</x:v>
+        <x:v>SAMANIEGO BRIONES</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>ANDREA LIZETH</x:v>
+        <x:v>PAOLA MERCEDES</x:v>
       </x:c>
       <x:c r="I31" s="4" t="str">
-        <x:v>asanchezz@ups.edu.ec</x:v>
+        <x:v>psamaniego@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="92" customHeight="1">
@@ -15648,19 +15899,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
-        <x:v>FISIOTERAPIA</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F32" s="8" t="str">
-        <x:v>1757712839</x:v>
+        <x:v>0966185225</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
-        <x:v>SANTAELLA PALMA</x:v>
+        <x:v>SANCHEZ ALMARAZ</x:v>
       </x:c>
       <x:c r="H32" s="4" t="str">
-        <x:v>LUIS EDUARDO</x:v>
+        <x:v>FRANCISCO</x:v>
       </x:c>
       <x:c r="I32" s="4" t="str">
-        <x:v>lsantaella@ups.edu.ec</x:v>
+        <x:v>fsanchez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="92" customHeight="1">
@@ -15678,19 +15929,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>FISIOTERAPIA</x:v>
       </x:c>
       <x:c r="F33" s="8" t="str">
-        <x:v>0924194889</x:v>
+        <x:v>1719094540</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
-        <x:v>SESME CAJO</x:v>
+        <x:v>SANCHEZ ZARSOSA</x:v>
       </x:c>
       <x:c r="H33" s="4" t="str">
-        <x:v>CINTHYA BEATRIZ</x:v>
+        <x:v>ANDREA LIZETH</x:v>
       </x:c>
       <x:c r="I33" s="4" t="str">
-        <x:v>csesme@ups.edu.ec</x:v>
+        <x:v>asanchezz@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="92" customHeight="1">
@@ -15708,19 +15959,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E34" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>FISIOTERAPIA</x:v>
       </x:c>
       <x:c r="F34" s="8" t="str">
-        <x:v>0950594754</x:v>
+        <x:v>1757712839</x:v>
       </x:c>
       <x:c r="G34" s="4" t="str">
-        <x:v>TRIVIÑO BURBANO</x:v>
+        <x:v>SANTAELLA PALMA</x:v>
       </x:c>
       <x:c r="H34" s="4" t="str">
-        <x:v>MARIA VANESSA</x:v>
+        <x:v>LUIS EDUARDO</x:v>
       </x:c>
       <x:c r="I34" s="4" t="str">
-        <x:v>mtrivino@ups.edu.ec</x:v>
+        <x:v>lsantaella@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="92" customHeight="1">
@@ -15738,19 +15989,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E35" s="4" t="str">
-        <x:v>FISIOTERAPIA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F35" s="8" t="str">
-        <x:v>0914858287</x:v>
+        <x:v>0924194889</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
-        <x:v>UNDA VERNELLE</x:v>
+        <x:v>SESME CAJO</x:v>
       </x:c>
       <x:c r="H35" s="4" t="str">
-        <x:v>ALICIA MARGOTH</x:v>
+        <x:v>CINTHYA BEATRIZ</x:v>
       </x:c>
       <x:c r="I35" s="4" t="str">
-        <x:v>aunda@ups.edu.ec</x:v>
+        <x:v>csesme@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="92" customHeight="1">
@@ -15768,19 +16019,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E36" s="4" t="str">
-        <x:v>BIOQUIMICA Y FARMACIA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F36" s="8" t="str">
-        <x:v>0202465365</x:v>
+        <x:v>0950594754</x:v>
       </x:c>
       <x:c r="G36" s="4" t="str">
-        <x:v>URREA CAMACHO</x:v>
+        <x:v>TRIVIÑO BURBANO</x:v>
       </x:c>
       <x:c r="H36" s="4" t="str">
-        <x:v>KAREN JULISSA</x:v>
+        <x:v>MARIA VANESSA</x:v>
       </x:c>
       <x:c r="I36" s="4" t="str">
-        <x:v>kurrea@ups.edu.ec</x:v>
+        <x:v>mtrivino@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="92" customHeight="1">
@@ -15798,19 +16049,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E37" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>FISIOTERAPIA</x:v>
       </x:c>
       <x:c r="F37" s="8" t="str">
-        <x:v>0922028915</x:v>
+        <x:v>0914858287</x:v>
       </x:c>
       <x:c r="G37" s="4" t="str">
-        <x:v>VILLACRÉS BARREIRO</x:v>
+        <x:v>UNDA VERNELLE</x:v>
       </x:c>
       <x:c r="H37" s="4" t="str">
-        <x:v>ARIADNA SOFÍA</x:v>
+        <x:v>ALICIA MARGOTH</x:v>
       </x:c>
       <x:c r="I37" s="4" t="str">
-        <x:v>avillacres@ups.edu.ec</x:v>
+        <x:v>aunda@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="92" customHeight="1">
@@ -15828,18 +16079,78 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E38" s="4" t="str">
+        <x:v>BIOQUIMICA Y FARMACIA</x:v>
+      </x:c>
+      <x:c r="F38" s="8" t="str">
+        <x:v>0202465365</x:v>
+      </x:c>
+      <x:c r="G38" s="4" t="str">
+        <x:v>URREA CAMACHO</x:v>
+      </x:c>
+      <x:c r="H38" s="4" t="str">
+        <x:v>KAREN JULISSA</x:v>
+      </x:c>
+      <x:c r="I38" s="4" t="str">
+        <x:v>kurrea@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="92" customHeight="1">
+      <x:c r="A39" s="9" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B39" s="9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C39" s="4" t="str">
+        <x:v>ELENA DEL ROCIO COYAGO CRUZ (DIRECTOR NACIONAL)
+LOPEZ ULLOA BRENDA PATRICIA (RESPONSABLE SEDE)</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="str">
+        <x:v>Aula D204</x:v>
+      </x:c>
+      <x:c r="E39" s="4" t="str">
         <x:v>ODONTOLOGIA</x:v>
       </x:c>
-      <x:c r="F38" s="8" t="str">
+      <x:c r="F39" s="8" t="str">
+        <x:v>0922028915</x:v>
+      </x:c>
+      <x:c r="G39" s="4" t="str">
+        <x:v>VILLACRÉS BARREIRO</x:v>
+      </x:c>
+      <x:c r="H39" s="4" t="str">
+        <x:v>ARIADNA SOFÍA</x:v>
+      </x:c>
+      <x:c r="I39" s="4" t="str">
+        <x:v>avillacres@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="92" customHeight="1">
+      <x:c r="A40" s="9" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B40" s="9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C40" s="4" t="str">
+        <x:v>ELENA DEL ROCIO COYAGO CRUZ (DIRECTOR NACIONAL)
+LOPEZ ULLOA BRENDA PATRICIA (RESPONSABLE SEDE)</x:v>
+      </x:c>
+      <x:c r="D40" s="4" t="str">
+        <x:v>Aula D204</x:v>
+      </x:c>
+      <x:c r="E40" s="4" t="str">
+        <x:v>ODONTOLOGIA</x:v>
+      </x:c>
+      <x:c r="F40" s="8" t="str">
         <x:v>0954979449</x:v>
       </x:c>
-      <x:c r="G38" s="4" t="str">
+      <x:c r="G40" s="4" t="str">
         <x:v>YAROSSI MATA</x:v>
       </x:c>
-      <x:c r="H38" s="4" t="str">
+      <x:c r="H40" s="4" t="str">
         <x:v>KATHERINA</x:v>
       </x:c>
-      <x:c r="I38" s="4" t="str">
+      <x:c r="I40" s="4" t="str">
         <x:v>kyarossi@ups.edu.ec</x:v>
       </x:c>
     </x:row>
@@ -16445,11 +16756,11 @@
       </x:c>
       <x:c r="C27" s="4" t="str">
         <x:v>T4: por área de conocimiento
-T5 y T6: No Convocado</x:v>
+T5 y T6: DIRECTOR/A DE CARRERA (convocado por responsabilidad de carrera)</x:v>
       </x:c>
       <x:c r="D27" s="4" t="str">
         <x:v>T4: Grupo 5 - Aula D204
-T5 y T6: No Convocado</x:v>
+T5 y T6: Grupo 5 - Aula D204</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
         <x:v>jballesterosl@ups.edu.ec</x:v>
@@ -17127,11 +17438,11 @@
       </x:c>
       <x:c r="C58" s="4" t="str">
         <x:v>T4: por área de conocimiento
-T5 y T6: No Convocado</x:v>
+T5 y T6: DIRECTOR/A DE CARRERA (convocado por responsabilidad de carrera)</x:v>
       </x:c>
       <x:c r="D58" s="4" t="str">
         <x:v>T4: Grupo 6 - Aula D205
-T5 y T6: No Convocado</x:v>
+T5 y T6: Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="E58" s="4" t="str">
         <x:v>acedeno@ups.edu.ec</x:v>
@@ -17259,11 +17570,11 @@
       </x:c>
       <x:c r="C64" s="4" t="str">
         <x:v>T4: por área de conocimiento
-T5 y T6: No Convocado</x:v>
+T5 y T6: DIRECTOR/A DE CARRERA (convocado por responsabilidad de carrera)</x:v>
       </x:c>
       <x:c r="D64" s="4" t="str">
         <x:v>T4: Grupo 5 - Aula D204
-T5 y T6: No Convocado</x:v>
+T5 y T6: Grupo 5 - Aula D204</x:v>
       </x:c>
       <x:c r="E64" s="4" t="str">
         <x:v>kchavezg@ups.edu.ec</x:v>
@@ -17941,11 +18252,11 @@
       </x:c>
       <x:c r="C95" s="4" t="str">
         <x:v>T4: por área de conocimiento
-T5 y T6: No Convocado</x:v>
+T5 y T6: DIRECTOR/A DE CARRERA (convocado por responsabilidad de carrera)</x:v>
       </x:c>
       <x:c r="D95" s="4" t="str">
         <x:v>T4: Grupo 2 - Aula D201
-T5 y T6: No Convocado</x:v>
+T5 y T6: Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="E95" s="4" t="str">
         <x:v>sescobar@ups.edu.ec</x:v>
@@ -18073,11 +18384,11 @@
       </x:c>
       <x:c r="C101" s="4" t="str">
         <x:v>T4: por área de conocimiento
-T5 y T6: No Convocado</x:v>
+T5 y T6: DIRECTOR/A DE CARRERA (convocado por responsabilidad de carrera)</x:v>
       </x:c>
       <x:c r="D101" s="4" t="str">
         <x:v>T4: Grupo 3 - Aula D202
-T5 y T6: No Convocado</x:v>
+T5 y T6: Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="E101" s="4" t="str">
         <x:v>jfarino@ups.edu.ec</x:v>
@@ -18139,11 +18450,11 @@
       </x:c>
       <x:c r="C104" s="4" t="str">
         <x:v>T4: por área de conocimiento
-T5 y T6: No Convocado</x:v>
+T5 y T6: DIRECTOR/A DE CARRERA (convocado por responsabilidad de carrera)</x:v>
       </x:c>
       <x:c r="D104" s="4" t="str">
         <x:v>T4: Grupo 4 - Aula D203
-T5 y T6: No Convocado</x:v>
+T5 y T6: Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="E104" s="4" t="str">
         <x:v>pfierro@ups.edu.ec</x:v>
@@ -19371,11 +19682,11 @@
       </x:c>
       <x:c r="C160" s="4" t="str">
         <x:v>T4: por área de conocimiento
-T5 y T6: No Convocado</x:v>
+T5 y T6: DIRECTOR/A DE CARRERA (convocado por responsabilidad de carrera)</x:v>
       </x:c>
       <x:c r="D160" s="4" t="str">
         <x:v>T4: Grupo 3 - Aula D202
-T5 y T6: No Convocado</x:v>
+T5 y T6: Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="E160" s="4" t="str">
         <x:v>alopez@ups.edu.ec</x:v>
@@ -20361,11 +20672,11 @@
       </x:c>
       <x:c r="C205" s="4" t="str">
         <x:v>T4: por área de conocimiento
-T5 y T6: No Convocado</x:v>
+T5 y T6: DIRECTOR/A DE CARRERA (convocado por responsabilidad de carrera)</x:v>
       </x:c>
       <x:c r="D205" s="4" t="str">
         <x:v>T4: Grupo 3 - Aula D202
-T5 y T6: No Convocado</x:v>
+T5 y T6: Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="E205" s="4" t="str">
         <x:v>vpenaranda@ups.edu.ec</x:v>
@@ -20427,11 +20738,11 @@
       </x:c>
       <x:c r="C208" s="4" t="str">
         <x:v>T4: por área de conocimiento
-T5 y T6: No Convocado</x:v>
+T5 y T6: DIRECTOR/A DE CARRERA (convocado por responsabilidad de carrera)</x:v>
       </x:c>
       <x:c r="D208" s="4" t="str">
         <x:v>T4: Grupo 4 - Aula D203
-T5 y T6: No Convocado</x:v>
+T5 y T6: Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="E208" s="4" t="str">
         <x:v>dplua@ups.edu.ec</x:v>
@@ -21395,11 +21706,11 @@
       </x:c>
       <x:c r="C252" s="4" t="str">
         <x:v>T4: por área de conocimiento
-T5 y T6: No Convocado</x:v>
+T5 y T6: DIRECTOR/A DE CARRERA (convocado por responsabilidad de carrera)</x:v>
       </x:c>
       <x:c r="D252" s="4" t="str">
         <x:v>T4: Grupo 3 - Aula D202
-T5 y T6: No Convocado</x:v>
+T5 y T6: Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="E252" s="4" t="str">
         <x:v>hsantillan@ups.edu.ec</x:v>
@@ -22053,11 +22364,11 @@
       </x:c>
       <x:c r="C282" s="4" t="str">
         <x:v>T4: por área de conocimiento
-T5 y T6: No Convocado</x:v>
+T5 y T6: DIRECTOR/A DE CARRERA (convocado por responsabilidad de carrera)</x:v>
       </x:c>
       <x:c r="D282" s="4" t="str">
         <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: No Convocado</x:v>
+T5 y T6: Grupo 1 - Aula D200</x:v>
       </x:c>
       <x:c r="E282" s="4" t="str">
         <x:v>kvallejo@ups.edu.ec</x:v>
@@ -22553,16 +22864,16 @@
         <x:v>EDUCACION INICIAL</x:v>
       </x:c>
       <x:c r="F4" s="8" t="str">
-        <x:v>0959611450</x:v>
+        <x:v>0925779365</x:v>
       </x:c>
       <x:c r="G4" s="4" t="str">
-        <x:v>GONZALEZ RIVERA</x:v>
+        <x:v>CEDEÑO TELLO</x:v>
       </x:c>
       <x:c r="H4" s="4" t="str">
-        <x:v>PEDRO LUIS</x:v>
+        <x:v>ALICIA MARIA</x:v>
       </x:c>
       <x:c r="I4" s="4" t="str">
-        <x:v>pgonzalezr@ups.edu.ec</x:v>
+        <x:v>acedeno@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="92" customHeight="1">
@@ -22583,16 +22894,16 @@
         <x:v>EDUCACION INICIAL</x:v>
       </x:c>
       <x:c r="F5" s="8" t="str">
-        <x:v>0912155652</x:v>
+        <x:v>0959611450</x:v>
       </x:c>
       <x:c r="G5" s="4" t="str">
-        <x:v>POMBO BERMEO</x:v>
+        <x:v>GONZALEZ RIVERA</x:v>
       </x:c>
       <x:c r="H5" s="4" t="str">
-        <x:v>ANGELICA SUSANA</x:v>
+        <x:v>PEDRO LUIS</x:v>
       </x:c>
       <x:c r="I5" s="4" t="str">
-        <x:v>apombo@ups.edu.ec</x:v>
+        <x:v>pgonzalezr@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="92" customHeight="1">
@@ -22613,15 +22924,45 @@
         <x:v>EDUCACION INICIAL</x:v>
       </x:c>
       <x:c r="F6" s="8" t="str">
+        <x:v>0912155652</x:v>
+      </x:c>
+      <x:c r="G6" s="4" t="str">
+        <x:v>POMBO BERMEO</x:v>
+      </x:c>
+      <x:c r="H6" s="4" t="str">
+        <x:v>ANGELICA SUSANA</x:v>
+      </x:c>
+      <x:c r="I6" s="4" t="str">
+        <x:v>apombo@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="92" customHeight="1">
+      <x:c r="A7" s="9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="str">
+        <x:v>ALICIA MARIA CEDEÑO TELLO (DIRECTOR NACIONAL)
+ALENCASTRO CARRIEL MONICA SANDRA (RESPONSABLE SEDE)</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="str">
+        <x:v>Aula D205</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="str">
+        <x:v>EDUCACION INICIAL</x:v>
+      </x:c>
+      <x:c r="F7" s="8" t="str">
         <x:v>0907787915</x:v>
       </x:c>
-      <x:c r="G6" s="4" t="str">
+      <x:c r="G7" s="4" t="str">
         <x:v>RECALDE RAYMONDY</x:v>
       </x:c>
-      <x:c r="H6" s="4" t="str">
+      <x:c r="H7" s="4" t="str">
         <x:v>RITA ELIZABETH</x:v>
       </x:c>
-      <x:c r="I6" s="4" t="str">
+      <x:c r="I7" s="4" t="str">
         <x:v>rrecalde@ups.edu.ec</x:v>
       </x:c>
     </x:row>
@@ -31319,7 +31660,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="E12" s="24" t="str">
-        <x:v>Desde el miércoles por la tarde: solo quienes tengan SI en CONVOCADOS - GRUPO FORMADO AREA CONOCIMIENTO.</x:v>
+        <x:v>Desde el miércoles por la tarde: convocados con SI, más los directores de carrera identificados en los archivos.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="45" customHeight="1">
@@ -31327,7 +31668,7 @@
       <x:c r="B13"/>
       <x:c r="C13" s="20"/>
       <x:c r="E13" s="24" t="str">
-        <x:v>Talleres 5 y 6: 168 convocados. Quienes tengan NO o la convocatoria vacía figuran como No Convocado.</x:v>
+        <x:v>Talleres 5 y 6: 179 convocados (168 originales y 11 directores añadidos). Los demás figuran como No Convocado.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="45" customHeight="1">
@@ -31423,6 +31764,9 @@
         <x:f>COUNTIFS('Convocatoria'!$G$2:$G$299,A20)</x:f>
         <x:v>79</x:v>
       </x:c>
+      <x:c r="E20" s="24" t="str">
+        <x:v>Directores: se cruzaron CARGO y DIRECTOR_CARRERA. La hoja Directores carrera conserva la convocatoria original.</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="65" customHeight="1">
       <x:c r="A21" s="4" t="str">
@@ -31434,6 +31778,9 @@
       <x:c r="C21" s="18" t="n">
         <x:f>COUNTIFS('Convocatoria'!$G$2:$G$299,A21)</x:f>
         <x:v>11</x:v>
+      </x:c>
+      <x:c r="E21" s="24" t="str">
+        <x:v>Alicia María Cedeño Tello y Karol Leonor Chávez González: directoras confirmadas por el organizador, convocadas en Educación y Ciencias de la Vida / Salud.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="65" customHeight="1">
@@ -32562,7 +32909,7 @@
       </x:c>
       <x:c r="C3" s="14" t="n">
         <x:f>'T5-6 Resumen'!D3</x:f>
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS, CONTABILIDAD Y AUDITORIA, DIRECCION TECNICA DE PLANEACION EVALUACION Y ACREDITACION, ECONOMIA, MAESTRIA EN GERENCIA TRIBUTARIA, NEGOCIOS DIGITALES</x:v>
@@ -32580,7 +32927,7 @@
       </x:c>
       <x:c r="C4" s="14" t="n">
         <x:f>'T5-6 Resumen'!D4</x:f>
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
         <x:v>COMUNICACION SOCIAL, DERECHO, DISEÑO MULTIMEDIA</x:v>
@@ -32598,10 +32945,10 @@
       </x:c>
       <x:c r="C5" s="14" t="n">
         <x:f>'T5-6 Resumen'!D5</x:f>
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:v>BIOMEDICINA, ELECTRICIDAD, ELECTRONICA Y AUTOMATIZACION, INGENIERIA AUTOMOTRIZ, MECATRONICA, TELECOMUNICACIONES</x:v>
+        <x:v>BIOMEDICINA, ELECTRICIDAD, ELECTRONICA Y AUTOMATIZACION, INGENIERIA AUTOMOTRIZ, INGENIERIA INDUSTRIAL, MECATRONICA, TELECOMUNICACIONES</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
         <x:v>CIENCIA Y TECNOLOGÍA | CIENCIAS EXACTAS</x:v>
@@ -32616,10 +32963,10 @@
       </x:c>
       <x:c r="C6" s="14" t="n">
         <x:f>'T5-6 Resumen'!D6</x:f>
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
-        <x:v>ARQUITECTURA, COMPUTACION, INGENIERIA CIVIL, INGENIERIA ELECTRICA, INGENIERIA INDUSTRIAL, MAESTRIA EN ANALITICA DE DATOS, MAESTRÍA EN SEGURIDAD, SALUD E HIGIENE INDUSTRIAL, SEGURIDAD DE LA INFORMACION-LINEA, TECNOLOGIA ELECTRICIDAD INDUSTRIAL, TECNOLOGIA MECANICA INDUSTRIAL</x:v>
+        <x:v>ARQUITECTURA, COMPUTACION, INGENIERIA AUTOMOTRIZ, INGENIERIA CIVIL, INGENIERIA ELECTRICA, INGENIERIA INDUSTRIAL, MAESTRIA EN ANALITICA DE DATOS, MAESTRÍA EN SEGURIDAD, SALUD E HIGIENE INDUSTRIAL, SEGURIDAD DE LA INFORMACION-LINEA, TECNOLOGIA ELECTRICIDAD INDUSTRIAL, TECNOLOGIA MECANICA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
         <x:v>CIENCIA Y TECNOLOGÍA | CIENCIAS EXACTAS</x:v>
@@ -32634,7 +32981,7 @@
       </x:c>
       <x:c r="C7" s="14" t="n">
         <x:f>'T5-6 Resumen'!D7</x:f>
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
         <x:v>BIOQUIMICA Y FARMACIA, BIOTECNOLOGIA, ENFERMERIA, FISIOTERAPIA, INGENIERIA AMBIENTAL, ODONTOLOGIA, PSICOLOGIA, PSICOLOGIA CLINICA</x:v>
@@ -32652,7 +32999,7 @@
       </x:c>
       <x:c r="C8" s="14" t="n">
         <x:f>'T5-6 Resumen'!D8</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
         <x:v>EDUCACION INICIAL</x:v>
@@ -32686,7 +33033,7 @@
       <x:c r="B10" s="25"/>
       <x:c r="C10" s="26" t="n">
         <x:f>SUM(C3:C9)</x:f>
-        <x:v>168</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D10" s="25"/>
       <x:c r="E10" s="25"/>
@@ -33071,6 +33418,696 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF1F3864"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="47" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="56" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="62" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="27" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="27" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="23" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="31" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="52" customHeight="1">
+      <x:c r="A1" s="11" t="str">
+        <x:v>Directores de carrera convocados a los talleres 5 y 6</x:v>
+      </x:c>
+      <x:c r="B1" s="11"/>
+      <x:c r="C1" s="11"/>
+      <x:c r="D1" s="11"/>
+      <x:c r="E1" s="11"/>
+      <x:c r="F1" s="11"/>
+      <x:c r="G1" s="11"/>
+      <x:c r="H1" s="11"/>
+    </x:row>
+    <x:row r="2" ht="38" customHeight="1">
+      <x:c r="A2" s="7" t="str">
+        <x:v>NOMBRE</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>CARGO REGISTRADO</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>CARRERAS QUE DIRIGE</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>CÉDULA</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>TALLER 5</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>TALLER 6</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="str">
+        <x:v>CONVOCATORIA ORIGINAL</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>IDENTIFICADO EN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="76" customHeight="1">
+      <x:c r="A3" s="4" t="str">
+        <x:v>ARCOS TORRES DESIRE LISBETH</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE DERECHO</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="str">
+        <x:v>DERECHO</x:v>
+      </x:c>
+      <x:c r="D3" s="8" t="str">
+        <x:v>0941164956</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="str">
+        <x:v>Grupo 2 - Aula D201</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="str">
+        <x:v>Grupo 2 - Aula D201</x:v>
+      </x:c>
+      <x:c r="G3" s="4" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="H3" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="76" customHeight="1">
+      <x:c r="A4" s="4" t="str">
+        <x:v>BALLESTEROS LARA JOSE LUIS</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="str">
+        <x:v>DIRECTOR/A DE CARRERA DE BIOQUIMICA Y FARMACIA</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="str">
+        <x:v>BIOQUIMICA Y FARMACIA, INGENIERIA AMBIENTAL</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="str">
+        <x:v>1714838123</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="str">
+        <x:v>Grupo 5 - Aula D204</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="str">
+        <x:v>Grupo 5 - Aula D204</x:v>
+      </x:c>
+      <x:c r="G4" s="4" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H4" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="76" customHeight="1">
+      <x:c r="A5" s="4" t="str">
+        <x:v>BUSTAMANTE RUIZ ORLANDO FERNANDO</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE PSICOLOGIA CLINICA</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="str">
+        <x:v>PSICOLOGIA, PSICOLOGIA CLINICA</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>0917215956</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="str">
+        <x:v>Grupo 5 - Aula D204</x:v>
+      </x:c>
+      <x:c r="F5" s="4" t="str">
+        <x:v>Grupo 5 - Aula D204</x:v>
+      </x:c>
+      <x:c r="G5" s="4" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="H5" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="76" customHeight="1">
+      <x:c r="A6" s="4" t="str">
+        <x:v>CABRERA MORAN FAUSTO FRANCISCO</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE INGENIERIA CIVIL</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="str">
+        <x:v>INGENIERIA CIVIL</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="str">
+        <x:v>0919755272</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="str">
+        <x:v>Grupo 4 - Aula D203</x:v>
+      </x:c>
+      <x:c r="F6" s="4" t="str">
+        <x:v>Grupo 4 - Aula D203</x:v>
+      </x:c>
+      <x:c r="G6" s="4" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="H6" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="76" customHeight="1">
+      <x:c r="A7" s="4" t="str">
+        <x:v>CACERES GALAN CESAR ANTONIO</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="str">
+        <x:v>DIRECTOR/A DE CARRERA TERCER NIVEL TECNICO-TECNOLOGICO</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="str">
+        <x:v>TECNOLOGIA ELECTRICIDAD INDUSTRIAL, TECNOLOGIA MECANICA INDUSTRIAL</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="str">
+        <x:v>0911477776</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="str">
+        <x:v>Grupo 4 - Aula D203</x:v>
+      </x:c>
+      <x:c r="F7" s="4" t="str">
+        <x:v>Grupo 4 - Aula D203</x:v>
+      </x:c>
+      <x:c r="G7" s="4" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="H7" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="76" customHeight="1">
+      <x:c r="A8" s="4" t="str">
+        <x:v>CEDEÑO TELLO ALICIA MARIA</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="str">
+        <x:v>DIRECTOR DE AREA DEL CONOCIMIENTO DE EDUCACION</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="str">
+        <x:v>EDUCACION BASICA, EDUCACION INICIAL</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="str">
+        <x:v>0925779365</x:v>
+      </x:c>
+      <x:c r="E8" s="4" t="str">
+        <x:v>Grupo 6 - Aula D205</x:v>
+      </x:c>
+      <x:c r="F8" s="4" t="str">
+        <x:v>Grupo 6 - Aula D205</x:v>
+      </x:c>
+      <x:c r="G8" s="4" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H8" s="4" t="str">
+        <x:v>DIRECTOR_CARRERA y confirmación del organizador</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="76" customHeight="1">
+      <x:c r="A9" s="4" t="str">
+        <x:v>CHANG PAPPE DENNIS STEVE</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE DISEÑO MULTIMEDIA</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="str">
+        <x:v>DISEÑO MULTIMEDIA</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="str">
+        <x:v>0924375009</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="str">
+        <x:v>Grupo 2 - Aula D201</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="str">
+        <x:v>Grupo 2 - Aula D201</x:v>
+      </x:c>
+      <x:c r="G9" s="4" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="76" customHeight="1">
+      <x:c r="A10" s="4" t="str">
+        <x:v>CHAVEZ GONZALEZ KAROL LEONOR</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="str">
+        <x:v>DOCENTE</x:v>
+      </x:c>
+      <x:c r="C10" s="4" t="str">
+        <x:v>ODONTOLOGIA</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="str">
+        <x:v>0930971593</x:v>
+      </x:c>
+      <x:c r="E10" s="4" t="str">
+        <x:v>Grupo 5 - Aula D204</x:v>
+      </x:c>
+      <x:c r="F10" s="4" t="str">
+        <x:v>Grupo 5 - Aula D204</x:v>
+      </x:c>
+      <x:c r="G10" s="4" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H10" s="4" t="str">
+        <x:v>DIRECTOR_CARRERA y confirmación del organizador</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="76" customHeight="1">
+      <x:c r="A11" s="4" t="str">
+        <x:v>DE LA CRUZ MORA MARIA ALEJANDRA</x:v>
+      </x:c>
+      <x:c r="B11" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE BIOTECNOLOGIA</x:v>
+      </x:c>
+      <x:c r="C11" s="4" t="str">
+        <x:v>BIOTECNOLOGIA</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str">
+        <x:v>1003233689</x:v>
+      </x:c>
+      <x:c r="E11" s="4" t="str">
+        <x:v>Grupo 5 - Aula D204</x:v>
+      </x:c>
+      <x:c r="F11" s="4" t="str">
+        <x:v>Grupo 5 - Aula D204</x:v>
+      </x:c>
+      <x:c r="G11" s="4" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="H11" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="76" customHeight="1">
+      <x:c r="A12" s="4" t="str">
+        <x:v>DELGADO FIGUEROA STELLA PAOLA</x:v>
+      </x:c>
+      <x:c r="B12" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE ADMINISTRACION DE EMPRESAS</x:v>
+      </x:c>
+      <x:c r="C12" s="4" t="str">
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+      </x:c>
+      <x:c r="D12" s="8" t="str">
+        <x:v>0916656408</x:v>
+      </x:c>
+      <x:c r="E12" s="4" t="str">
+        <x:v>Grupo 1 - Aula D200</x:v>
+      </x:c>
+      <x:c r="F12" s="4" t="str">
+        <x:v>Grupo 1 - Aula D200</x:v>
+      </x:c>
+      <x:c r="G12" s="4" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="H12" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="76" customHeight="1">
+      <x:c r="A13" s="4" t="str">
+        <x:v>DIAZ ARAUJO PAULA JACQUELINE</x:v>
+      </x:c>
+      <x:c r="B13" s="4" t="str">
+        <x:v>DIRECTOR/A DE CARRERA</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="str">
+        <x:v>ENFERMERIA</x:v>
+      </x:c>
+      <x:c r="D13" s="8" t="str">
+        <x:v>1207725597</x:v>
+      </x:c>
+      <x:c r="E13" s="4" t="str">
+        <x:v>Grupo 5 - Aula D204</x:v>
+      </x:c>
+      <x:c r="F13" s="4" t="str">
+        <x:v>Grupo 5 - Aula D204</x:v>
+      </x:c>
+      <x:c r="G13" s="4" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="H13" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="76" customHeight="1">
+      <x:c r="A14" s="4" t="str">
+        <x:v>ESCOBAR TERAN SUSAN CATHERINE</x:v>
+      </x:c>
+      <x:c r="B14" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE COMUNICACION</x:v>
+      </x:c>
+      <x:c r="C14" s="4" t="str">
+        <x:v>COMUNICACION SOCIAL</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="str">
+        <x:v>1202606404</x:v>
+      </x:c>
+      <x:c r="E14" s="4" t="str">
+        <x:v>Grupo 2 - Aula D201</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="str">
+        <x:v>Grupo 2 - Aula D201</x:v>
+      </x:c>
+      <x:c r="G14" s="4" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H14" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="76" customHeight="1">
+      <x:c r="A15" s="4" t="str">
+        <x:v>FARIÑO CEDEÑO JORGE BLADIMIR</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE MECATRONICA</x:v>
+      </x:c>
+      <x:c r="C15" s="4" t="str">
+        <x:v>MECATRONICA</x:v>
+      </x:c>
+      <x:c r="D15" s="8" t="str">
+        <x:v>0914335484</x:v>
+      </x:c>
+      <x:c r="E15" s="4" t="str">
+        <x:v>Grupo 3 - Aula D202</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="str">
+        <x:v>Grupo 3 - Aula D202</x:v>
+      </x:c>
+      <x:c r="G15" s="4" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H15" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="76" customHeight="1">
+      <x:c r="A16" s="4" t="str">
+        <x:v>FIERRO JIMENEZ PABLO RENATO</x:v>
+      </x:c>
+      <x:c r="B16" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE INGENIERIA AUTOMOTRIZ</x:v>
+      </x:c>
+      <x:c r="C16" s="4" t="str">
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="str">
+        <x:v>1103588578</x:v>
+      </x:c>
+      <x:c r="E16" s="4" t="str">
+        <x:v>Grupo 4 - Aula D203</x:v>
+      </x:c>
+      <x:c r="F16" s="4" t="str">
+        <x:v>Grupo 4 - Aula D203</x:v>
+      </x:c>
+      <x:c r="G16" s="4" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H16" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="76" customHeight="1">
+      <x:c r="A17" s="4" t="str">
+        <x:v>LOPEZ VARGAS ARMANDO FABRIZZIO</x:v>
+      </x:c>
+      <x:c r="B17" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE INGENIERIA INDUSTRIAL</x:v>
+      </x:c>
+      <x:c r="C17" s="4" t="str">
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
+      </x:c>
+      <x:c r="D17" s="8" t="str">
+        <x:v>0912034790</x:v>
+      </x:c>
+      <x:c r="E17" s="4" t="str">
+        <x:v>Grupo 3 - Aula D202</x:v>
+      </x:c>
+      <x:c r="F17" s="4" t="str">
+        <x:v>Grupo 3 - Aula D202</x:v>
+      </x:c>
+      <x:c r="G17" s="4" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H17" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="76" customHeight="1">
+      <x:c r="A18" s="4" t="str">
+        <x:v>PEÑARANDA IDROVO VICENTE AVELINO</x:v>
+      </x:c>
+      <x:c r="B18" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE INGENIERIA ELECTRONICA Y AUTOMATIZACION</x:v>
+      </x:c>
+      <x:c r="C18" s="4" t="str">
+        <x:v>ELECTRONICA Y AUTOMATIZACION, ING. EN REDES INTELIGENTES Y CIBERSEGURIDAD, TELECOMUNICACIONES</x:v>
+      </x:c>
+      <x:c r="D18" s="8" t="str">
+        <x:v>0916113426</x:v>
+      </x:c>
+      <x:c r="E18" s="4" t="str">
+        <x:v>Grupo 3 - Aula D202</x:v>
+      </x:c>
+      <x:c r="F18" s="4" t="str">
+        <x:v>Grupo 3 - Aula D202</x:v>
+      </x:c>
+      <x:c r="G18" s="4" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H18" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="76" customHeight="1">
+      <x:c r="A19" s="4" t="str">
+        <x:v>PLUA MORAN DANIEL HUMBERTO</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE COMPUTACION</x:v>
+      </x:c>
+      <x:c r="C19" s="4" t="str">
+        <x:v>COMPUTACION</x:v>
+      </x:c>
+      <x:c r="D19" s="8" t="str">
+        <x:v>0920382785</x:v>
+      </x:c>
+      <x:c r="E19" s="4" t="str">
+        <x:v>Grupo 4 - Aula D203</x:v>
+      </x:c>
+      <x:c r="F19" s="4" t="str">
+        <x:v>Grupo 4 - Aula D203</x:v>
+      </x:c>
+      <x:c r="G19" s="4" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H19" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="76" customHeight="1">
+      <x:c r="A20" s="4" t="str">
+        <x:v>ROMERO SANTISTEVAN DARIO XAVIER</x:v>
+      </x:c>
+      <x:c r="B20" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE BIOMEDICINA</x:v>
+      </x:c>
+      <x:c r="C20" s="4" t="str">
+        <x:v>BIOMEDICINA</x:v>
+      </x:c>
+      <x:c r="D20" s="8" t="str">
+        <x:v>1206442616</x:v>
+      </x:c>
+      <x:c r="E20" s="4" t="str">
+        <x:v>Grupo 3 - Aula D202</x:v>
+      </x:c>
+      <x:c r="F20" s="4" t="str">
+        <x:v>Grupo 3 - Aula D202</x:v>
+      </x:c>
+      <x:c r="G20" s="4" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="H20" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="76" customHeight="1">
+      <x:c r="A21" s="4" t="str">
+        <x:v>SANTILLAN CARRANZA HOLGER JORGE</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE ELECTRICIDAD</x:v>
+      </x:c>
+      <x:c r="C21" s="4" t="str">
+        <x:v>ELECTRICIDAD, INGENIERIA ELECTRICA</x:v>
+      </x:c>
+      <x:c r="D21" s="8" t="str">
+        <x:v>0916303134</x:v>
+      </x:c>
+      <x:c r="E21" s="4" t="str">
+        <x:v>Grupo 3 - Aula D202</x:v>
+      </x:c>
+      <x:c r="F21" s="4" t="str">
+        <x:v>Grupo 3 - Aula D202</x:v>
+      </x:c>
+      <x:c r="G21" s="4" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H21" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="76" customHeight="1">
+      <x:c r="A22" s="4" t="str">
+        <x:v>UNDA VERNELLE ALICIA MARGOTH</x:v>
+      </x:c>
+      <x:c r="B22" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE FISIOTERAPIA</x:v>
+      </x:c>
+      <x:c r="C22" s="4" t="str">
+        <x:v>FISIOTERAPIA</x:v>
+      </x:c>
+      <x:c r="D22" s="8" t="str">
+        <x:v>0914858287</x:v>
+      </x:c>
+      <x:c r="E22" s="4" t="str">
+        <x:v>Grupo 5 - Aula D204</x:v>
+      </x:c>
+      <x:c r="F22" s="4" t="str">
+        <x:v>Grupo 5 - Aula D204</x:v>
+      </x:c>
+      <x:c r="G22" s="4" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="H22" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="76" customHeight="1">
+      <x:c r="A23" s="4" t="str">
+        <x:v>VALLEJO LEON KARINA ROXANA</x:v>
+      </x:c>
+      <x:c r="B23" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE ECONOMIA</x:v>
+      </x:c>
+      <x:c r="C23" s="4" t="str">
+        <x:v>ECONOMIA</x:v>
+      </x:c>
+      <x:c r="D23" s="8" t="str">
+        <x:v>0917770778</x:v>
+      </x:c>
+      <x:c r="E23" s="4" t="str">
+        <x:v>Grupo 1 - Aula D200</x:v>
+      </x:c>
+      <x:c r="F23" s="4" t="str">
+        <x:v>Grupo 1 - Aula D200</x:v>
+      </x:c>
+      <x:c r="G23" s="4" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H23" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="76" customHeight="1">
+      <x:c r="A24" s="4" t="str">
+        <x:v>VILLACRES BELTRAN FABIAN ISAAC</x:v>
+      </x:c>
+      <x:c r="B24" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE NEGOCIOS DIGITALES</x:v>
+      </x:c>
+      <x:c r="C24" s="4" t="str">
+        <x:v>NEGOCIOS DIGITALES</x:v>
+      </x:c>
+      <x:c r="D24" s="8" t="str">
+        <x:v>1204142937</x:v>
+      </x:c>
+      <x:c r="E24" s="4" t="str">
+        <x:v>Grupo 1 - Aula D200</x:v>
+      </x:c>
+      <x:c r="F24" s="4" t="str">
+        <x:v>Grupo 1 - Aula D200</x:v>
+      </x:c>
+      <x:c r="G24" s="4" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="H24" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="76" customHeight="1">
+      <x:c r="A25" s="4" t="str">
+        <x:v>VITERI PALOMEQUE MARIA FERNANDA</x:v>
+      </x:c>
+      <x:c r="B25" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE ARQUITECTURA</x:v>
+      </x:c>
+      <x:c r="C25" s="4" t="str">
+        <x:v>ARQUITECTURA</x:v>
+      </x:c>
+      <x:c r="D25" s="8" t="str">
+        <x:v>0910867407</x:v>
+      </x:c>
+      <x:c r="E25" s="4" t="str">
+        <x:v>Grupo 4 - Aula D203</x:v>
+      </x:c>
+      <x:c r="F25" s="4" t="str">
+        <x:v>Grupo 4 - Aula D203</x:v>
+      </x:c>
+      <x:c r="G25" s="4" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="H25" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="76" customHeight="1">
+      <x:c r="A26" s="4" t="str">
+        <x:v>ZAMBRANO PARRALES FLORA ANGELICA</x:v>
+      </x:c>
+      <x:c r="B26" s="4" t="str">
+        <x:v>DIRECTOR DE CARRERA DE CONTABILIDAD Y AUDITORIA</x:v>
+      </x:c>
+      <x:c r="C26" s="4" t="str">
+        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
+      </x:c>
+      <x:c r="D26" s="8" t="str">
+        <x:v>0917360554</x:v>
+      </x:c>
+      <x:c r="E26" s="4" t="str">
+        <x:v>Grupo 1 - Aula D200</x:v>
+      </x:c>
+      <x:c r="F26" s="4" t="str">
+        <x:v>Grupo 1 - Aula D200</x:v>
+      </x:c>
+      <x:c r="G26" s="4" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="H26" s="4" t="str">
+        <x:v>CARGO y DIRECTOR_CARRERA</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="G3:G26">
+    <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="NO"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>

--- a/src/assets/data/Grupos_66.xlsx
+++ b/src/assets/data/Grupos_66.xlsx
@@ -496,13 +496,13 @@
         <x:v>0909119299</x:v>
       </x:c>
       <x:c r="D2" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F2" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G2" s="9" t="str">
         <x:v>Grupo 3 - Aula D202</x:v>
@@ -592,7 +592,7 @@
         <x:v>Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="G5" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H5" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -621,13 +621,13 @@
         <x:v>Grupo 5 - Aula D204</x:v>
       </x:c>
       <x:c r="G6" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H6" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I6" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="65" customHeight="1">
@@ -757,13 +757,13 @@
         <x:v>0922639752</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G11" s="9" t="str">
         <x:v>Grupo 3 - Aula D202</x:v>
@@ -824,13 +824,13 @@
         <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="G13" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H13" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I13" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="65" customHeight="1">
@@ -998,13 +998,13 @@
         <x:v>Grupo 9 - Aula D208</x:v>
       </x:c>
       <x:c r="G19" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H19" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I19" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="65" customHeight="1">
@@ -1018,13 +1018,13 @@
         <x:v>0102054871</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F20" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G20" s="9" t="str">
         <x:v>Grupo 4 - Aula D203</x:v>
@@ -1172,13 +1172,13 @@
         <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="G25" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H25" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I25" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="65" customHeight="1">
@@ -1279,13 +1279,13 @@
         <x:v>0910743954</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F29" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G29" s="9" t="str">
         <x:v>Grupo 5 - Aula D204</x:v>
@@ -1404,13 +1404,13 @@
         <x:v>Grupo 5 - Aula D204</x:v>
       </x:c>
       <x:c r="G33" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H33" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I33" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="65" customHeight="1">
@@ -1491,7 +1491,7 @@
         <x:v>Grupo 8 - Aula D207</x:v>
       </x:c>
       <x:c r="G36" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H36" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -1540,13 +1540,13 @@
         <x:v>0914078290</x:v>
       </x:c>
       <x:c r="D38" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E38" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F38" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G38" s="9" t="str">
         <x:v>Grupo 5 - Aula D204</x:v>
@@ -1636,7 +1636,7 @@
         <x:v>Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="G41" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H41" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -1801,13 +1801,13 @@
         <x:v>0202336749</x:v>
       </x:c>
       <x:c r="D47" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E47" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F47" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G47" s="9" t="str">
         <x:v>Grupo 4 - Aula D203</x:v>
@@ -2013,13 +2013,13 @@
         <x:v>Grupo 8 - Aula D207</x:v>
       </x:c>
       <x:c r="G54" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H54" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I54" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="65" customHeight="1">
@@ -2062,13 +2062,13 @@
         <x:v>1102293402</x:v>
       </x:c>
       <x:c r="D56" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E56" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F56" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G56" s="9" t="str">
         <x:v>Grupo 3 - Aula D202</x:v>
@@ -2323,13 +2323,13 @@
         <x:v>1204922544</x:v>
       </x:c>
       <x:c r="D65" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E65" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F65" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G65" s="9" t="str">
         <x:v>Grupo 3 - Aula D202</x:v>
@@ -2361,13 +2361,13 @@
         <x:v>Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="G66" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H66" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I66" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="65" customHeight="1">
@@ -2584,13 +2584,13 @@
         <x:v>0919123067</x:v>
       </x:c>
       <x:c r="D74" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E74" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F74" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G74" s="9" t="str">
         <x:v>Grupo 3 - Aula D202</x:v>
@@ -2738,13 +2738,13 @@
         <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="G79" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H79" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I79" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="65" customHeight="1">
@@ -2767,7 +2767,7 @@
         <x:v>Grupo 7 - Aula D206</x:v>
       </x:c>
       <x:c r="G80" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H80" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -2845,22 +2845,22 @@
         <x:v>0916168784</x:v>
       </x:c>
       <x:c r="D83" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E83" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F83" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G83" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H83" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I83" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="65" customHeight="1">
@@ -2912,13 +2912,13 @@
         <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="G85" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H85" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I85" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="65" customHeight="1">
@@ -3057,7 +3057,7 @@
         <x:v>Grupo 8 - Aula D207</x:v>
       </x:c>
       <x:c r="G90" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H90" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -3106,13 +3106,13 @@
         <x:v>0921267951</x:v>
       </x:c>
       <x:c r="D92" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E92" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F92" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G92" s="9" t="str">
         <x:v>Grupo 5 - Aula D204</x:v>
@@ -3318,13 +3318,13 @@
         <x:v>Grupo 8 - Aula D207</x:v>
       </x:c>
       <x:c r="G99" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H99" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I99" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="65" customHeight="1">
@@ -3367,13 +3367,13 @@
         <x:v>0914335484</x:v>
       </x:c>
       <x:c r="D101" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E101" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F101" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G101" s="9" t="str">
         <x:v>Grupo 3 - Aula D202</x:v>
@@ -3405,13 +3405,13 @@
         <x:v>Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="G102" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H102" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I102" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="65" customHeight="1">
@@ -3550,13 +3550,13 @@
         <x:v>Grupo 7 - Aula D206</x:v>
       </x:c>
       <x:c r="G107" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H107" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I107" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="65" customHeight="1">
@@ -3608,13 +3608,13 @@
         <x:v>Grupo 9 - Aula D208</x:v>
       </x:c>
       <x:c r="G109" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H109" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I109" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="65" customHeight="1">
@@ -3628,13 +3628,13 @@
         <x:v>0917208084</x:v>
       </x:c>
       <x:c r="D110" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E110" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F110" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G110" s="9" t="str">
         <x:v>Grupo 3 - Aula D202</x:v>
@@ -3889,13 +3889,13 @@
         <x:v>0911019529</x:v>
       </x:c>
       <x:c r="D119" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E119" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F119" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G119" s="9" t="str">
         <x:v>Grupo 4 - Aula D203</x:v>
@@ -4043,7 +4043,7 @@
         <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="G124" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H124" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -4130,13 +4130,13 @@
         <x:v>Grupo 9 - Aula D208</x:v>
       </x:c>
       <x:c r="G127" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H127" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I127" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="65" customHeight="1">
@@ -4150,13 +4150,13 @@
         <x:v>0915336945</x:v>
       </x:c>
       <x:c r="D128" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E128" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F128" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G128" s="9" t="str">
         <x:v>Grupo 8 - Aula por confirmar</x:v>
@@ -4333,13 +4333,13 @@
         <x:v>Grupo 8 - Aula D207</x:v>
       </x:c>
       <x:c r="G134" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H134" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I134" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="65" customHeight="1">
@@ -4382,13 +4382,13 @@
         <x:v>0926684325</x:v>
       </x:c>
       <x:c r="D136" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E136" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F136" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G136" s="9" t="str">
         <x:v>Grupo 5 - Aula D204</x:v>
@@ -4420,13 +4420,13 @@
         <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="G137" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H137" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I137" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="65" customHeight="1">
@@ -4507,13 +4507,13 @@
         <x:v>Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="G140" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H140" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I140" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="65" customHeight="1">
@@ -4652,7 +4652,7 @@
         <x:v>Grupo 9 - Aula D208</x:v>
       </x:c>
       <x:c r="G145" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H145" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -4672,13 +4672,13 @@
         <x:v>0930340112</x:v>
       </x:c>
       <x:c r="D146" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E146" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F146" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G146" s="9" t="str">
         <x:v>Grupo 5 - Aula D204</x:v>
@@ -4768,13 +4768,13 @@
         <x:v>Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="G149" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H149" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I149" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="65" customHeight="1">
@@ -4933,13 +4933,13 @@
         <x:v>0919514117</x:v>
       </x:c>
       <x:c r="D155" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E155" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F155" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G155" s="9" t="str">
         <x:v>Grupo 7 - Aula D206</x:v>
@@ -4971,7 +4971,7 @@
         <x:v>Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="G156" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H156" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -5000,13 +5000,13 @@
         <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="G157" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H157" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I157" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="65" customHeight="1">
@@ -5116,13 +5116,13 @@
         <x:v>Grupo 7 - Aula D206</x:v>
       </x:c>
       <x:c r="G161" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H161" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I161" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="65" customHeight="1">
@@ -5194,13 +5194,13 @@
         <x:v>0914286042</x:v>
       </x:c>
       <x:c r="D164" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E164" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F164" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G164" s="9" t="str">
         <x:v>Grupo 8 - Aula por confirmar</x:v>
@@ -5319,7 +5319,7 @@
         <x:v>Grupo 5 - Aula D204</x:v>
       </x:c>
       <x:c r="G168" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H168" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -5348,7 +5348,7 @@
         <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="G169" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H169" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -5455,13 +5455,13 @@
         <x:v>0905056016</x:v>
       </x:c>
       <x:c r="D173" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E173" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F173" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G173" s="9" t="str">
         <x:v>Grupo 3 - Aula D202</x:v>
@@ -5696,13 +5696,13 @@
         <x:v>Grupo 9 - Aula D208</x:v>
       </x:c>
       <x:c r="G181" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H181" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I181" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="65" customHeight="1">
@@ -5716,13 +5716,13 @@
         <x:v>1310835457</x:v>
       </x:c>
       <x:c r="D182" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E182" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F182" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G182" s="9" t="str">
         <x:v>Grupo 4 - Aula D203</x:v>
@@ -5977,13 +5977,13 @@
         <x:v>1755500665</x:v>
       </x:c>
       <x:c r="D191" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E191" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F191" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G191" s="9" t="str">
         <x:v>Grupo 5 - Aula D204</x:v>
@@ -6218,7 +6218,7 @@
         <x:v>Grupo 9 - Aula D208</x:v>
       </x:c>
       <x:c r="G199" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H199" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -6238,13 +6238,13 @@
         <x:v>0602579948</x:v>
       </x:c>
       <x:c r="D200" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E200" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F200" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G200" s="9" t="str">
         <x:v>Grupo 3 - Aula D202</x:v>
@@ -6499,13 +6499,13 @@
         <x:v>0912155652</x:v>
       </x:c>
       <x:c r="D209" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E209" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F209" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G209" s="9" t="str">
         <x:v>Grupo 6 - Aula D205</x:v>
@@ -6566,13 +6566,13 @@
         <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="G211" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H211" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I211" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="65" customHeight="1">
@@ -6653,7 +6653,7 @@
         <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="G214" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H214" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -6760,13 +6760,13 @@
         <x:v>0922799655</x:v>
       </x:c>
       <x:c r="D218" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E218" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F218" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G218" s="9" t="str">
         <x:v>Grupo 4 - Aula D203</x:v>
@@ -7021,13 +7021,13 @@
         <x:v>0917494890</x:v>
       </x:c>
       <x:c r="D227" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E227" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F227" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G227" s="9" t="str">
         <x:v>Grupo 5 - Aula D204</x:v>
@@ -7282,13 +7282,13 @@
         <x:v>0602162539</x:v>
       </x:c>
       <x:c r="D236" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E236" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F236" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G236" s="9" t="str">
         <x:v>Grupo 6 - Aula D205</x:v>
@@ -7349,7 +7349,7 @@
         <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="G238" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H238" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -7436,13 +7436,13 @@
         <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="G241" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H241" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I241" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="65" customHeight="1">
@@ -7543,16 +7543,16 @@
         <x:v>0910952571</x:v>
       </x:c>
       <x:c r="D245" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E245" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F245" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G245" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H245" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -7804,13 +7804,13 @@
         <x:v>0924194889</x:v>
       </x:c>
       <x:c r="D254" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E254" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F254" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G254" s="9" t="str">
         <x:v>Grupo 5 - Aula D204</x:v>
@@ -7958,13 +7958,13 @@
         <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="G259" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H259" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I259" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="260" ht="65" customHeight="1">
@@ -8065,13 +8065,13 @@
         <x:v>0917242448</x:v>
       </x:c>
       <x:c r="D263" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E263" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F263" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G263" s="9" t="str">
         <x:v>Grupo 4 - Aula D203</x:v>
@@ -8324,13 +8324,13 @@
         <x:v>0950594754</x:v>
       </x:c>
       <x:c r="D272" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E272" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F272" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G272" s="9" t="str">
         <x:v>Grupo 5 - Aula D204</x:v>
@@ -8585,13 +8585,13 @@
         <x:v>1705290128</x:v>
       </x:c>
       <x:c r="D281" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E281" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F281" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G281" s="9" t="str">
         <x:v>Grupo 4 - Aula D203</x:v>
@@ -8623,13 +8623,13 @@
         <x:v>Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="G282" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H282" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I282" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="283" ht="65" customHeight="1">
@@ -8797,13 +8797,13 @@
         <x:v>Grupo 8 - Aula D207</x:v>
       </x:c>
       <x:c r="G288" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H288" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I288" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="289" ht="65" customHeight="1">
@@ -8817,22 +8817,22 @@
         <x:v>1204142937</x:v>
       </x:c>
       <x:c r="D289" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E289" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F289" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G289" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H289" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I289" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="290" ht="65" customHeight="1">
@@ -9000,13 +9000,13 @@
         <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="G295" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H295" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I295" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="296" ht="65" customHeight="1">
@@ -9058,13 +9058,13 @@
         <x:v>Grupo 8 - Aula D207</x:v>
       </x:c>
       <x:c r="G297" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H297" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I297" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="298" ht="65" customHeight="1">
@@ -9087,13 +9087,13 @@
         <x:v>Grupo 9 - Aula D208</x:v>
       </x:c>
       <x:c r="G298" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H298" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I298" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
     <x:row r="299" ht="65" customHeight="1">
@@ -9107,22 +9107,22 @@
         <x:v>0917375537</x:v>
       </x:c>
       <x:c r="D299" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E299" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F299" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G299" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="H299" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="I299" s="9" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10626,7 +10626,7 @@
     </x:row>
     <x:row r="3" ht="93" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="B3" s="4" t="str">
         <x:v>FABIÁN LEONARDO CUESTA ASTUDILLO (DIRECTOR NACIONAL)
@@ -10884,7 +10884,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -10914,7 +10914,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
         <x:v>NEGOCIOS DIGITALES</x:v>
@@ -10944,7 +10944,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -10974,7 +10974,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -11004,7 +11004,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -11034,7 +11034,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -11064,7 +11064,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -11094,7 +11094,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -11124,7 +11124,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -11154,7 +11154,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D12" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -11184,7 +11184,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
         <x:v>MAESTRIA EN GERENCIA TRIBUTARIA</x:v>
@@ -11214,7 +11214,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D14" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -11244,7 +11244,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D15" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
         <x:v>DIRECCION TECNICA DE PLANEACION EVALUACION Y ACREDITACION</x:v>
@@ -11274,7 +11274,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
         <x:v>ECONOMIA</x:v>
@@ -11304,7 +11304,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -11334,7 +11334,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -11364,7 +11364,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -11394,7 +11394,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -11424,7 +11424,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -11454,7 +11454,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D22" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
         <x:v>ECONOMIA</x:v>
@@ -11484,7 +11484,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -11514,7 +11514,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D24" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
         <x:v>NEGOCIOS DIGITALES</x:v>
@@ -11544,7 +11544,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
         <x:v>ECONOMIA</x:v>
@@ -11574,7 +11574,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D26" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -11604,7 +11604,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D27" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -11634,7 +11634,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D28" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
         <x:v>ECONOMIA</x:v>
@@ -11664,7 +11664,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D29" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -11694,7 +11694,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D30" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
         <x:v>NEGOCIOS DIGITALES</x:v>
@@ -11724,7 +11724,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D31" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
         <x:v>NEGOCIOS DIGITALES</x:v>
@@ -11754,7 +11754,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D32" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -11784,7 +11784,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D33" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -11814,7 +11814,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D34" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E34" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -16275,7 +16275,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
@@ -16297,8 +16297,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
         <x:v>lalarcon@ups.edu.ec</x:v>
@@ -16451,8 +16451,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
         <x:v>eandradee@ups.edu.ec</x:v>
@@ -16583,8 +16583,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
         <x:v>kascencio@ups.edu.ec</x:v>
@@ -16715,8 +16715,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
         <x:v>jbalas@ups.edu.ec</x:v>
@@ -16891,8 +16891,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D33" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
         <x:v>mbastidas@ups.edu.ec</x:v>
@@ -16957,7 +16957,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D36" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E36" s="4" t="str">
@@ -17067,7 +17067,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D41" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E41" s="4" t="str">
@@ -17353,8 +17353,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D54" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E54" s="4" t="str">
         <x:v>jcarreraj@ups.edu.ec</x:v>
@@ -17617,8 +17617,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D66" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E66" s="4" t="str">
         <x:v>mchavez@ups.edu.ec</x:v>
@@ -17903,8 +17903,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D79" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E79" s="4" t="str">
         <x:v>jcueva@ups.edu.ec</x:v>
@@ -17925,7 +17925,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D80" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E80" s="4" t="str">
@@ -17991,8 +17991,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D83" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E83" s="4" t="str">
         <x:v>ddefas@ups.edu.ec</x:v>
@@ -18035,8 +18035,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D85" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E85" s="4" t="str">
         <x:v>sdelgadof@ups.edu.ec</x:v>
@@ -18145,7 +18145,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D90" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E90" s="4" t="str">
@@ -18343,8 +18343,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D99" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E99" s="4" t="str">
         <x:v>gespinozar@ups.edu.ec</x:v>
@@ -18409,8 +18409,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D102" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E102" s="4" t="str">
         <x:v>ofiallos@ups.edu.ec</x:v>
@@ -18519,8 +18519,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D107" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E107" s="4" t="str">
         <x:v>efranco@ups.edu.ec</x:v>
@@ -18563,8 +18563,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D109" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E109" s="4" t="str">
         <x:v>jfreirem@ups.edu.ec</x:v>
@@ -18893,7 +18893,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D124" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E124" s="4" t="str">
@@ -18959,8 +18959,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D127" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E127" s="4" t="str">
         <x:v>fherrera@ups.edu.ec</x:v>
@@ -19113,8 +19113,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D134" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E134" s="4" t="str">
         <x:v>eissa@ups.edu.ec</x:v>
@@ -19179,8 +19179,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D137" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E137" s="4" t="str">
         <x:v>hiniguez@ups.edu.ec</x:v>
@@ -19245,8 +19245,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D140" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E140" s="4" t="str">
         <x:v>mjaram@ups.edu.ec</x:v>
@@ -19355,7 +19355,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D145" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E145" s="4" t="str">
@@ -19443,8 +19443,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D149" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E149" s="4" t="str">
         <x:v>fleonb@ups.edu.ec</x:v>
@@ -19597,7 +19597,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D156" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E156" s="4" t="str">
@@ -19619,8 +19619,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D157" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E157" s="4" t="str">
         <x:v>alopezn@ups.edu.ec</x:v>
@@ -19707,8 +19707,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D161" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E161" s="4" t="str">
         <x:v>alozano@ups.edu.ec</x:v>
@@ -19861,7 +19861,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D168" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E168" s="4" t="str">
@@ -19883,7 +19883,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D169" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E169" s="4" t="str">
@@ -20147,8 +20147,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D181" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E181" s="4" t="str">
         <x:v>jmorenod@ups.edu.ec</x:v>
@@ -20543,7 +20543,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D199" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E199" s="4" t="str">
@@ -20807,8 +20807,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D211" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E211" s="4" t="str">
         <x:v>spozo@ups.edu.ec</x:v>
@@ -20873,7 +20873,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D214" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E214" s="4" t="str">
@@ -21401,7 +21401,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D238" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E238" s="4" t="str">
@@ -21467,8 +21467,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D241" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E241" s="4" t="str">
         <x:v>esalazar@ups.edu.ec</x:v>
@@ -21555,7 +21555,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D245" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
+        <x:v>T4: Grupo 1 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E245" s="4" t="str">
@@ -21863,8 +21863,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D259" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E259" s="4" t="str">
         <x:v>nsumba@ups.edu.ec</x:v>
@@ -22367,8 +22367,8 @@
 T5 y T6: DIRECTOR/A DE CARRERA (convocado por responsabilidad de carrera)</x:v>
       </x:c>
       <x:c r="D282" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E282" s="4" t="str">
         <x:v>kvallejo@ups.edu.ec</x:v>
@@ -22499,8 +22499,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D288" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E288" s="4" t="str">
         <x:v>vvera@ups.edu.ec</x:v>
@@ -22521,8 +22521,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D289" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E289" s="4" t="str">
         <x:v>fvillacres@ups.edu.ec</x:v>
@@ -22653,8 +22653,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D295" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E295" s="4" t="str">
         <x:v>tyaguana@ups.edu.ec</x:v>
@@ -22697,8 +22697,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D297" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E297" s="4" t="str">
         <x:v>fzambrano@ups.edu.ec</x:v>
@@ -22719,8 +22719,8 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D298" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E298" s="4" t="str">
         <x:v>nzea@ups.edu.ec</x:v>
@@ -22741,8 +22741,8 @@
 T5 y T6: RESP. AREA CONOC. SEDE</x:v>
       </x:c>
       <x:c r="D299" s="4" t="str">
-        <x:v>T4: Grupo 1 - Aula D200
-T5 y T6: Grupo 1 - Aula D200</x:v>
+        <x:v>T4: Grupo 1 - Aula D209
+T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E299" s="4" t="str">
         <x:v>mzunigaa@ups.edu.ec</x:v>
@@ -23272,7 +23272,7 @@
   <x:sheetData>
     <x:row r="1" ht="52" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>TALLERES 1, 2 Y 3 — Lunes 12 y martes 13 de octubre — Grupo 1 — Campus Centenario - Edif. D - Piso 1 - Aula D200</x:v>
+        <x:v>TALLERES 1, 2 Y 3 — Lunes 12 y martes 13 de octubre — Grupo 1 — Campus Centenario - Edif. D - Piso 1 - Aula D209</x:v>
       </x:c>
       <x:c r="B1" s="11"/>
       <x:c r="C1" s="11"/>
@@ -23323,7 +23323,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
         <x:v>INGENIERIA AUTOMOTRIZ</x:v>
@@ -23352,7 +23352,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
         <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
@@ -23381,7 +23381,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
         <x:v>INGENIERIA ELECTRICA</x:v>
@@ -23410,7 +23410,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
         <x:v>ODONTOLOGIA</x:v>
@@ -23439,7 +23439,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
         <x:v>INGENIERIA AMBIENTAL</x:v>
@@ -23468,7 +23468,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
         <x:v>INGENIERIA AUTOMOTRIZ</x:v>
@@ -23497,7 +23497,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
         <x:v>TELECOMUNICACIONES</x:v>
@@ -23526,7 +23526,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
         <x:v>INGENIERIA CIVIL</x:v>
@@ -23555,7 +23555,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
         <x:v>TELECOMUNICACIONES</x:v>
@@ -23584,7 +23584,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D12" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -23613,7 +23613,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
         <x:v>PSICOLOGIA CLINICA</x:v>
@@ -23642,7 +23642,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D14" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
         <x:v>MECATRONICA</x:v>
@@ -23671,7 +23671,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D15" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
         <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
@@ -23700,7 +23700,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
         <x:v>INGENIERIA INDUSTRIAL</x:v>
@@ -23729,7 +23729,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
         <x:v>INSTITUTO DE IDIOMAS</x:v>
@@ -23758,7 +23758,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
         <x:v>ODONTOLOGIA</x:v>
@@ -23787,7 +23787,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
         <x:v>ODONTOLOGIA</x:v>
@@ -23816,7 +23816,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
         <x:v>TEOLOGIA MODALIDAD EN LINEA</x:v>
@@ -23845,7 +23845,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
         <x:v>INSTITUTO DE IDIOMAS</x:v>
@@ -23874,7 +23874,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D22" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
         <x:v>INGENIERIA INDUSTRIAL</x:v>
@@ -23903,7 +23903,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
         <x:v>INGENIERIA CIVIL</x:v>
@@ -23932,7 +23932,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D24" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
         <x:v>ODONTOLOGIA</x:v>
@@ -23961,7 +23961,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
         <x:v>COORDINACIÓN DE DESARROLLO ACADÉMICO</x:v>
@@ -23990,7 +23990,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D26" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
         <x:v>EDUCACION INICIAL</x:v>
@@ -24019,7 +24019,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D27" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
         <x:v>MAESTRIA EN ANALITICA DE DATOS</x:v>
@@ -24048,7 +24048,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D28" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
         <x:v>ODONTOLOGIA</x:v>
@@ -24077,7 +24077,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D29" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
         <x:v>PEDAGOGIA DE LA ACTIVIDAD FISICA</x:v>
@@ -24106,7 +24106,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D30" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -24135,7 +24135,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D31" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
         <x:v>PSICOLOGIA CLINICA</x:v>
@@ -24164,7 +24164,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D32" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
         <x:v>INGENIERIA INDUSTRIAL</x:v>
@@ -24193,7 +24193,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D33" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
         <x:v>PSICOLOGIA CLINICA</x:v>
@@ -24222,7 +24222,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D34" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E34" s="4" t="str">
         <x:v>ARQUITECTURA</x:v>
@@ -24251,7 +24251,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D35" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E35" s="4" t="str">
         <x:v>NEGOCIOS DIGITALES</x:v>
@@ -24280,7 +24280,7 @@
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
       </x:c>
       <x:c r="D36" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E36" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -31517,7 +31517,7 @@
     </x:row>
     <x:row r="3" ht="45" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="B3" s="4" t="str">
         <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
@@ -31695,7 +31695,7 @@
     </x:row>
     <x:row r="16" ht="65" customHeight="1">
       <x:c r="A16" s="4" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
         <x:v>Administración y economía</x:v>
@@ -32905,7 +32905,7 @@
         <x:v>Grupo 1</x:v>
       </x:c>
       <x:c r="B3" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="C3" s="14" t="n">
         <x:f>'T5-6 Resumen'!D3</x:f>
@@ -33725,10 +33725,10 @@
         <x:v>0916656408</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F12" s="4" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
         <x:v>SI</x:v>
@@ -34011,10 +34011,10 @@
         <x:v>0917770778</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F23" s="4" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
         <x:v>NO</x:v>
@@ -34037,10 +34037,10 @@
         <x:v>1204142937</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F24" s="4" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
         <x:v>SI</x:v>
@@ -34089,10 +34089,10 @@
         <x:v>0917360554</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="F26" s="4" t="str">
-        <x:v>Grupo 1 - Aula D200</x:v>
+        <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
         <x:v>SI</x:v>
@@ -34164,7 +34164,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
         <x:v>FABIÁN LEONARDO CUESTA ASTUDILLO (DIRECTOR NACIONAL)
@@ -34413,7 +34413,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -34443,7 +34443,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -34473,7 +34473,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
         <x:v>NEGOCIOS DIGITALES</x:v>
@@ -34503,7 +34503,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -34533,7 +34533,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -34563,7 +34563,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -34593,7 +34593,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
         <x:v>ECONOMIA</x:v>
@@ -34623,7 +34623,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -34653,7 +34653,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -34683,7 +34683,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D12" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -34713,7 +34713,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -34743,7 +34743,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D14" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -34773,7 +34773,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D15" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -34803,7 +34803,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -34833,7 +34833,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -34863,7 +34863,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
         <x:v>MAESTRIA EN GERENCIA TRIBUTARIA</x:v>
@@ -34893,7 +34893,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -34923,7 +34923,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
         <x:v>DIRECCION TECNICA DE PLANEACION EVALUACION Y ACREDITACION</x:v>
@@ -34953,7 +34953,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
         <x:v>ECONOMIA</x:v>
@@ -34983,7 +34983,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D22" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -35013,7 +35013,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -35043,7 +35043,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D24" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -35073,7 +35073,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -35103,7 +35103,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D26" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -35133,7 +35133,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D27" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
         <x:v>VICERRECTORADO DE SEDE</x:v>
@@ -35163,7 +35163,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D28" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -35193,7 +35193,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D29" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -35223,7 +35223,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D30" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
         <x:v>ECONOMIA</x:v>
@@ -35253,7 +35253,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D31" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -35283,7 +35283,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D32" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
         <x:v>DIRECCION TECNICA DE VINCULACION CON LA SOCIEDAD</x:v>
@@ -35313,7 +35313,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D33" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -35343,7 +35343,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D34" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E34" s="4" t="str">
         <x:v>NEGOCIOS DIGITALES</x:v>
@@ -35373,7 +35373,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D35" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E35" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -35403,7 +35403,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D36" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E36" s="4" t="str">
         <x:v>ECONOMIA</x:v>
@@ -35433,7 +35433,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D37" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E37" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -35463,7 +35463,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D38" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E38" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -35493,7 +35493,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D39" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E39" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -35523,7 +35523,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D40" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E40" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -35553,7 +35553,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D41" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E41" s="4" t="str">
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
@@ -35583,7 +35583,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D42" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E42" s="4" t="str">
         <x:v>ECONOMIA</x:v>
@@ -35613,7 +35613,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D43" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E43" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -35643,7 +35643,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D44" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E44" s="4" t="str">
         <x:v>NEGOCIOS DIGITALES</x:v>
@@ -35673,7 +35673,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D45" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E45" s="4" t="str">
         <x:v>NEGOCIOS DIGITALES</x:v>
@@ -35703,7 +35703,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D46" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E46" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -35733,7 +35733,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D47" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E47" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
@@ -35763,7 +35763,7 @@
 ZUÑIGA ALVARADO MARIA ALEJANDRA (RESPONSABLE SEDE)</x:v>
       </x:c>
       <x:c r="D48" s="4" t="str">
-        <x:v>Aula D200</x:v>
+        <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E48" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>

--- a/src/assets/data/Grupos_66.xlsx
+++ b/src/assets/data/Grupos_66.xlsx
@@ -1,41 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convocatoria" sheetId="1" r:id="Rec5f3c4259f24e97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mié-Jue detalle" sheetId="2" r:id="Rdf719e138c164131"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="3" r:id="R89b3d14c50cd4b51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2-4 Resumen" sheetId="34" r:id="Rf858a1599fb94555"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2-4 Grupo 1" sheetId="35" r:id="Rd6e247c21cdc400f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2-4 Grupo 2" sheetId="36" r:id="R808cac62b3364120"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2-4 Grupo 3" sheetId="37" r:id="Rbe819fde72e44e8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2-4 Grupo 4" sheetId="38" r:id="Rb796f42cacbc4f0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2-4 Grupo 5" sheetId="39" r:id="R90981f01882a4e2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2-4 Grupo 6" sheetId="40" r:id="R6f3ce9c1e8364d3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2-4 Grupo 7" sheetId="41" r:id="R4cdce8fdc6f7443d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2-4 Grupo 8" sheetId="42" r:id="R95a54401a08d4810"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2-4 Grupo 9" sheetId="43" r:id="R4445c14f152c47b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2-4 Grupo 10" sheetId="44" r:id="R14f7e1da1b3341e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Resumen" sheetId="14" r:id="R64d7c9dd8ba04d69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 1" sheetId="15" r:id="R9ea891b89c764ddd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 2" sheetId="16" r:id="R1369cd6050f6488e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 3" sheetId="17" r:id="Rec7e678b413b4310"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 4" sheetId="18" r:id="R30333be86014471e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 5" sheetId="19" r:id="R73e9d760a23d4249"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 6" sheetId="20" r:id="R3c43523b3f894372"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5-6 Grupo 7" sheetId="21" r:id="Rf9a6b312a31e49c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 1" sheetId="22" r:id="R883f60047c064521"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 2" sheetId="23" r:id="R65233397374a4d20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 3" sheetId="24" r:id="R45350e439abb4b29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 4" sheetId="25" r:id="Re53901fca2894b91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 5" sheetId="26" r:id="Rbf449210f7b8448d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 6" sheetId="27" r:id="R8109894ad90f4582"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 7" sheetId="28" r:id="R4a0e55665552401e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 8" sheetId="29" r:id="Rddce088f8d874046"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Grupo 9" sheetId="30" r:id="Rcf656e9cbfd442c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T6 Resumen" sheetId="31" r:id="R3dfcf29ad3b84b88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inactivos fuente" sheetId="32" r:id="Rdb83b1dcc58a4390"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Directores carrera" sheetId="33" r:id="Re448a26498654db5"/>
+    <x:sheet name="Convocatoria" sheetId="1" r:id="R304440d49f564a79"/>
+    <x:sheet name="Mié-Jue detalle" sheetId="2" r:id="Rc1fec1db9d9a42f0"/>
+    <x:sheet name="Resumen" sheetId="3" r:id="R72687a25a4674416"/>
+    <x:sheet name="T2-4 Resumen" sheetId="34" r:id="R2dba01e8c85f49c3"/>
+    <x:sheet name="T2-4 Grupo 1" sheetId="35" r:id="Rbb60b6dc31da4228"/>
+    <x:sheet name="T2-4 Grupo 2" sheetId="36" r:id="R759a4d4d84df42df"/>
+    <x:sheet name="T2-4 Grupo 3" sheetId="37" r:id="Rf72df327c79646d2"/>
+    <x:sheet name="T2-4 Grupo 4" sheetId="38" r:id="R6a8b5ce54fdd43bf"/>
+    <x:sheet name="T2-4 Grupo 5" sheetId="39" r:id="R1f30d46a0c704aae"/>
+    <x:sheet name="T2-4 Grupo 6" sheetId="40" r:id="R4fba87e246c34e4c"/>
+    <x:sheet name="T2-4 Grupo 7" sheetId="41" r:id="R88bfa82a9c1c4c04"/>
+    <x:sheet name="T2-4 Grupo 8" sheetId="42" r:id="R95f762a6e1174ff9"/>
+    <x:sheet name="T2-4 Grupo 9" sheetId="43" r:id="R4453d32408fb4f38"/>
+    <x:sheet name="T5-6 Resumen" sheetId="14" r:id="Rd7e5b749f75a44eb"/>
+    <x:sheet name="T5-6 Grupo 1" sheetId="15" r:id="R41c704eb32ec4959"/>
+    <x:sheet name="T5-6 Grupo 2" sheetId="16" r:id="R032e402623f44038"/>
+    <x:sheet name="T5-6 Grupo 3" sheetId="17" r:id="R38eb4d7961d34bdc"/>
+    <x:sheet name="T5-6 Grupo 4" sheetId="18" r:id="R5cdda0cfdc804a71"/>
+    <x:sheet name="T5-6 Grupo 5" sheetId="19" r:id="R9c47fb1695b44da1"/>
+    <x:sheet name="T5-6 Grupo 6" sheetId="20" r:id="Rce885464738a4a52"/>
+    <x:sheet name="T5-6 Grupo 7" sheetId="21" r:id="Rfa2a9e512899402f"/>
+    <x:sheet name="T1 Grupo 1" sheetId="22" r:id="R8028e97e563042a8"/>
+    <x:sheet name="T1 Grupo 2" sheetId="23" r:id="Rdb1289ed6f7d4c2a"/>
+    <x:sheet name="T1 Grupo 3" sheetId="24" r:id="R3247cb908e394a5d"/>
+    <x:sheet name="T1 Grupo 4" sheetId="25" r:id="R0326042f9e7d4050"/>
+    <x:sheet name="T1 Grupo 5" sheetId="26" r:id="R2cfd34f967e347ed"/>
+    <x:sheet name="T1 Grupo 6" sheetId="27" r:id="Rea5474ef42354659"/>
+    <x:sheet name="T1 Grupo 7" sheetId="28" r:id="R8b95918a04414336"/>
+    <x:sheet name="T1 Grupo 8" sheetId="29" r:id="R0b2c369cb09c42a1"/>
+    <x:sheet name="T1 Grupo 9" sheetId="30" r:id="R9460fdfd942d428b"/>
+    <x:sheet name="T6 Resumen" sheetId="31" r:id="R02d30ed9ae2246b4"/>
+    <x:sheet name="Inactivos fuente" sheetId="32" r:id="Rda5c411054fe492d"/>
+    <x:sheet name="Directores carrera" sheetId="33" r:id="Raa6f49a327334dfc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -580,13 +579,13 @@
         <x:v>Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 3 - Aula D203</x:v>
       </x:c>
       <x:c r="F3" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 3 - Aula D203</x:v>
       </x:c>
       <x:c r="G3" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 3 - Aula D203</x:v>
       </x:c>
       <x:c r="H3" s="9" t="str">
         <x:v>Grupo 3 - Aula D202</x:v>
@@ -841,13 +840,13 @@
         <x:v>Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 1 - Aula D201</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 1 - Aula D201</x:v>
       </x:c>
       <x:c r="G12" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 1 - Aula D201</x:v>
       </x:c>
       <x:c r="H12" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -1247,13 +1246,13 @@
         <x:v>Grupo 7 - Aula D206</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 6 - Aula D206</x:v>
       </x:c>
       <x:c r="F26" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 6 - Aula D206</x:v>
       </x:c>
       <x:c r="G26" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 6 - Aula D206</x:v>
       </x:c>
       <x:c r="H26" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -1624,13 +1623,13 @@
         <x:v>Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="E39" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 4 - Aula D204</x:v>
       </x:c>
       <x:c r="F39" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 4 - Aula D204</x:v>
       </x:c>
       <x:c r="G39" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 4 - Aula D204</x:v>
       </x:c>
       <x:c r="H39" s="9" t="str">
         <x:v>Grupo 2 - Aula D201</x:v>
@@ -1711,13 +1710,13 @@
         <x:v>Grupo 5 - Aula D204</x:v>
       </x:c>
       <x:c r="E42" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 1 - Aula D201</x:v>
       </x:c>
       <x:c r="F42" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 1 - Aula D201</x:v>
       </x:c>
       <x:c r="G42" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 1 - Aula D201</x:v>
       </x:c>
       <x:c r="H42" s="9" t="str">
         <x:v>Grupo 5 - Aula D204</x:v>
@@ -1827,13 +1826,13 @@
         <x:v>Grupo 9 - Aula D208</x:v>
       </x:c>
       <x:c r="E46" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 5 - Aula D205</x:v>
       </x:c>
       <x:c r="F46" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 5 - Aula D205</x:v>
       </x:c>
       <x:c r="G46" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 5 - Aula D205</x:v>
       </x:c>
       <x:c r="H46" s="9" t="str">
         <x:v>Grupo 4 - Aula D203</x:v>
@@ -1856,13 +1855,13 @@
         <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E47" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 2 - Aula D202</x:v>
       </x:c>
       <x:c r="F47" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 2 - Aula D202</x:v>
       </x:c>
       <x:c r="G47" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 2 - Aula D202</x:v>
       </x:c>
       <x:c r="H47" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -2610,13 +2609,13 @@
         <x:v>Grupo 9 - Aula D208</x:v>
       </x:c>
       <x:c r="E73" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 8 - Aula D208</x:v>
       </x:c>
       <x:c r="F73" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 8 - Aula D208</x:v>
       </x:c>
       <x:c r="G73" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 8 - Aula D208</x:v>
       </x:c>
       <x:c r="H73" s="9" t="str">
         <x:v>Grupo 7 - Aula D206</x:v>
@@ -2871,13 +2870,13 @@
         <x:v>Grupo 9 - Aula D208</x:v>
       </x:c>
       <x:c r="E82" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 8 - Aula D208</x:v>
       </x:c>
       <x:c r="F82" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 8 - Aula D208</x:v>
       </x:c>
       <x:c r="G82" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 8 - Aula D208</x:v>
       </x:c>
       <x:c r="H82" s="9" t="str">
         <x:v>Grupo 3 - Aula D202</x:v>
@@ -2900,13 +2899,13 @@
         <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E83" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 9 - Aula D209</x:v>
       </x:c>
       <x:c r="F83" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 9 - Aula D209</x:v>
       </x:c>
       <x:c r="G83" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 9 - Aula D209</x:v>
       </x:c>
       <x:c r="H83" s="9" t="str">
         <x:v>Grupo 1 - Aula D209</x:v>
@@ -3074,13 +3073,13 @@
         <x:v>Grupo 7 - Aula D206</x:v>
       </x:c>
       <x:c r="E89" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 3 - Aula D203</x:v>
       </x:c>
       <x:c r="F89" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 3 - Aula D203</x:v>
       </x:c>
       <x:c r="G89" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 3 - Aula D203</x:v>
       </x:c>
       <x:c r="H89" s="9" t="str">
         <x:v>Grupo 2 - Aula D201</x:v>
@@ -3103,13 +3102,13 @@
         <x:v>Grupo 8 - Aula D207</x:v>
       </x:c>
       <x:c r="E90" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 6 - Aula D206</x:v>
       </x:c>
       <x:c r="F90" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 6 - Aula D206</x:v>
       </x:c>
       <x:c r="G90" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 6 - Aula D206</x:v>
       </x:c>
       <x:c r="H90" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -4002,13 +4001,13 @@
         <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="E121" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 1 - Aula D201</x:v>
       </x:c>
       <x:c r="F121" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 1 - Aula D201</x:v>
       </x:c>
       <x:c r="G121" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 1 - Aula D201</x:v>
       </x:c>
       <x:c r="H121" s="9" t="str">
         <x:v>Grupo 3 - Aula D202</x:v>
@@ -4089,13 +4088,13 @@
         <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="E124" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 7 - Aula D207</x:v>
       </x:c>
       <x:c r="F124" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 7 - Aula D207</x:v>
       </x:c>
       <x:c r="G124" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 7 - Aula D207</x:v>
       </x:c>
       <x:c r="H124" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -4147,13 +4146,13 @@
         <x:v>Grupo 8 - Aula D207</x:v>
       </x:c>
       <x:c r="E126" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 2 - Aula D202</x:v>
       </x:c>
       <x:c r="F126" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 2 - Aula D202</x:v>
       </x:c>
       <x:c r="G126" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 2 - Aula D202</x:v>
       </x:c>
       <x:c r="H126" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -4234,13 +4233,13 @@
         <x:v>Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="E129" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 9 - Aula D209</x:v>
       </x:c>
       <x:c r="F129" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 9 - Aula D209</x:v>
       </x:c>
       <x:c r="G129" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 9 - Aula D209</x:v>
       </x:c>
       <x:c r="H129" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -5336,13 +5335,13 @@
         <x:v>Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="E167" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 9 - Aula D209</x:v>
       </x:c>
       <x:c r="F167" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 9 - Aula D209</x:v>
       </x:c>
       <x:c r="G167" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 9 - Aula D209</x:v>
       </x:c>
       <x:c r="H167" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -5394,13 +5393,13 @@
         <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="E169" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 5 - Aula D205</x:v>
       </x:c>
       <x:c r="F169" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 5 - Aula D205</x:v>
       </x:c>
       <x:c r="G169" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 5 - Aula D205</x:v>
       </x:c>
       <x:c r="H169" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -5974,13 +5973,13 @@
         <x:v>Grupo 8 - Aula D207</x:v>
       </x:c>
       <x:c r="E189" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 8 - Aula D208</x:v>
       </x:c>
       <x:c r="F189" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 8 - Aula D208</x:v>
       </x:c>
       <x:c r="G189" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 8 - Aula D208</x:v>
       </x:c>
       <x:c r="H189" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -6293,13 +6292,13 @@
         <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E200" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 9 - Aula D209</x:v>
       </x:c>
       <x:c r="F200" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 9 - Aula D209</x:v>
       </x:c>
       <x:c r="G200" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 9 - Aula D209</x:v>
       </x:c>
       <x:c r="H200" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -6467,13 +6466,13 @@
         <x:v>Grupo 8 - Aula D207</x:v>
       </x:c>
       <x:c r="E206" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 7 - Aula D207</x:v>
       </x:c>
       <x:c r="F206" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 7 - Aula D207</x:v>
       </x:c>
       <x:c r="G206" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 7 - Aula D207</x:v>
       </x:c>
       <x:c r="H206" s="9" t="str">
         <x:v>Grupo 4 - Aula D203</x:v>
@@ -6554,13 +6553,13 @@
         <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E209" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 6 - Aula D206</x:v>
       </x:c>
       <x:c r="F209" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 6 - Aula D206</x:v>
       </x:c>
       <x:c r="G209" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 6 - Aula D206</x:v>
       </x:c>
       <x:c r="H209" s="9" t="str">
         <x:v>Grupo 6 - Aula D205</x:v>
@@ -6583,13 +6582,13 @@
         <x:v>Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="E210" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 1 - Aula D201</x:v>
       </x:c>
       <x:c r="F210" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 1 - Aula D201</x:v>
       </x:c>
       <x:c r="G210" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 1 - Aula D201</x:v>
       </x:c>
       <x:c r="H210" s="9" t="str">
         <x:v>Grupo 2 - Aula D201</x:v>
@@ -7250,13 +7249,13 @@
         <x:v>Grupo 7 - Aula D206</x:v>
       </x:c>
       <x:c r="E233" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 3 - Aula D203</x:v>
       </x:c>
       <x:c r="F233" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 3 - Aula D203</x:v>
       </x:c>
       <x:c r="G233" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 3 - Aula D203</x:v>
       </x:c>
       <x:c r="H233" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -7975,13 +7974,13 @@
         <x:v>Grupo 5 - Aula D204</x:v>
       </x:c>
       <x:c r="E258" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 5 - Aula D205</x:v>
       </x:c>
       <x:c r="F258" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 5 - Aula D205</x:v>
       </x:c>
       <x:c r="G258" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 5 - Aula D205</x:v>
       </x:c>
       <x:c r="H258" s="9" t="str">
         <x:v>No Convocado</x:v>
@@ -8091,13 +8090,13 @@
         <x:v>Grupo 9 - Aula D208</x:v>
       </x:c>
       <x:c r="E262" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 4 - Aula D204</x:v>
       </x:c>
       <x:c r="F262" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 4 - Aula D204</x:v>
       </x:c>
       <x:c r="G262" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 4 - Aula D204</x:v>
       </x:c>
       <x:c r="H262" s="9" t="str">
         <x:v>Grupo 4 - Aula D203</x:v>
@@ -8640,13 +8639,13 @@
         <x:v>Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E281" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 2 - Aula D202</x:v>
       </x:c>
       <x:c r="F281" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 2 - Aula D202</x:v>
       </x:c>
       <x:c r="G281" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 2 - Aula D202</x:v>
       </x:c>
       <x:c r="H281" s="9" t="str">
         <x:v>Grupo 4 - Aula D203</x:v>
@@ -8785,13 +8784,13 @@
         <x:v>Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="E286" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 4 - Aula D204</x:v>
       </x:c>
       <x:c r="F286" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 4 - Aula D204</x:v>
       </x:c>
       <x:c r="G286" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 4 - Aula D204</x:v>
       </x:c>
       <x:c r="H286" s="9" t="str">
         <x:v>Grupo 2 - Aula D201</x:v>
@@ -8959,13 +8958,13 @@
         <x:v>Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="E292" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 7 - Aula D207</x:v>
       </x:c>
       <x:c r="F292" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 7 - Aula D207</x:v>
       </x:c>
       <x:c r="G292" s="9" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
+        <x:v>Grupo 7 - Aula D207</x:v>
       </x:c>
       <x:c r="H292" s="9" t="str">
         <x:v>Grupo 4 - Aula D203</x:v>
@@ -9346,19 +9345,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F6" s="8" t="str">
-        <x:v>1309445714</x:v>
+        <x:v>0918282617</x:v>
       </x:c>
       <x:c r="G6" s="4" t="str">
-        <x:v>BARCIA AYALA</x:v>
+        <x:v>BALLADARES FIGUEROA</x:v>
       </x:c>
       <x:c r="H6" s="4" t="str">
-        <x:v>ORLANDO GIOVANNI</x:v>
+        <x:v>LUIS ALBERTO</x:v>
       </x:c>
       <x:c r="I6" s="4" t="str">
-        <x:v>obarcia@ups.edu.ec</x:v>
+        <x:v>lballadares@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
@@ -9375,19 +9374,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F7" s="8" t="str">
-        <x:v>1103547848</x:v>
+        <x:v>1309445714</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
-        <x:v>BASTIDAS SANCHEZ</x:v>
+        <x:v>BARCIA AYALA</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>EDGAR VICENTE</x:v>
+        <x:v>ORLANDO GIOVANNI</x:v>
       </x:c>
       <x:c r="I7" s="4" t="str">
-        <x:v>ebastidas@ups.edu.ec</x:v>
+        <x:v>obarcia@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
@@ -9404,19 +9403,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
-        <x:v>ECONOMIA</x:v>
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str">
-        <x:v>0913582490</x:v>
+        <x:v>1103547848</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
-        <x:v>BAYOLO GARAY</x:v>
+        <x:v>BASTIDAS SANCHEZ</x:v>
       </x:c>
       <x:c r="H8" s="4" t="str">
-        <x:v>ANDRES FABIAN</x:v>
+        <x:v>EDGAR VICENTE</x:v>
       </x:c>
       <x:c r="I8" s="4" t="str">
-        <x:v>abayolo@ups.edu.ec</x:v>
+        <x:v>ebastidas@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
@@ -9433,19 +9432,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>MECATRONICA</x:v>
+        <x:v>ECONOMIA</x:v>
       </x:c>
       <x:c r="F9" s="8" t="str">
-        <x:v>0926417106</x:v>
+        <x:v>0913582490</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
-        <x:v>CARDENAS IBAÑEZ</x:v>
+        <x:v>BAYOLO GARAY</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>MICHELLE DE LOS ANGELES</x:v>
+        <x:v>ANDRES FABIAN</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
-        <x:v>mcardenasi@ups.edu.ec</x:v>
+        <x:v>abayolo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -9462,19 +9461,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str">
-        <x:v>0927211706</x:v>
+        <x:v>0926417106</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
-        <x:v>CHÁVEZ SÁNCHEZ</x:v>
+        <x:v>CARDENAS IBAÑEZ</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>HECTOR ANDRÉS</x:v>
+        <x:v>MICHELLE DE LOS ANGELES</x:v>
       </x:c>
       <x:c r="I10" s="4" t="str">
-        <x:v>hchavez@ups.edu.ec</x:v>
+        <x:v>mcardenasi@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
@@ -9491,19 +9490,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>0803477900</x:v>
+        <x:v>0927211706</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>CORTEZ CAICEDO</x:v>
+        <x:v>CHÁVEZ SÁNCHEZ</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>EDUARDO ENRIQUE</x:v>
+        <x:v>HECTOR ANDRÉS</x:v>
       </x:c>
       <x:c r="I11" s="4" t="str">
-        <x:v>ecortez@ups.edu.ec</x:v>
+        <x:v>hchavez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
@@ -9520,19 +9519,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>0925868549</x:v>
+        <x:v>0803477900</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>DAU JARAMA</x:v>
+        <x:v>CORTEZ CAICEDO</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>GABRIELA ESTEPHANIE</x:v>
+        <x:v>EDUARDO ENRIQUE</x:v>
       </x:c>
       <x:c r="I12" s="4" t="str">
-        <x:v>gdau@ups.edu.ec</x:v>
+        <x:v>ecortez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
@@ -9549,19 +9548,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>1712706462</x:v>
+        <x:v>0925868549</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>ESCOBAR PEREZ</x:v>
+        <x:v>DAU JARAMA</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>JOSE RICARDO</x:v>
+        <x:v>GABRIELA ESTEPHANIE</x:v>
       </x:c>
       <x:c r="I13" s="4" t="str">
-        <x:v>jescobarp@ups.edu.ec</x:v>
+        <x:v>gdau@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
@@ -9578,19 +9577,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>0922357702</x:v>
+        <x:v>0906680871</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>GARCIA FLOR</x:v>
+        <x:v>DOMINGUEZ COLOMA</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>GEOVANNY XAVIER</x:v>
+        <x:v>PATRICIA MARIA DE LOURDES</x:v>
       </x:c>
       <x:c r="I14" s="4" t="str">
-        <x:v>ggarciaf1@ups.edu.ec</x:v>
+        <x:v>pdominguez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
@@ -9607,19 +9606,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>FISIOTERAPIA</x:v>
+        <x:v>ARQUITECTURA</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>0931611024</x:v>
+        <x:v>1712706462</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>GUERRA REYNA</x:v>
+        <x:v>ESCOBAR PEREZ</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>VANESSA VICTORIA</x:v>
+        <x:v>JOSE RICARDO</x:v>
       </x:c>
       <x:c r="I15" s="4" t="str">
-        <x:v>vguerra@ups.edu.ec</x:v>
+        <x:v>jescobarp@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
@@ -9636,19 +9635,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>0917423360</x:v>
+        <x:v>0922357702</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>ISSA MORALES</x:v>
+        <x:v>GARCIA FLOR</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>ERICKA HELENA</x:v>
+        <x:v>GEOVANNY XAVIER</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>eissa@ups.edu.ec</x:v>
+        <x:v>ggarciaf1@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
@@ -9665,19 +9664,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>FISIOTERAPIA</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>0914884879</x:v>
+        <x:v>0931611024</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>LLERENA IZQUIERDO</x:v>
+        <x:v>GUERRA REYNA</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>JOE FRAND</x:v>
+        <x:v>VANESSA VICTORIA</x:v>
       </x:c>
       <x:c r="I17" s="4" t="str">
-        <x:v>jllerena@ups.edu.ec</x:v>
+        <x:v>vguerra@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
@@ -9694,19 +9693,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>INSTITUTO DE IDIOMAS</x:v>
+        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
-        <x:v>0916052384</x:v>
+        <x:v>0917423360</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>MENDOZA COBEÑA</x:v>
+        <x:v>ISSA MORALES</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>ROSY MERCEDES</x:v>
+        <x:v>ERICKA HELENA</x:v>
       </x:c>
       <x:c r="I18" s="4" t="str">
-        <x:v>rmendoza@ups.edu.ec</x:v>
+        <x:v>eissa@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
@@ -9723,19 +9722,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>INGENIERIA CIVIL</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>1310835457</x:v>
+        <x:v>0914884879</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>MOYA CHAVEZ</x:v>
+        <x:v>LLERENA IZQUIERDO</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>LUIS EDUARDO</x:v>
+        <x:v>JOE FRAND</x:v>
       </x:c>
       <x:c r="I19" s="4" t="str">
-        <x:v>lmoya@ups.edu.ec</x:v>
+        <x:v>jllerena@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -9752,19 +9751,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>INSTITUTO DE IDIOMAS</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>0916883093</x:v>
+        <x:v>0916052384</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>NARANJO SANCHEZ</x:v>
+        <x:v>MENDOZA COBEÑA</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>RICARDO ALFREDO</x:v>
+        <x:v>ROSY MERCEDES</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>rnaranjo@ups.edu.ec</x:v>
+        <x:v>rmendoza@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
@@ -9781,19 +9780,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+        <x:v>INGENIERIA CIVIL</x:v>
       </x:c>
       <x:c r="F21" s="8" t="str">
-        <x:v>0916850274</x:v>
+        <x:v>1310835457</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>NG ROBLES</x:v>
+        <x:v>MOYA CHAVEZ</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>THOMAS LANHEN</x:v>
+        <x:v>LUIS EDUARDO</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>tng@ups.edu.ec</x:v>
+        <x:v>lmoya@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
@@ -9810,19 +9809,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F22" s="8" t="str">
-        <x:v>1755500665</x:v>
+        <x:v>0916883093</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>ORELLANA ROMERO</x:v>
+        <x:v>NARANJO SANCHEZ</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>ANDREA VICTORIA</x:v>
+        <x:v>RICARDO ALFREDO</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>aorellanar@ups.edu.ec</x:v>
+        <x:v>rnaranjo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
@@ -9839,19 +9838,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>BIOTECNOLOGIA</x:v>
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>0930726112</x:v>
+        <x:v>0916850274</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>PACHECO FLORES DE VALGAZ</x:v>
+        <x:v>NG ROBLES</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>ANGELA VANESSA</x:v>
+        <x:v>THOMAS LANHEN</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>apachecof@ups.edu.ec</x:v>
+        <x:v>tng@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -9868,19 +9867,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>DERECHO</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F24" s="8" t="str">
-        <x:v>0102808144</x:v>
+        <x:v>1755500665</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>PESANTEZ CASTILLO</x:v>
+        <x:v>ORELLANA ROMERO</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>MARIA AGUSTINA</x:v>
+        <x:v>ANDREA VICTORIA</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>mpesantezc@ups.edu.ec</x:v>
+        <x:v>aorellanar@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
@@ -9897,19 +9896,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+        <x:v>BIOTECNOLOGIA</x:v>
       </x:c>
       <x:c r="F25" s="8" t="str">
-        <x:v>0104025838</x:v>
+        <x:v>0930726112</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>ROCHE INTRIAGO</x:v>
+        <x:v>PACHECO FLORES DE VALGAZ</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>CARLOS WLADIMIR</x:v>
+        <x:v>ANGELA VANESSA</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>croche@ups.edu.ec</x:v>
+        <x:v>apachecof@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -9926,19 +9925,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>INSTITUTO DE IDIOMAS</x:v>
+        <x:v>DERECHO</x:v>
       </x:c>
       <x:c r="F26" s="8" t="str">
-        <x:v>0913139689</x:v>
+        <x:v>0102808144</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>RODRIGUEZ ESPINOZA DE LOS MONTEROS</x:v>
+        <x:v>PESANTEZ CASTILLO</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>AMALIA ELVIRA</x:v>
+        <x:v>MARIA AGUSTINA</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>arodriguez@ups.edu.ec</x:v>
+        <x:v>mpesantezc@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
@@ -9955,19 +9954,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>INSTITUTO DE IDIOMAS</x:v>
+        <x:v>EDUCACION INICIAL</x:v>
       </x:c>
       <x:c r="F27" s="8" t="str">
-        <x:v>0918854035</x:v>
+        <x:v>0912155652</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>SAA PEREZ</x:v>
+        <x:v>POMBO BERMEO</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>LILIANA MARTHA</x:v>
+        <x:v>ANGELICA SUSANA</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>lsaa@ups.edu.ec</x:v>
+        <x:v>apombo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
@@ -9984,19 +9983,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F28" s="8" t="str">
-        <x:v>1203815277</x:v>
+        <x:v>0104025838</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>TAMAYO MENDOZA</x:v>
+        <x:v>ROCHE INTRIAGO</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>MARIA DE LOURDES</x:v>
+        <x:v>CARLOS WLADIMIR</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>mtamayom@ups.edu.ec</x:v>
+        <x:v>croche@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
@@ -10013,19 +10012,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>INSTITUTO DE IDIOMAS</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>0401488564</x:v>
+        <x:v>0913139689</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>TORO LOPEZ</x:v>
+        <x:v>RODRIGUEZ ESPINOZA DE LOS MONTEROS</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>JENNY ELIZABETH</x:v>
+        <x:v>AMALIA ELVIRA</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>jtorol@ups.edu.ec</x:v>
+        <x:v>arodriguez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
@@ -10042,19 +10041,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
+        <x:v>INSTITUTO DE IDIOMAS</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>0926416280</x:v>
+        <x:v>0918854035</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>TRUJILLO MOLINA</x:v>
+        <x:v>SAA PEREZ</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>JOEL DAVID</x:v>
+        <x:v>LILIANA MARTHA</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>jtrujillom@ups.edu.ec</x:v>
+        <x:v>lsaa@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
@@ -10071,19 +10070,19 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>ARQUITECTURA</x:v>
       </x:c>
       <x:c r="F31" s="8" t="str">
-        <x:v>0930225537</x:v>
+        <x:v>1203815277</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>VILLALVA MIELES</x:v>
+        <x:v>TAMAYO MENDOZA</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>KARIN FERNANDA</x:v>
+        <x:v>MARIA DE LOURDES</x:v>
       </x:c>
       <x:c r="I31" s="4" t="str">
-        <x:v>kvillalva@ups.edu.ec</x:v>
+        <x:v>mtamayom@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="48" customHeight="1">
@@ -10100,18 +10099,105 @@
         <x:v>Aula D206</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
+        <x:v>PSICOLOGIA CLINICA</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="str">
+        <x:v>0401488564</x:v>
+      </x:c>
+      <x:c r="G32" s="4" t="str">
+        <x:v>TORO LOPEZ</x:v>
+      </x:c>
+      <x:c r="H32" s="4" t="str">
+        <x:v>JENNY ELIZABETH</x:v>
+      </x:c>
+      <x:c r="I32" s="4" t="str">
+        <x:v>jtorol@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="48" customHeight="1">
+      <x:c r="A33" s="9" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B33" s="9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="str">
+        <x:v>DUNIA JUDITH OJEDA LOAIZA</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>Aula D206</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>ARQUITECTURA</x:v>
+      </x:c>
+      <x:c r="F33" s="8" t="str">
+        <x:v>0926416280</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>TRUJILLO MOLINA</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>JOEL DAVID</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>jtrujillom@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="A34" s="9" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="str">
+        <x:v>DUNIA JUDITH OJEDA LOAIZA</x:v>
+      </x:c>
+      <x:c r="D34" s="4" t="str">
+        <x:v>Aula D206</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="str">
+        <x:v>ODONTOLOGIA</x:v>
+      </x:c>
+      <x:c r="F34" s="8" t="str">
+        <x:v>0930225537</x:v>
+      </x:c>
+      <x:c r="G34" s="4" t="str">
+        <x:v>VILLALVA MIELES</x:v>
+      </x:c>
+      <x:c r="H34" s="4" t="str">
+        <x:v>KARIN FERNANDA</x:v>
+      </x:c>
+      <x:c r="I34" s="4" t="str">
+        <x:v>kvillalva@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="9" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B35" s="9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="str">
+        <x:v>DUNIA JUDITH OJEDA LOAIZA</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>Aula D206</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
       </x:c>
-      <x:c r="F32" s="8" t="str">
+      <x:c r="F35" s="8" t="str">
         <x:v>0917360554</x:v>
       </x:c>
-      <x:c r="G32" s="4" t="str">
+      <x:c r="G35" s="4" t="str">
         <x:v>ZAMBRANO PARRALES</x:v>
       </x:c>
-      <x:c r="H32" s="4" t="str">
+      <x:c r="H35" s="4" t="str">
         <x:v>FLORA ANGELICA</x:v>
       </x:c>
-      <x:c r="I32" s="4" t="str">
+      <x:c r="I35" s="4" t="str">
         <x:v>fzambrano@ups.edu.ec</x:v>
       </x:c>
     </x:row>
@@ -10574,19 +10660,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>0917206294</x:v>
+        <x:v>0917770737</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>HUILCAPI SUBIA</x:v>
+        <x:v>GUERRA VILLALTA</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>VICTOR MANUEL</x:v>
+        <x:v>CHRISTIAN ENRIQUE</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>vhuilcapi@ups.edu.ec</x:v>
+        <x:v>cguerra@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
@@ -10603,19 +10689,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>0601854128</x:v>
+        <x:v>0917206294</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>LEON BARZALLO</x:v>
+        <x:v>HUILCAPI SUBIA</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>FELIX IVAN</x:v>
+        <x:v>VICTOR MANUEL</x:v>
       </x:c>
       <x:c r="I17" s="4" t="str">
-        <x:v>fleonb@ups.edu.ec</x:v>
+        <x:v>vhuilcapi@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
@@ -10632,19 +10718,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>ECONOMIA</x:v>
+        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
-        <x:v>0926904525</x:v>
+        <x:v>0601854128</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>LOPEZ NEMTSEVA</x:v>
+        <x:v>LEON BARZALLO</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>ANA MARIA</x:v>
+        <x:v>FELIX IVAN</x:v>
       </x:c>
       <x:c r="I18" s="4" t="str">
-        <x:v>alopezn@ups.edu.ec</x:v>
+        <x:v>fleonb@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
@@ -10661,19 +10747,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>DISEÑO MULTIMEDIA</x:v>
+        <x:v>ECONOMIA</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>0924000011</x:v>
+        <x:v>0926904525</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>LUCERO GONZALEZ</x:v>
+        <x:v>LOPEZ NEMTSEVA</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>LORENA ISABEL</x:v>
+        <x:v>ANA MARIA</x:v>
       </x:c>
       <x:c r="I19" s="4" t="str">
-        <x:v>llucero@ups.edu.ec</x:v>
+        <x:v>alopezn@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -10690,19 +10776,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>EDUCACION BASICA</x:v>
+        <x:v>DISEÑO MULTIMEDIA</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>0914691910</x:v>
+        <x:v>0924000011</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>MASSUH VILLAVICENCIO</x:v>
+        <x:v>LUCERO GONZALEZ</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>CARLOS MANUEL</x:v>
+        <x:v>LORENA ISABEL</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>cmassuh@ups.edu.ec</x:v>
+        <x:v>llucero@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
@@ -10719,19 +10805,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>EDUCACION BASICA</x:v>
       </x:c>
       <x:c r="F21" s="8" t="str">
-        <x:v>0912380474</x:v>
+        <x:v>0914691910</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>NARANJO SANCHEZ</x:v>
+        <x:v>MASSUH VILLAVICENCIO</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>BERTHA ALICE</x:v>
+        <x:v>CARLOS MANUEL</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>bnaranjo@ups.edu.ec</x:v>
+        <x:v>cmassuh@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
@@ -10748,19 +10834,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F22" s="8" t="str">
-        <x:v>1311942971</x:v>
+        <x:v>0912380474</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>ORLANDO SANTANA</x:v>
+        <x:v>NARANJO SANCHEZ</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>MISHEL DENISSE</x:v>
+        <x:v>BERTHA ALICE</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>morlando@ups.edu.ec</x:v>
+        <x:v>bnaranjo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
@@ -10780,16 +10866,16 @@
         <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>0923512073</x:v>
+        <x:v>1311942971</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>PANCHANA VARGAS</x:v>
+        <x:v>ORLANDO SANTANA</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>GEANELLA JUDITH</x:v>
+        <x:v>MISHEL DENISSE</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>gpanchana@ups.edu.ec</x:v>
+        <x:v>morlando@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -10806,19 +10892,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>DIRECCION TECNICA DE ADMINISTRACION E INVENTARIOS</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F24" s="8" t="str">
-        <x:v>0913456851</x:v>
+        <x:v>0923512073</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>PEREZ MALDONADO</x:v>
+        <x:v>PANCHANA VARGAS</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>CARLOS LUIS</x:v>
+        <x:v>GEANELLA JUDITH</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>cperez@ups.edu.ec</x:v>
+        <x:v>gpanchana@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
@@ -10835,19 +10921,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>DERECHO</x:v>
+        <x:v>DIRECCION TECNICA DE ADMINISTRACION E INVENTARIOS</x:v>
       </x:c>
       <x:c r="F25" s="8" t="str">
-        <x:v>0929557916</x:v>
+        <x:v>0913456851</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>QUITO MEGO</x:v>
+        <x:v>PEREZ MALDONADO</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>ROSSMERY ASHLEY</x:v>
+        <x:v>CARLOS LUIS</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>rquitom@ups.edu.ec</x:v>
+        <x:v>cperez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -10864,19 +10950,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>TECNOLOGIA MECANICA INDUSTRIAL</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F26" s="8" t="str">
-        <x:v>0930744206</x:v>
+        <x:v>0920565066</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>RODRIGUEZ ECHEVERRIA</x:v>
+        <x:v>PIZARRO VASQUEZ</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>CHRISTIAN EDUARDO</x:v>
+        <x:v>GUILLERMO OMAR</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>crodrigueze1@ups.edu.ec</x:v>
+        <x:v>gpizarro@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
@@ -10893,19 +10979,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>DIRECCION TECNICA DE PASTORAL</x:v>
+        <x:v>DERECHO</x:v>
       </x:c>
       <x:c r="F27" s="8" t="str">
-        <x:v>0911978252</x:v>
+        <x:v>0929557916</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>RODRIGUEZ FARIAS</x:v>
+        <x:v>QUITO MEGO</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>MARTHA GISELLA</x:v>
+        <x:v>ROSSMERY ASHLEY</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>mrodriguezf@ups.edu.ec</x:v>
+        <x:v>rquitom@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
@@ -10922,19 +11008,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>TECNOLOGIA MECANICA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F28" s="8" t="str">
-        <x:v>0929198943</x:v>
+        <x:v>0930744206</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>SALGADO ROSADO</x:v>
+        <x:v>RODRIGUEZ ECHEVERRIA</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>THALIA CAROLINA</x:v>
+        <x:v>CHRISTIAN EDUARDO</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>tsalgado@ups.edu.ec</x:v>
+        <x:v>crodrigueze1@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
@@ -10951,19 +11037,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>DISEÑO MULTIMEDIA</x:v>
+        <x:v>DIRECCION TECNICA DE PASTORAL</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>0918508573</x:v>
+        <x:v>0911978252</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>TOLEDO HERRERA</x:v>
+        <x:v>RODRIGUEZ FARIAS</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>LINDA JOHANIE</x:v>
+        <x:v>MARTHA GISELLA</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>ltoledo@ups.edu.ec</x:v>
+        <x:v>mrodriguezf@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
@@ -10980,19 +11066,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>0918552233</x:v>
+        <x:v>0929198943</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>UGALDE VELASQUEZ</x:v>
+        <x:v>SALGADO ROSADO</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>LELYS ANDRES</x:v>
+        <x:v>THALIA CAROLINA</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>lugalde@ups.edu.ec</x:v>
+        <x:v>tsalgado@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
@@ -11009,19 +11095,19 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>FISIOTERAPIA</x:v>
+        <x:v>DISEÑO MULTIMEDIA</x:v>
       </x:c>
       <x:c r="F31" s="8" t="str">
-        <x:v>0914858287</x:v>
+        <x:v>0918508573</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>UNDA VERNELLE</x:v>
+        <x:v>TOLEDO HERRERA</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>ALICIA MARGOTH</x:v>
+        <x:v>LINDA JOHANIE</x:v>
       </x:c>
       <x:c r="I31" s="4" t="str">
-        <x:v>aunda@ups.edu.ec</x:v>
+        <x:v>ltoledo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="48" customHeight="1">
@@ -11038,19 +11124,106 @@
         <x:v>Aula D207</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="str">
+        <x:v>0918552233</x:v>
+      </x:c>
+      <x:c r="G32" s="4" t="str">
+        <x:v>UGALDE VELASQUEZ</x:v>
+      </x:c>
+      <x:c r="H32" s="4" t="str">
+        <x:v>LELYS ANDRES</x:v>
+      </x:c>
+      <x:c r="I32" s="4" t="str">
+        <x:v>lugalde@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="48" customHeight="1">
+      <x:c r="A33" s="9" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B33" s="9" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="str">
+        <x:v>AVILA BAILON JOHN ALEJANDRO</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>Aula D207</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>FISIOTERAPIA</x:v>
+      </x:c>
+      <x:c r="F33" s="8" t="str">
+        <x:v>0914858287</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>UNDA VERNELLE</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>ALICIA MARGOTH</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>aunda@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="A34" s="9" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="str">
+        <x:v>AVILA BAILON JOHN ALEJANDRO</x:v>
+      </x:c>
+      <x:c r="D34" s="4" t="str">
+        <x:v>Aula D207</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="str">
         <x:v>ODONTOLOGIA</x:v>
       </x:c>
-      <x:c r="F32" s="8" t="str">
+      <x:c r="F34" s="8" t="str">
         <x:v>0922028915</x:v>
       </x:c>
-      <x:c r="G32" s="4" t="str">
+      <x:c r="G34" s="4" t="str">
         <x:v>VILLACRÉS BARREIRO</x:v>
       </x:c>
-      <x:c r="H32" s="4" t="str">
+      <x:c r="H34" s="4" t="str">
         <x:v>ARIADNA SOFÍA</x:v>
       </x:c>
-      <x:c r="I32" s="4" t="str">
+      <x:c r="I34" s="4" t="str">
         <x:v>avillacres@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="9" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B35" s="9" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="str">
+        <x:v>AVILA BAILON JOHN ALEJANDRO</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>Aula D207</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
+        <x:v>TECNOLOGIA MECANICA INDUSTRIAL</x:v>
+      </x:c>
+      <x:c r="F35" s="8" t="str">
+        <x:v>0923622476</x:v>
+      </x:c>
+      <x:c r="G35" s="4" t="str">
+        <x:v>VILLAMARIN PINO</x:v>
+      </x:c>
+      <x:c r="H35" s="4" t="str">
+        <x:v>JORGE ALFREDO</x:v>
+      </x:c>
+      <x:c r="I35" s="4" t="str">
+        <x:v>jvillamarinp@ups.edu.ec</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11367,19 +11540,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>TELECOMUNICACIONES</x:v>
+        <x:v>TEOLOGIA MODALIDAD EN LINEA</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>0919123067</x:v>
+        <x:v>1102375019</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>CORDOVA LEON</x:v>
+        <x:v>CONZA BARBA</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>JOSE RENATO</x:v>
+        <x:v>RAUL ANTONIO</x:v>
       </x:c>
       <x:c r="I11" s="4" t="str">
-        <x:v>jcordova@ups.edu.ec</x:v>
+        <x:v>rconza@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
@@ -11396,19 +11569,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+        <x:v>TELECOMUNICACIONES</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>0916656408</x:v>
+        <x:v>0919123067</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>DELGADO FIGUEROA</x:v>
+        <x:v>CORDOVA LEON</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>STELLA PAOLA</x:v>
+        <x:v>JOSE RENATO</x:v>
       </x:c>
       <x:c r="I12" s="4" t="str">
-        <x:v>sdelgadof@ups.edu.ec</x:v>
+        <x:v>jcordova@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
@@ -11425,19 +11598,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>TELECOMUNICACIONES</x:v>
+        <x:v>ELECTRICIDAD</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>0916893357</x:v>
+        <x:v>0953330818</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>ECHEVERRIA AVILA</x:v>
+        <x:v>DECIMAVILLA MICHILENA</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>PABLO FABIAN</x:v>
+        <x:v>LORENA ELIZABETH</x:v>
       </x:c>
       <x:c r="I13" s="4" t="str">
-        <x:v>pecheverria@ups.edu.ec</x:v>
+        <x:v>ldecimavilla@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
@@ -11454,19 +11627,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>0803025493</x:v>
+        <x:v>0916656408</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>ESPINOSA CASTRO</x:v>
+        <x:v>DELGADO FIGUEROA</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>JENNIFER ALEXANDRA</x:v>
+        <x:v>STELLA PAOLA</x:v>
       </x:c>
       <x:c r="I14" s="4" t="str">
-        <x:v>jespinosac@ups.edu.ec</x:v>
+        <x:v>sdelgadof@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
@@ -11483,19 +11656,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>TELECOMUNICACIONES</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>0931689749</x:v>
+        <x:v>0916893357</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>EVANGELISTA CASTRO</x:v>
+        <x:v>ECHEVERRIA AVILA</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>NELLY BEATRIZ</x:v>
+        <x:v>PABLO FABIAN</x:v>
       </x:c>
       <x:c r="I15" s="4" t="str">
-        <x:v>nevangelista@ups.edu.ec</x:v>
+        <x:v>pecheverria@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
@@ -11512,19 +11685,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>COMUNICACION SOCIAL</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>1205726456</x:v>
+        <x:v>0803025493</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>FLORES PERALTA</x:v>
+        <x:v>ESPINOSA CASTRO</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>JUANA KATIUSCA</x:v>
+        <x:v>JENNIFER ALEXANDRA</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>jfloresp@ups.edu.ec</x:v>
+        <x:v>jespinosac@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
@@ -11541,19 +11714,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>INGENIERIA AMBIENTAL</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>0606165033</x:v>
+        <x:v>0931689749</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>GUEVARA VINZA</x:v>
+        <x:v>EVANGELISTA CASTRO</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>LUIS MIGUEL</x:v>
+        <x:v>NELLY BEATRIZ</x:v>
       </x:c>
       <x:c r="I17" s="4" t="str">
-        <x:v>lguevara@ups.edu.ec</x:v>
+        <x:v>nevangelista@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
@@ -11570,19 +11743,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>PSICOLOGIA</x:v>
+        <x:v>COMUNICACION SOCIAL</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
-        <x:v>1205707894</x:v>
+        <x:v>1205726456</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>HIDALGO SOTOMAYOR</x:v>
+        <x:v>FLORES PERALTA</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>DARWIN ANDRES</x:v>
+        <x:v>JUANA KATIUSCA</x:v>
       </x:c>
       <x:c r="I18" s="4" t="str">
-        <x:v>dhidalgo@ups.edu.ec</x:v>
+        <x:v>jfloresp@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
@@ -11599,19 +11772,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>DISEÑO MULTIMEDIA</x:v>
+        <x:v>INGENIERIA AMBIENTAL</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>0927400747</x:v>
+        <x:v>0606165033</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>LOPEZ RUIZ</x:v>
+        <x:v>GUEVARA VINZA</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>GILDA NOELIA</x:v>
+        <x:v>LUIS MIGUEL</x:v>
       </x:c>
       <x:c r="I19" s="4" t="str">
-        <x:v>glopez@ups.edu.ec</x:v>
+        <x:v>lguevara@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -11628,19 +11801,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>INSTITUTO DE IDIOMAS</x:v>
+        <x:v>PSICOLOGIA</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>0914286042</x:v>
+        <x:v>1205707894</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>MACIAS CHANG</x:v>
+        <x:v>HIDALGO SOTOMAYOR</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>MARIA BEATRIZ</x:v>
+        <x:v>DARWIN ANDRES</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>mmacias@ups.edu.ec</x:v>
+        <x:v>dhidalgo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
@@ -11657,19 +11830,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>DISEÑO MULTIMEDIA</x:v>
       </x:c>
       <x:c r="F21" s="8" t="str">
-        <x:v>0603117300</x:v>
+        <x:v>0927400747</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>MORAN REYES</x:v>
+        <x:v>LOPEZ RUIZ</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>LUIS ENRIQUE</x:v>
+        <x:v>GILDA NOELIA</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>lmoran@ups.edu.ec</x:v>
+        <x:v>glopez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
@@ -11686,19 +11859,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>INSTITUTO DE IDIOMAS</x:v>
       </x:c>
       <x:c r="F22" s="8" t="str">
-        <x:v>0916522444</x:v>
+        <x:v>0914286042</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>ORTIZ ROJAS</x:v>
+        <x:v>MACIAS CHANG</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>JAVIER GONZALO</x:v>
+        <x:v>MARIA BEATRIZ</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>jortiz@ups.edu.ec</x:v>
+        <x:v>mmacias@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
@@ -11715,19 +11888,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>INGENIERIA CIVIL</x:v>
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>0914565148</x:v>
+        <x:v>0603117300</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>PEÑA MONTOYA</x:v>
+        <x:v>MORAN REYES</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>PEDRO GERARDO</x:v>
+        <x:v>LUIS ENRIQUE</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>ppena@ups.edu.ec</x:v>
+        <x:v>lmoran@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -11744,19 +11917,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>DISEÑO MULTIMEDIA</x:v>
       </x:c>
       <x:c r="F24" s="8" t="str">
-        <x:v>1714540299</x:v>
+        <x:v>0932256951</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>RECALDE ZUMARRAGA</x:v>
+        <x:v>OLAYA ROJAS</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>CAMILA FERNANDA</x:v>
+        <x:v>JOHNSON CRISTOPHER</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>crecalde@ups.edu.ec</x:v>
+        <x:v>jolaya@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
@@ -11773,19 +11946,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F25" s="8" t="str">
-        <x:v>0910952571</x:v>
+        <x:v>0916522444</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>SANCHEZ IÑIGUEZ</x:v>
+        <x:v>ORTIZ ROJAS</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>LUIS ALBERTO</x:v>
+        <x:v>JAVIER GONZALO</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>lsanchezi@ups.edu.ec</x:v>
+        <x:v>jortiz@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -11802,19 +11975,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>EDUCACION INICIAL</x:v>
+        <x:v>INGENIERIA CIVIL</x:v>
       </x:c>
       <x:c r="F26" s="8" t="str">
-        <x:v>0102128857</x:v>
+        <x:v>0914565148</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>SANMARTIN GARCIA</x:v>
+        <x:v>PEÑA MONTOYA</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>ROMULO IGNACIO</x:v>
+        <x:v>PEDRO GERARDO</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>rsanmartin@ups.edu.ec</x:v>
+        <x:v>ppena@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
@@ -11831,19 +12004,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F27" s="8" t="str">
-        <x:v>1500748288</x:v>
+        <x:v>1714540299</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>TAPUY BENAVIDES</x:v>
+        <x:v>RECALDE ZUMARRAGA</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>DANNY PABLO</x:v>
+        <x:v>CAMILA FERNANDA</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>dtapuy@ups.edu.ec</x:v>
+        <x:v>crecalde@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
@@ -11860,18 +12033,20 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>Por confirmar</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F28" s="8" t="str">
-        <x:v>0916862170</x:v>
+        <x:v>0910952571</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>TOMALA CALDERON</x:v>
+        <x:v>SANCHEZ IÑIGUEZ</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>BYRONE MAURICIO</x:v>
-      </x:c>
-      <x:c r="I28" s="4"/>
+        <x:v>LUIS ALBERTO</x:v>
+      </x:c>
+      <x:c r="I28" s="4" t="str">
+        <x:v>lsanchezi@ups.edu.ec</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
       <x:c r="A29" s="9" t="n">
@@ -11887,19 +12062,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>BIOTECNOLOGIA</x:v>
+        <x:v>EDUCACION INICIAL</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>0105841217</x:v>
+        <x:v>0102128857</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>ULLOA HERAS</x:v>
+        <x:v>SANMARTIN GARCIA</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>CAROLINA ISABEL</x:v>
+        <x:v>ROMULO IGNACIO</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>culloah@ups.edu.ec</x:v>
+        <x:v>rsanmartin@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
@@ -11916,19 +12091,19 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>MECATRONICA</x:v>
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>0910678614</x:v>
+        <x:v>1500748288</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>VERA FIGUEROA</x:v>
+        <x:v>TAPUY BENAVIDES</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>JUAN PABLO</x:v>
+        <x:v>DANNY PABLO</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>jveraf@ups.edu.ec</x:v>
+        <x:v>dtapuy@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
@@ -11945,20 +12120,18 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>NEGOCIOS DIGITALES</x:v>
+        <x:v>Por confirmar</x:v>
       </x:c>
       <x:c r="F31" s="8" t="str">
-        <x:v>1204142937</x:v>
+        <x:v>0916862170</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>VILLACRES BELTRAN</x:v>
+        <x:v>TOMALA CALDERON</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>FABIAN ISAAC</x:v>
-      </x:c>
-      <x:c r="I31" s="4" t="str">
-        <x:v>fvillacres@ups.edu.ec</x:v>
-      </x:c>
+        <x:v>BYRONE MAURICIO</x:v>
+      </x:c>
+      <x:c r="I31" s="4"/>
     </x:row>
     <x:row r="32" ht="48" customHeight="1">
       <x:c r="A32" s="9" t="n">
@@ -11974,18 +12147,105 @@
         <x:v>Aula D208</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
+        <x:v>BIOTECNOLOGIA</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="str">
+        <x:v>0105841217</x:v>
+      </x:c>
+      <x:c r="G32" s="4" t="str">
+        <x:v>ULLOA HERAS</x:v>
+      </x:c>
+      <x:c r="H32" s="4" t="str">
+        <x:v>CAROLINA ISABEL</x:v>
+      </x:c>
+      <x:c r="I32" s="4" t="str">
+        <x:v>culloah@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="48" customHeight="1">
+      <x:c r="A33" s="9" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B33" s="9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="str">
+        <x:v>LOPEZ ULLOA BRENDA PATRICIA</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>Aula D208</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>MECATRONICA</x:v>
+      </x:c>
+      <x:c r="F33" s="8" t="str">
+        <x:v>0910678614</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>VERA FIGUEROA</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>JUAN PABLO</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>jveraf@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="A34" s="9" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="str">
+        <x:v>LOPEZ ULLOA BRENDA PATRICIA</x:v>
+      </x:c>
+      <x:c r="D34" s="4" t="str">
+        <x:v>Aula D208</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="str">
         <x:v>NEGOCIOS DIGITALES</x:v>
       </x:c>
-      <x:c r="F32" s="8" t="str">
+      <x:c r="F34" s="8" t="str">
+        <x:v>1204142937</x:v>
+      </x:c>
+      <x:c r="G34" s="4" t="str">
+        <x:v>VILLACRES BELTRAN</x:v>
+      </x:c>
+      <x:c r="H34" s="4" t="str">
+        <x:v>FABIAN ISAAC</x:v>
+      </x:c>
+      <x:c r="I34" s="4" t="str">
+        <x:v>fvillacres@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="9" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B35" s="9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="str">
+        <x:v>LOPEZ ULLOA BRENDA PATRICIA</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>Aula D208</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
+        <x:v>NEGOCIOS DIGITALES</x:v>
+      </x:c>
+      <x:c r="F35" s="8" t="str">
         <x:v>1103515902</x:v>
       </x:c>
-      <x:c r="G32" s="4" t="str">
+      <x:c r="G35" s="4" t="str">
         <x:v>YAGUANA HERRERA</x:v>
       </x:c>
-      <x:c r="H32" s="4" t="str">
+      <x:c r="H35" s="4" t="str">
         <x:v>TANIA GUADALUPE</x:v>
       </x:c>
-      <x:c r="I32" s="4" t="str">
+      <x:c r="I35" s="4" t="str">
         <x:v>tyaguana@ups.edu.ec</x:v>
       </x:c>
     </x:row>
@@ -12303,19 +12563,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>DIRECCION TECNICA DE PASTORAL</x:v>
+        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>0918119660</x:v>
+        <x:v>0916168784</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>DONOSO NOBOA</x:v>
+        <x:v>DEFAS RUGEL</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>ALBA GENOVEVA</x:v>
+        <x:v>DAVID ENRIQUE</x:v>
       </x:c>
       <x:c r="I11" s="4" t="str">
-        <x:v>adonoson@ups.edu.ec</x:v>
+        <x:v>ddefas@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
@@ -12332,19 +12592,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>DIRECCION TECNICA DE PLANEACION EVALUACION Y ACREDITACION</x:v>
+        <x:v>DIRECCION TECNICA DE PASTORAL</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>0915611537</x:v>
+        <x:v>0918119660</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>FRANCO CEDEÑO</x:v>
+        <x:v>DONOSO NOBOA</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>ERCILIA MARIA</x:v>
+        <x:v>ALBA GENOVEVA</x:v>
       </x:c>
       <x:c r="I12" s="4" t="str">
-        <x:v>efranco@ups.edu.ec</x:v>
+        <x:v>adonoson@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
@@ -12361,19 +12621,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>DIRECCION TECNICA DE PLANEACION EVALUACION Y ACREDITACION</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>0923328629</x:v>
+        <x:v>0915611537</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>FRANCO REINA</x:v>
+        <x:v>FRANCO CEDEÑO</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>RAFAEL CHRISTIAN</x:v>
+        <x:v>ERCILIA MARIA</x:v>
       </x:c>
       <x:c r="I13" s="4" t="str">
-        <x:v>rfranco@ups.edu.ec</x:v>
+        <x:v>efranco@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
@@ -12390,19 +12650,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>INSTITUTO DE IDIOMAS</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>0915336945</x:v>
+        <x:v>0923328629</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>HERRERA LOZANO</x:v>
+        <x:v>FRANCO REINA</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>SILVANA MARICELA</x:v>
+        <x:v>RAFAEL CHRISTIAN</x:v>
       </x:c>
       <x:c r="I14" s="4" t="str">
-        <x:v>sherrera@ups.edu.ec</x:v>
+        <x:v>rfranco@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
@@ -12419,19 +12679,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>INSTITUTO DE IDIOMAS</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>0926684325</x:v>
+        <x:v>0915336945</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>IZQUIERDO ORTEGA</x:v>
+        <x:v>HERRERA LOZANO</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>DENISSE</x:v>
+        <x:v>SILVANA MARICELA</x:v>
       </x:c>
       <x:c r="I15" s="4" t="str">
-        <x:v>dizquierdo@ups.edu.ec</x:v>
+        <x:v>sherrera@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
@@ -12448,19 +12708,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>INSTITUTO DE IDIOMAS</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>0920521127</x:v>
+        <x:v>0930846951</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>JIMENEZ CONTRERAS</x:v>
+        <x:v>HIDALGO QUILLIGANA</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>JOHNNY JOSE</x:v>
+        <x:v>DOMENICA ISABEL</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>jjimenez@ups.edu.ec</x:v>
+        <x:v>dhidalgoq@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
@@ -12477,19 +12737,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>EDUCACION INICIAL</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>0918018946</x:v>
+        <x:v>0926684325</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>JOSE REYES</x:v>
+        <x:v>IZQUIERDO ORTEGA</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>ALDANA RUTH</x:v>
+        <x:v>DENISSE</x:v>
       </x:c>
       <x:c r="I17" s="4" t="str">
-        <x:v>ajose@ups.edu.ec</x:v>
+        <x:v>dizquierdo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
@@ -12509,16 +12769,16 @@
         <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
-        <x:v>0911047058</x:v>
+        <x:v>0920521127</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>LEON VEAS</x:v>
+        <x:v>JIMENEZ CONTRERAS</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>JOFFRE LUIS</x:v>
+        <x:v>JOHNNY JOSE</x:v>
       </x:c>
       <x:c r="I18" s="4" t="str">
-        <x:v>jleon@ups.edu.ec</x:v>
+        <x:v>jjimenez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
@@ -12535,19 +12795,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>EDUCACION INICIAL</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>0909020679</x:v>
+        <x:v>0918018946</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>LLAGUNO VERA</x:v>
+        <x:v>JOSE REYES</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>JORGE GREGORIO</x:v>
+        <x:v>ALDANA RUTH</x:v>
       </x:c>
       <x:c r="I19" s="4" t="str">
-        <x:v>jllaguno@ups.edu.ec</x:v>
+        <x:v>ajose@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -12564,19 +12824,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>0912034790</x:v>
+        <x:v>0911047058</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>LOPEZ VARGAS</x:v>
+        <x:v>LEON VEAS</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>ARMANDO FABRIZZIO</x:v>
+        <x:v>JOFFRE LUIS</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>alopez@ups.edu.ec</x:v>
+        <x:v>jleon@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
@@ -12593,19 +12853,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>INSTITUTO DE IDIOMAS</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F21" s="8" t="str">
-        <x:v>0919915439</x:v>
+        <x:v>0909020679</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>MOREIRA CEREZO</x:v>
+        <x:v>LLAGUNO VERA</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>JOHANNA ELENA</x:v>
+        <x:v>JORGE GREGORIO</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>jmoreira@ups.edu.ec</x:v>
+        <x:v>jllaguno@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
@@ -12622,19 +12882,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>INGENIERIA AMBIENTAL</x:v>
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F22" s="8" t="str">
-        <x:v>0909780850</x:v>
+        <x:v>0912034790</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>ORDOÑEZ RAMIREZ</x:v>
+        <x:v>LOPEZ VARGAS</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>VIRGILIO ALONSO</x:v>
+        <x:v>ARMANDO FABRIZZIO</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>vordonezr@ups.edu.ec</x:v>
+        <x:v>alopez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
@@ -12651,19 +12911,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>EDUCACION INICIAL</x:v>
+        <x:v>DIRECCION TECNICA DE PASTORAL</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>0922440458</x:v>
+        <x:v>0201229523</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>ORMAZA ORMAZA</x:v>
+        <x:v>MANTILLA BOSQUEZ</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>HILDA INES</x:v>
+        <x:v>ANGEL VICENTE</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>hormaza@ups.edu.ec</x:v>
+        <x:v>amantilla@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -12680,19 +12940,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>INSTITUTO DE IDIOMAS</x:v>
       </x:c>
       <x:c r="F24" s="8" t="str">
-        <x:v>0916113426</x:v>
+        <x:v>0919915439</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>PEÑARANDA IDROVO</x:v>
+        <x:v>MOREIRA CEREZO</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>VICENTE AVELINO</x:v>
+        <x:v>JOHANNA ELENA</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>vpenaranda@ups.edu.ec</x:v>
+        <x:v>jmoreira@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
@@ -12709,19 +12969,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>INGENIERIA AMBIENTAL</x:v>
       </x:c>
       <x:c r="F25" s="8" t="str">
-        <x:v>0920382785</x:v>
+        <x:v>0909780850</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>PLUA MORAN</x:v>
+        <x:v>ORDOÑEZ RAMIREZ</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>DANIEL HUMBERTO</x:v>
+        <x:v>VIRGILIO ALONSO</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>dplua@ups.edu.ec</x:v>
+        <x:v>vordonezr@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -12738,19 +12998,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+        <x:v>EDUCACION INICIAL</x:v>
       </x:c>
       <x:c r="F26" s="8" t="str">
-        <x:v>0919998914</x:v>
+        <x:v>0922440458</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>PROAÑO CHACHA</x:v>
+        <x:v>ORMAZA ORMAZA</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>SONNIA ALEXANDRA</x:v>
+        <x:v>HILDA INES</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>sproano@ups.edu.ec</x:v>
+        <x:v>hormaza@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
@@ -12767,19 +13027,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>FISIOTERAPIA</x:v>
+        <x:v>COORDINACIÓN DE DESARROLLO ACADÉMICO</x:v>
       </x:c>
       <x:c r="F27" s="8" t="str">
-        <x:v>1757712839</x:v>
+        <x:v>0602579948</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>SANTAELLA PALMA</x:v>
+        <x:v>PARRA ROSERO</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>LUIS EDUARDO</x:v>
+        <x:v>PABLO GERMÁN</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>lsantaella@ups.edu.ec</x:v>
+        <x:v>pparra@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
@@ -12796,19 +13056,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>ELECTRICIDAD</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F28" s="8" t="str">
-        <x:v>0916303134</x:v>
+        <x:v>0916113426</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>SANTILLAN CARRANZA</x:v>
+        <x:v>PEÑARANDA IDROVO</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>HOLGER JORGE</x:v>
+        <x:v>VICENTE AVELINO</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>hsantillan@ups.edu.ec</x:v>
+        <x:v>vpenaranda@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
@@ -12825,19 +13085,19 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>MECATRONICA</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>0950992305</x:v>
+        <x:v>0920382785</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>SANTOS TERAN</x:v>
+        <x:v>PLUA MORAN</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>JOSE MIGUEL</x:v>
+        <x:v>DANIEL HUMBERTO</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>jsantost@ups.edu.ec</x:v>
+        <x:v>dplua@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
@@ -12857,16 +13117,16 @@
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>0921972592</x:v>
+        <x:v>0919998914</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>SUMBA NACIPUCHA</x:v>
+        <x:v>PROAÑO CHACHA</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>NICOLAS ARMANDO</x:v>
+        <x:v>SONNIA ALEXANDRA</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>nsumba@ups.edu.ec</x:v>
+        <x:v>sproano@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
@@ -12883,928 +13143,135 @@
         <x:v>Aula D209</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
+        <x:v>FISIOTERAPIA</x:v>
+      </x:c>
+      <x:c r="F31" s="8" t="str">
+        <x:v>1757712839</x:v>
+      </x:c>
+      <x:c r="G31" s="4" t="str">
+        <x:v>SANTAELLA PALMA</x:v>
+      </x:c>
+      <x:c r="H31" s="4" t="str">
+        <x:v>LUIS EDUARDO</x:v>
+      </x:c>
+      <x:c r="I31" s="4" t="str">
+        <x:v>lsantaella@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="48" customHeight="1">
+      <x:c r="A32" s="9" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B32" s="9" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C32" s="4" t="str">
+        <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
+      </x:c>
+      <x:c r="D32" s="4" t="str">
+        <x:v>Aula D209</x:v>
+      </x:c>
+      <x:c r="E32" s="4" t="str">
+        <x:v>ELECTRICIDAD</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="str">
+        <x:v>0916303134</x:v>
+      </x:c>
+      <x:c r="G32" s="4" t="str">
+        <x:v>SANTILLAN CARRANZA</x:v>
+      </x:c>
+      <x:c r="H32" s="4" t="str">
+        <x:v>HOLGER JORGE</x:v>
+      </x:c>
+      <x:c r="I32" s="4" t="str">
+        <x:v>hsantillan@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="48" customHeight="1">
+      <x:c r="A33" s="9" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B33" s="9" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="str">
+        <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>Aula D209</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>MECATRONICA</x:v>
+      </x:c>
+      <x:c r="F33" s="8" t="str">
+        <x:v>0950992305</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>SANTOS TERAN</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>JOSE MIGUEL</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>jsantost@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="A34" s="9" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="str">
+        <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
+      </x:c>
+      <x:c r="D34" s="4" t="str">
+        <x:v>Aula D209</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="str">
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+      </x:c>
+      <x:c r="F34" s="8" t="str">
+        <x:v>0921972592</x:v>
+      </x:c>
+      <x:c r="G34" s="4" t="str">
+        <x:v>SUMBA NACIPUCHA</x:v>
+      </x:c>
+      <x:c r="H34" s="4" t="str">
+        <x:v>NICOLAS ARMANDO</x:v>
+      </x:c>
+      <x:c r="I34" s="4" t="str">
+        <x:v>nsumba@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="9" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B35" s="9" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="str">
+        <x:v>FLORALBA DEL ROCIO AGUILAR GORDON</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>Aula D209</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
         <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
-      <x:c r="F31" s="8" t="str">
+      <x:c r="F35" s="8" t="str">
         <x:v>0917456998</x:v>
       </x:c>
-      <x:c r="G31" s="4" t="str">
+      <x:c r="G35" s="4" t="str">
         <x:v>TINGO SOLEDISPA</x:v>
       </x:c>
-      <x:c r="H31" s="4" t="str">
+      <x:c r="H35" s="4" t="str">
         <x:v>MARJORIE VERONICA</x:v>
       </x:c>
-      <x:c r="I31" s="4" t="str">
+      <x:c r="I35" s="4" t="str">
         <x:v>mtingo@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:I1"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:tabColor rgb="FF1F3864"/>
-  </x:sheetPr>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="9" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="39" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="27" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="29" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="31" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="52" customHeight="1">
-      <x:c r="A1" s="38" t="str">
-        <x:v>TALLERES 2, 3 Y 4 — Martes 13 y miércoles 14 de octubre (mañana) — Grupo 10 — Aula D211</x:v>
-      </x:c>
-      <x:c r="B1" s="38"/>
-      <x:c r="C1" s="38"/>
-      <x:c r="D1" s="38"/>
-      <x:c r="E1" s="38"/>
-      <x:c r="F1" s="38"/>
-      <x:c r="G1" s="38"/>
-      <x:c r="H1" s="38"/>
-      <x:c r="I1" s="38"/>
-    </x:row>
-    <x:row r="2" ht="38" customHeight="1">
-      <x:c r="A2" s="36" t="str">
-        <x:v>Nro.</x:v>
-      </x:c>
-      <x:c r="B2" s="36" t="str">
-        <x:v>GRUPO</x:v>
-      </x:c>
-      <x:c r="C2" s="36" t="str">
-        <x:v>Facilitador</x:v>
-      </x:c>
-      <x:c r="D2" s="36" t="str">
-        <x:v>Espacio Físico</x:v>
-      </x:c>
-      <x:c r="E2" s="36" t="str">
-        <x:v>Carrera / Unidad</x:v>
-      </x:c>
-      <x:c r="F2" s="36" t="str">
-        <x:v>Cédula</x:v>
-      </x:c>
-      <x:c r="G2" s="36" t="str">
-        <x:v>Apellidos</x:v>
-      </x:c>
-      <x:c r="H2" s="36" t="str">
-        <x:v>Nombres</x:v>
-      </x:c>
-      <x:c r="I2" s="36" t="str">
-        <x:v>Correo Institucional</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="48" customHeight="1">
-      <x:c r="A3" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D3" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E3" s="4" t="str">
-        <x:v>BIOMEDICINA</x:v>
-      </x:c>
-      <x:c r="F3" s="8" t="str">
-        <x:v>0912880028</x:v>
-      </x:c>
-      <x:c r="G3" s="4" t="str">
-        <x:v>AGUILERA SARRIA</x:v>
-      </x:c>
-      <x:c r="H3" s="4" t="str">
-        <x:v>CARLOS JONATHAN</x:v>
-      </x:c>
-      <x:c r="I3" s="4" t="str">
-        <x:v>caguilera@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="9" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B4" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>INGENIERIA AMBIENTAL</x:v>
-      </x:c>
-      <x:c r="F4" s="8" t="str">
-        <x:v>0919957316</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="str">
-        <x:v>ANDRADE DICAO</x:v>
-      </x:c>
-      <x:c r="H4" s="4" t="str">
-        <x:v>GABRIELA MICHELLE</x:v>
-      </x:c>
-      <x:c r="I4" s="4" t="str">
-        <x:v>gandrade@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B5" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
-      </x:c>
-      <x:c r="F5" s="8" t="str">
-        <x:v>0918282617</x:v>
-      </x:c>
-      <x:c r="G5" s="4" t="str">
-        <x:v>BALLADARES FIGUEROA</x:v>
-      </x:c>
-      <x:c r="H5" s="4" t="str">
-        <x:v>LUIS ALBERTO</x:v>
-      </x:c>
-      <x:c r="I5" s="4" t="str">
-        <x:v>lballadares@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B6" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D6" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E6" s="4" t="str">
-        <x:v>DERECHO</x:v>
-      </x:c>
-      <x:c r="F6" s="8" t="str">
-        <x:v>0930306477</x:v>
-      </x:c>
-      <x:c r="G6" s="4" t="str">
-        <x:v>BOHORQUEZ MORA</x:v>
-      </x:c>
-      <x:c r="H6" s="4" t="str">
-        <x:v>OSCAR KEVIN</x:v>
-      </x:c>
-      <x:c r="I6" s="4" t="str">
-        <x:v>obohorquez@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B7" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D7" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E7" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
-      </x:c>
-      <x:c r="F7" s="8" t="str">
-        <x:v>0917215956</x:v>
-      </x:c>
-      <x:c r="G7" s="4" t="str">
-        <x:v>BUSTAMANTE RUIZ</x:v>
-      </x:c>
-      <x:c r="H7" s="4" t="str">
-        <x:v>ORLANDO FERNANDO</x:v>
-      </x:c>
-      <x:c r="I7" s="4" t="str">
-        <x:v>obustamante@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="9" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B8" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D8" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E8" s="4" t="str">
-        <x:v>TECNOLOGIA ELECTRICIDAD INDUSTRIAL</x:v>
-      </x:c>
-      <x:c r="F8" s="8" t="str">
-        <x:v>0911477776</x:v>
-      </x:c>
-      <x:c r="G8" s="4" t="str">
-        <x:v>CACERES GALAN</x:v>
-      </x:c>
-      <x:c r="H8" s="4" t="str">
-        <x:v>CESAR ANTONIO</x:v>
-      </x:c>
-      <x:c r="I8" s="4" t="str">
-        <x:v>ccaceres@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="9" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B9" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E9" s="4" t="str">
-        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
-      </x:c>
-      <x:c r="F9" s="8" t="str">
-        <x:v>0202336749</x:v>
-      </x:c>
-      <x:c r="G9" s="4" t="str">
-        <x:v>CAMACHO VARGAS</x:v>
-      </x:c>
-      <x:c r="H9" s="4" t="str">
-        <x:v>JONNATHAN LEONARDO</x:v>
-      </x:c>
-      <x:c r="I9" s="4" t="str">
-        <x:v>jcamachov@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="9" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B10" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C10" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D10" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E10" s="4" t="str">
-        <x:v>TEOLOGIA MODALIDAD EN LINEA</x:v>
-      </x:c>
-      <x:c r="F10" s="8" t="str">
-        <x:v>1102375019</x:v>
-      </x:c>
-      <x:c r="G10" s="4" t="str">
-        <x:v>CONZA BARBA</x:v>
-      </x:c>
-      <x:c r="H10" s="4" t="str">
-        <x:v>RAUL ANTONIO</x:v>
-      </x:c>
-      <x:c r="I10" s="4" t="str">
-        <x:v>rconza@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="9" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B11" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D11" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E11" s="4" t="str">
-        <x:v>ELECTRICIDAD</x:v>
-      </x:c>
-      <x:c r="F11" s="8" t="str">
-        <x:v>0953330818</x:v>
-      </x:c>
-      <x:c r="G11" s="4" t="str">
-        <x:v>DECIMAVILLA MICHILENA</x:v>
-      </x:c>
-      <x:c r="H11" s="4" t="str">
-        <x:v>LORENA ELIZABETH</x:v>
-      </x:c>
-      <x:c r="I11" s="4" t="str">
-        <x:v>ldecimavilla@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B12" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D12" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E12" s="4" t="str">
-        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
-      </x:c>
-      <x:c r="F12" s="8" t="str">
-        <x:v>0916168784</x:v>
-      </x:c>
-      <x:c r="G12" s="4" t="str">
-        <x:v>DEFAS RUGEL</x:v>
-      </x:c>
-      <x:c r="H12" s="4" t="str">
-        <x:v>DAVID ENRIQUE</x:v>
-      </x:c>
-      <x:c r="I12" s="4" t="str">
-        <x:v>ddefas@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="9" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B13" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D13" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E13" s="4" t="str">
-        <x:v>DERECHO</x:v>
-      </x:c>
-      <x:c r="F13" s="8" t="str">
-        <x:v>0926648155</x:v>
-      </x:c>
-      <x:c r="G13" s="4" t="str">
-        <x:v>DIAZ VELEZ</x:v>
-      </x:c>
-      <x:c r="H13" s="4" t="str">
-        <x:v>CAROLINA ELIZABETH</x:v>
-      </x:c>
-      <x:c r="I13" s="4" t="str">
-        <x:v>cdiazv@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="48" customHeight="1">
-      <x:c r="A14" s="9" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B14" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C14" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D14" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E14" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
-      </x:c>
-      <x:c r="F14" s="8" t="str">
-        <x:v>0906680871</x:v>
-      </x:c>
-      <x:c r="G14" s="4" t="str">
-        <x:v>DOMINGUEZ COLOMA</x:v>
-      </x:c>
-      <x:c r="H14" s="4" t="str">
-        <x:v>PATRICIA MARIA DE LOURDES</x:v>
-      </x:c>
-      <x:c r="I14" s="4" t="str">
-        <x:v>pdominguez@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="48" customHeight="1">
-      <x:c r="A15" s="9" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B15" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C15" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D15" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E15" s="4" t="str">
-        <x:v>BIOMEDICINA</x:v>
-      </x:c>
-      <x:c r="F15" s="8" t="str">
-        <x:v>0912439486</x:v>
-      </x:c>
-      <x:c r="G15" s="4" t="str">
-        <x:v>GRUNAUER ESPINOZA</x:v>
-      </x:c>
-      <x:c r="H15" s="4" t="str">
-        <x:v>CECILIA CATALINA</x:v>
-      </x:c>
-      <x:c r="I15" s="4" t="str">
-        <x:v>cgrunauer@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="48" customHeight="1">
-      <x:c r="A16" s="9" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B16" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C16" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D16" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E16" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
-      </x:c>
-      <x:c r="F16" s="8" t="str">
-        <x:v>0917770737</x:v>
-      </x:c>
-      <x:c r="G16" s="4" t="str">
-        <x:v>GUERRA VILLALTA</x:v>
-      </x:c>
-      <x:c r="H16" s="4" t="str">
-        <x:v>CHRISTIAN ENRIQUE</x:v>
-      </x:c>
-      <x:c r="I16" s="4" t="str">
-        <x:v>cguerra@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="48" customHeight="1">
-      <x:c r="A17" s="9" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B17" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C17" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D17" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E17" s="4" t="str">
-        <x:v>PSICOLOGIA</x:v>
-      </x:c>
-      <x:c r="F17" s="8" t="str">
-        <x:v>0920200821</x:v>
-      </x:c>
-      <x:c r="G17" s="4" t="str">
-        <x:v>GUZÑAY VENTURA</x:v>
-      </x:c>
-      <x:c r="H17" s="4" t="str">
-        <x:v>ANGEL MILTON</x:v>
-      </x:c>
-      <x:c r="I17" s="4" t="str">
-        <x:v>aguznay@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="48" customHeight="1">
-      <x:c r="A18" s="9" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B18" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C18" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D18" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E18" s="4" t="str">
-        <x:v>INSTITUTO DE IDIOMAS</x:v>
-      </x:c>
-      <x:c r="F18" s="8" t="str">
-        <x:v>0930846951</x:v>
-      </x:c>
-      <x:c r="G18" s="4" t="str">
-        <x:v>HIDALGO QUILLIGANA</x:v>
-      </x:c>
-      <x:c r="H18" s="4" t="str">
-        <x:v>DOMENICA ISABEL</x:v>
-      </x:c>
-      <x:c r="I18" s="4" t="str">
-        <x:v>dhidalgoq@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="48" customHeight="1">
-      <x:c r="A19" s="9" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B19" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C19" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D19" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E19" s="4" t="str">
-        <x:v>DIRECCION TECNICA DE PASTORAL</x:v>
-      </x:c>
-      <x:c r="F19" s="8" t="str">
-        <x:v>0201229523</x:v>
-      </x:c>
-      <x:c r="G19" s="4" t="str">
-        <x:v>MANTILLA BOSQUEZ</x:v>
-      </x:c>
-      <x:c r="H19" s="4" t="str">
-        <x:v>ANGEL VICENTE</x:v>
-      </x:c>
-      <x:c r="I19" s="4" t="str">
-        <x:v>amantilla@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="48" customHeight="1">
-      <x:c r="A20" s="9" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B20" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C20" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D20" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E20" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
-      </x:c>
-      <x:c r="F20" s="8" t="str">
-        <x:v>0930054432</x:v>
-      </x:c>
-      <x:c r="G20" s="4" t="str">
-        <x:v>MARTINEZ FIGUEROA</x:v>
-      </x:c>
-      <x:c r="H20" s="4" t="str">
-        <x:v>JUAN PABLO</x:v>
-      </x:c>
-      <x:c r="I20" s="4" t="str">
-        <x:v>jmartinezf@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="48" customHeight="1">
-      <x:c r="A21" s="9" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B21" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C21" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D21" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E21" s="4" t="str">
-        <x:v>DISEÑO MULTIMEDIA</x:v>
-      </x:c>
-      <x:c r="F21" s="8" t="str">
-        <x:v>0932256951</x:v>
-      </x:c>
-      <x:c r="G21" s="4" t="str">
-        <x:v>OLAYA ROJAS</x:v>
-      </x:c>
-      <x:c r="H21" s="4" t="str">
-        <x:v>JOHNSON CRISTOPHER</x:v>
-      </x:c>
-      <x:c r="I21" s="4" t="str">
-        <x:v>jolaya@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="48" customHeight="1">
-      <x:c r="A22" s="9" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B22" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C22" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D22" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E22" s="4" t="str">
-        <x:v>COORDINACIÓN DE DESARROLLO ACADÉMICO</x:v>
-      </x:c>
-      <x:c r="F22" s="8" t="str">
-        <x:v>0602579948</x:v>
-      </x:c>
-      <x:c r="G22" s="4" t="str">
-        <x:v>PARRA ROSERO</x:v>
-      </x:c>
-      <x:c r="H22" s="4" t="str">
-        <x:v>PABLO GERMÁN</x:v>
-      </x:c>
-      <x:c r="I22" s="4" t="str">
-        <x:v>pparra@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="48" customHeight="1">
-      <x:c r="A23" s="9" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B23" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C23" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D23" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E23" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
-      </x:c>
-      <x:c r="F23" s="8" t="str">
-        <x:v>0920565066</x:v>
-      </x:c>
-      <x:c r="G23" s="4" t="str">
-        <x:v>PIZARRO VASQUEZ</x:v>
-      </x:c>
-      <x:c r="H23" s="4" t="str">
-        <x:v>GUILLERMO OMAR</x:v>
-      </x:c>
-      <x:c r="I23" s="4" t="str">
-        <x:v>gpizarro@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="48" customHeight="1">
-      <x:c r="A24" s="9" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B24" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C24" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D24" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E24" s="4" t="str">
-        <x:v>EDUCACION INICIAL</x:v>
-      </x:c>
-      <x:c r="F24" s="8" t="str">
-        <x:v>0912155652</x:v>
-      </x:c>
-      <x:c r="G24" s="4" t="str">
-        <x:v>POMBO BERMEO</x:v>
-      </x:c>
-      <x:c r="H24" s="4" t="str">
-        <x:v>ANGELICA SUSANA</x:v>
-      </x:c>
-      <x:c r="I24" s="4" t="str">
-        <x:v>apombo@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="48" customHeight="1">
-      <x:c r="A25" s="9" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B25" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C25" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D25" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E25" s="4" t="str">
-        <x:v>DISEÑO MULTIMEDIA</x:v>
-      </x:c>
-      <x:c r="F25" s="8" t="str">
-        <x:v>0926631573</x:v>
-      </x:c>
-      <x:c r="G25" s="4" t="str">
-        <x:v>PORTUGAL GOROZABEL</x:v>
-      </x:c>
-      <x:c r="H25" s="4" t="str">
-        <x:v>JONATAN ANDRES</x:v>
-      </x:c>
-      <x:c r="I25" s="4" t="str">
-        <x:v>jportugal@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="48" customHeight="1">
-      <x:c r="A26" s="9" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B26" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C26" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D26" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E26" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
-      </x:c>
-      <x:c r="F26" s="8" t="str">
-        <x:v>0914817010</x:v>
-      </x:c>
-      <x:c r="G26" s="4" t="str">
-        <x:v>RODRIGUEZ QUINTANA</x:v>
-      </x:c>
-      <x:c r="H26" s="4" t="str">
-        <x:v>ROMULO EDUARDO</x:v>
-      </x:c>
-      <x:c r="I26" s="4" t="str">
-        <x:v>rrodriguez@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="48" customHeight="1">
-      <x:c r="A27" s="9" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B27" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C27" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D27" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E27" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
-      </x:c>
-      <x:c r="F27" s="8" t="str">
-        <x:v>0924149081</x:v>
-      </x:c>
-      <x:c r="G27" s="4" t="str">
-        <x:v>SUASNAVAS MERINO</x:v>
-      </x:c>
-      <x:c r="H27" s="4" t="str">
-        <x:v>KATHERINE MELISSA</x:v>
-      </x:c>
-      <x:c r="I27" s="4" t="str">
-        <x:v>ksuasnavas@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="48" customHeight="1">
-      <x:c r="A28" s="9" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B28" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C28" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D28" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E28" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
-      </x:c>
-      <x:c r="F28" s="8" t="str">
-        <x:v>0914759576</x:v>
-      </x:c>
-      <x:c r="G28" s="4" t="str">
-        <x:v>TEJADA ESCOBAR</x:v>
-      </x:c>
-      <x:c r="H28" s="4" t="str">
-        <x:v>FREDDY JAVIER</x:v>
-      </x:c>
-      <x:c r="I28" s="4" t="str">
-        <x:v>ftejada@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="48" customHeight="1">
-      <x:c r="A29" s="9" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B29" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C29" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D29" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E29" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
-      </x:c>
-      <x:c r="F29" s="8" t="str">
-        <x:v>1705290128</x:v>
-      </x:c>
-      <x:c r="G29" s="4" t="str">
-        <x:v>VALLADARES CARRILLO</x:v>
-      </x:c>
-      <x:c r="H29" s="4" t="str">
-        <x:v>ALVARO MANUEL</x:v>
-      </x:c>
-      <x:c r="I29" s="4" t="str">
-        <x:v>avalladares@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="48" customHeight="1">
-      <x:c r="A30" s="9" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B30" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C30" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D30" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E30" s="4" t="str">
-        <x:v>DISEÑO MULTIMEDIA</x:v>
-      </x:c>
-      <x:c r="F30" s="8" t="str">
-        <x:v>0916155112</x:v>
-      </x:c>
-      <x:c r="G30" s="4" t="str">
-        <x:v>VELOZ ARCE</x:v>
-      </x:c>
-      <x:c r="H30" s="4" t="str">
-        <x:v>ALONSO EDUARDO</x:v>
-      </x:c>
-      <x:c r="I30" s="4" t="str">
-        <x:v>aveloz@ups.edu.ec</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="48" customHeight="1">
-      <x:c r="A31" s="9" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B31" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C31" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="D31" s="4" t="str">
-        <x:v>Aula D211</x:v>
-      </x:c>
-      <x:c r="E31" s="4" t="str">
-        <x:v>TECNOLOGIA MECANICA INDUSTRIAL</x:v>
-      </x:c>
-      <x:c r="F31" s="8" t="str">
-        <x:v>0923622476</x:v>
-      </x:c>
-      <x:c r="G31" s="4" t="str">
-        <x:v>VILLAMARIN PINO</x:v>
-      </x:c>
-      <x:c r="H31" s="4" t="str">
-        <x:v>JORGE ALFREDO</x:v>
-      </x:c>
-      <x:c r="I31" s="4" t="str">
-        <x:v>jvillamarinp@ups.edu.ec</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -18254,7 +17721,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 3 - Aula D203
 T5 y T6: Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
@@ -18452,7 +17919,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D12" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 1 - Aula D201
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
@@ -18760,7 +18227,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D26" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 6 - Aula D206
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
@@ -19046,7 +18513,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D39" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 4 - Aula D204
 T5 y T6: Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="E39" s="4" t="str">
@@ -19112,7 +18579,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D42" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 1 - Aula D201
 T5 y T6: Grupo 5 - Aula D204</x:v>
       </x:c>
       <x:c r="E42" s="4" t="str">
@@ -19200,7 +18667,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D46" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 5 - Aula D205
 T5 y T6: Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="E46" s="4" t="str">
@@ -19222,7 +18689,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D47" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 2 - Aula D202
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E47" s="4" t="str">
@@ -19794,7 +19261,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D73" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 8 - Aula D208
 T5 y T6: Grupo 7 - Aula D206</x:v>
       </x:c>
       <x:c r="E73" s="4" t="str">
@@ -19992,7 +19459,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D82" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 8 - Aula D208
 T5 y T6: Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="E82" s="4" t="str">
@@ -20014,7 +19481,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D83" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 9 - Aula D209
 T5 y T6: Grupo 1 - Aula D209</x:v>
       </x:c>
       <x:c r="E83" s="4" t="str">
@@ -20146,7 +19613,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D89" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 3 - Aula D203
 T5 y T6: Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="E89" s="4" t="str">
@@ -20168,7 +19635,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D90" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 6 - Aula D206
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E90" s="4" t="str">
@@ -20850,7 +20317,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D121" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 1 - Aula D201
 T5 y T6: Grupo 3 - Aula D202</x:v>
       </x:c>
       <x:c r="E121" s="4" t="str">
@@ -20916,7 +20383,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D124" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 7 - Aula D207
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E124" s="4" t="str">
@@ -20960,7 +20427,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D126" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 2 - Aula D202
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E126" s="4" t="str">
@@ -21026,7 +20493,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D129" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 9 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E129" s="4" t="str">
@@ -21862,7 +21329,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D167" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 9 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E167" s="4" t="str">
@@ -21906,7 +21373,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D169" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 5 - Aula D205
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E169" s="4" t="str">
@@ -22346,7 +21813,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D189" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 8 - Aula D208
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E189" s="4" t="str">
@@ -22588,7 +22055,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D200" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 9 - Aula D209
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E200" s="4" t="str">
@@ -22720,7 +22187,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D206" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 7 - Aula D207
 T5 y T6: Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="E206" s="4" t="str">
@@ -22786,7 +22253,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D209" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 6 - Aula D206
 T5 y T6: Grupo 6 - Aula D205</x:v>
       </x:c>
       <x:c r="E209" s="4" t="str">
@@ -22808,7 +22275,7 @@
 T5 y T6: RESP. AREA CONOC. SEDE</x:v>
       </x:c>
       <x:c r="D210" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 1 - Aula D201
 T5 y T6: Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="E210" s="4" t="str">
@@ -23314,7 +22781,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D233" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 3 - Aula D203
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E233" s="4" t="str">
@@ -23864,7 +23331,7 @@
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="D258" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 5 - Aula D205
 T5 y T6: No Convocado</x:v>
       </x:c>
       <x:c r="E258" s="4" t="str">
@@ -23952,7 +23419,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D262" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 4 - Aula D204
 T5 y T6: Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="E262" s="4" t="str">
@@ -24368,7 +23835,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D281" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 2 - Aula D202
 T5 y T6: Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="E281" s="4" t="str">
@@ -24478,7 +23945,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D286" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 4 - Aula D204
 T5 y T6: Grupo 2 - Aula D201</x:v>
       </x:c>
       <x:c r="E286" s="4" t="str">
@@ -24610,7 +24077,7 @@
 T5 y T6: PARTICIPANTE</x:v>
       </x:c>
       <x:c r="D292" s="4" t="str">
-        <x:v>T4: Grupo 10 - Aula D211
+        <x:v>T4: Grupo 7 - Aula D207
 T5 y T6: Grupo 4 - Aula D203</x:v>
       </x:c>
       <x:c r="E292" s="4" t="str">
@@ -33778,7 +33245,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str">
-        <x:v>Martes y miércoles por la mañana: talleres 2, 3 y 4 con una nueva distribución aleatoria de 10 grupos.</x:v>
+        <x:v>Martes y miércoles por la mañana: talleres 2, 3 y 4 con la misma distribución aleatoria de 9 grupos.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="45" customHeight="1">
@@ -33793,7 +33260,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str">
-        <x:v>Los 298 participantes se distribuyen en 8 grupos de 30 personas y 2 grupos de 29.</x:v>
+        <x:v>Los 298 participantes se distribuyen en un grupo de 34 personas y ocho grupos de 33.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="45" customHeight="1">
@@ -33808,7 +33275,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str">
-        <x:v>Aulas para los talleres 2, 3 y 4: D201 a D209 y D211. El facilitador del aula D211 queda por confirmar.</x:v>
+        <x:v>Aulas para los talleres 2, 3 y 4: D201 a D209.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="45" customHeight="1">
@@ -33908,7 +33375,7 @@
       </x:c>
       <x:c r="C16" s="32" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A16)</x:f>
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E16" s="24" t="str">
         <x:v>Estructura y formato de referencia: Grupos_66.xlsx. Se reemplazó el listado de Quito.</x:v>
@@ -33923,7 +33390,7 @@
       </x:c>
       <x:c r="C17" s="32" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A17)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E17" s="24" t="str">
         <x:v>Fechas y horarios: Agenda_Jornadas_Capacitacion_Docente_Periodo_69_2026_ACTUALIZADA_2.pdf.</x:v>
@@ -33938,7 +33405,7 @@
       </x:c>
       <x:c r="C18" s="32" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A18)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E18" s="24" t="str">
         <x:v>Taller 6 (15 oct.): 09h40 - 10h50; 11h20 - 12h30; 16h00 - 18h00.</x:v>
@@ -33953,10 +33420,10 @@
       </x:c>
       <x:c r="C19" s="32" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A19)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E19" s="24" t="str">
-        <x:v>Agrupación: lunes con los grupos originales; martes y miércoles por la mañana con los mismos 10 grupos nuevos.</x:v>
+        <x:v>Agrupación: lunes con los grupos originales; martes y miércoles por la mañana con los mismos 9 grupos aleatorios.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="65" customHeight="1">
@@ -33968,7 +33435,7 @@
       </x:c>
       <x:c r="C20" s="32" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A20)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E20" s="24" t="str">
         <x:v>Directores: se cruzaron CARGO y DIRECTOR_CARRERA. La hoja Directores carrera conserva la convocatoria original.</x:v>
@@ -33983,7 +33450,7 @@
       </x:c>
       <x:c r="C21" s="32" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A21)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E21" s="24" t="str">
         <x:v>Alicia María Cedeño Tello y Karol Leonor Chávez González: directoras confirmadas por el organizador, convocadas en Educación y Ciencias de la Vida / Salud.</x:v>
@@ -33998,7 +33465,7 @@
       </x:c>
       <x:c r="C22" s="32" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A22)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="65" customHeight="1">
@@ -34010,7 +33477,7 @@
       </x:c>
       <x:c r="C23" s="32" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A23)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="65" customHeight="1">
@@ -34022,30 +33489,23 @@
       </x:c>
       <x:c r="C24" s="32" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A24)</x:f>
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="65" customHeight="1">
-      <x:c r="A25" s="31" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
-      </x:c>
-      <x:c r="B25" s="31" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="C25" s="32" t="n">
-        <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A25)</x:f>
-        <x:v>29</x:v>
+      <x:c r="A25" s="13" t="str">
+        <x:v>TOTAL TALLERES 2, 3 Y 4</x:v>
+      </x:c>
+      <x:c r="B25" s="13"/>
+      <x:c r="C25" s="19" t="n">
+        <x:f>SUM(C16:C24)</x:f>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="13" t="str">
-        <x:v>TOTAL TALLERES 2, 3 Y 4</x:v>
-      </x:c>
-      <x:c r="B26" s="13"/>
-      <x:c r="C26" s="19" t="n">
-        <x:f>SUM(C16:C25)</x:f>
-        <x:v>298</x:v>
-      </x:c>
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -37371,7 +36831,7 @@
   <x:sheetData>
     <x:row r="1" ht="52" customHeight="1">
       <x:c r="A1" s="38" t="str">
-        <x:v>TALLERES 2, 3 Y 4 — Martes y miércoles por la mañana — 10 grupos aleatorios</x:v>
+        <x:v>TALLERES 2, 3 Y 4 — Martes y miércoles por la mañana — 9 grupos aleatorios</x:v>
       </x:c>
       <x:c r="B1" s="38"/>
       <x:c r="C1" s="38"/>
@@ -37404,7 +36864,7 @@
       </x:c>
       <x:c r="C3" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A3)</x:f>
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
         <x:v>Martes 13 y miércoles 14 (mañana)</x:v>
@@ -37422,7 +36882,7 @@
       </x:c>
       <x:c r="C4" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A4)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
         <x:v>Martes 13 y miércoles 14 (mañana)</x:v>
@@ -37440,7 +36900,7 @@
       </x:c>
       <x:c r="C5" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A5)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
         <x:v>Martes 13 y miércoles 14 (mañana)</x:v>
@@ -37458,7 +36918,7 @@
       </x:c>
       <x:c r="C6" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A6)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
         <x:v>Martes 13 y miércoles 14 (mañana)</x:v>
@@ -37476,7 +36936,7 @@
       </x:c>
       <x:c r="C7" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A7)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
         <x:v>Martes 13 y miércoles 14 (mañana)</x:v>
@@ -37494,7 +36954,7 @@
       </x:c>
       <x:c r="C8" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A8)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
         <x:v>Martes 13 y miércoles 14 (mañana)</x:v>
@@ -37512,7 +36972,7 @@
       </x:c>
       <x:c r="C9" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A9)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
         <x:v>Martes 13 y miércoles 14 (mañana)</x:v>
@@ -37530,7 +36990,7 @@
       </x:c>
       <x:c r="C10" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A10)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
         <x:v>Martes 13 y miércoles 14 (mañana)</x:v>
@@ -37548,7 +37008,7 @@
       </x:c>
       <x:c r="C11" s="14" t="n">
         <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A11)</x:f>
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
         <x:v>Martes 13 y miércoles 14 (mañana)</x:v>
@@ -37558,34 +37018,23 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="4" t="str">
-        <x:v>Grupo 10 - Aula D211</x:v>
-      </x:c>
-      <x:c r="B12" s="4" t="str">
-        <x:v>Por confirmar</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="n">
-        <x:f>COUNTIFS('Convocatoria'!$E$2:$E$299,A12)</x:f>
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D12" s="4" t="str">
-        <x:v>Martes 13 y miércoles 14 (mañana)</x:v>
-      </x:c>
-      <x:c r="E12" s="4" t="str">
-        <x:v>2, 3 y 4</x:v>
-      </x:c>
+      <x:c r="A12" s="25" t="str">
+        <x:v>TOTAL</x:v>
+      </x:c>
+      <x:c r="B12" s="25"/>
+      <x:c r="C12" s="26" t="n">
+        <x:f>SUM(C3:C11)</x:f>
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="D12" s="25"/>
+      <x:c r="E12" s="25"/>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="25" t="str">
-        <x:v>TOTAL</x:v>
-      </x:c>
-      <x:c r="B13" s="25"/>
-      <x:c r="C13" s="26" t="n">
-        <x:f>SUM(C3:C12)</x:f>
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="D13" s="25"/>
-      <x:c r="E13" s="25"/>
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -37756,19 +37205,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
-        <x:v>COMUNICACION SOCIAL</x:v>
+        <x:v>INGENIERIA AMBIENTAL</x:v>
       </x:c>
       <x:c r="F6" s="8" t="str">
-        <x:v>0920008240</x:v>
+        <x:v>0919957316</x:v>
       </x:c>
       <x:c r="G6" s="4" t="str">
-        <x:v>ARANA MITE</x:v>
+        <x:v>ANDRADE DICAO</x:v>
       </x:c>
       <x:c r="H6" s="4" t="str">
-        <x:v>BISMARCK ALBERTO</x:v>
+        <x:v>GABRIELA MICHELLE</x:v>
       </x:c>
       <x:c r="I6" s="4" t="str">
-        <x:v>barana@ups.edu.ec</x:v>
+        <x:v>gandrade@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
@@ -37785,19 +37234,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+        <x:v>COMUNICACION SOCIAL</x:v>
       </x:c>
       <x:c r="F7" s="8" t="str">
-        <x:v>0910621465</x:v>
+        <x:v>0920008240</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
-        <x:v>BASTIDAS JIMENEZ</x:v>
+        <x:v>ARANA MITE</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>MARCELO JAVIER</x:v>
+        <x:v>BISMARCK ALBERTO</x:v>
       </x:c>
       <x:c r="I7" s="4" t="str">
-        <x:v>mbastidas@ups.edu.ec</x:v>
+        <x:v>barana@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
@@ -37817,16 +37266,16 @@
         <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str">
-        <x:v>0915371801</x:v>
+        <x:v>0910621465</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
-        <x:v>CARRERA JIMENEZ</x:v>
+        <x:v>BASTIDAS JIMENEZ</x:v>
       </x:c>
       <x:c r="H8" s="4" t="str">
-        <x:v>JAVIER ANTONIO</x:v>
+        <x:v>MARCELO JAVIER</x:v>
       </x:c>
       <x:c r="I8" s="4" t="str">
-        <x:v>jcarreraj@ups.edu.ec</x:v>
+        <x:v>mbastidas@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
@@ -37843,19 +37292,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>MECATRONICA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F9" s="8" t="str">
-        <x:v>0963020193</x:v>
+        <x:v>0917215956</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
-        <x:v>CORTEZ SARAVIA</x:v>
+        <x:v>BUSTAMANTE RUIZ</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>DAVID MATEO</x:v>
+        <x:v>ORLANDO FERNANDO</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
-        <x:v>dcortezs@ups.edu.ec</x:v>
+        <x:v>obustamante@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -37872,19 +37321,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str">
-        <x:v>1103588578</x:v>
+        <x:v>0915371801</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
-        <x:v>FIERRO JIMENEZ</x:v>
+        <x:v>CARRERA JIMENEZ</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>PABLO RENATO</x:v>
+        <x:v>JAVIER ANTONIO</x:v>
       </x:c>
       <x:c r="I10" s="4" t="str">
-        <x:v>pfierro@ups.edu.ec</x:v>
+        <x:v>jcarreraj@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
@@ -37901,19 +37350,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>ECONOMIA</x:v>
+        <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>0908973308</x:v>
+        <x:v>0963020193</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>FREIRE MORAN</x:v>
+        <x:v>CORTEZ SARAVIA</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>JORGE FABRICIO</x:v>
+        <x:v>DAVID MATEO</x:v>
       </x:c>
       <x:c r="I11" s="4" t="str">
-        <x:v>jfreirem@ups.edu.ec</x:v>
+        <x:v>dcortezs@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
@@ -37930,19 +37379,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>ELECTRICIDAD</x:v>
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>0301791893</x:v>
+        <x:v>1103588578</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>LATA GARCIA</x:v>
+        <x:v>FIERRO JIMENEZ</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>JUAN CARLOS</x:v>
+        <x:v>PABLO RENATO</x:v>
       </x:c>
       <x:c r="I12" s="4" t="str">
-        <x:v>jlatag@ups.edu.ec</x:v>
+        <x:v>pfierro@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
@@ -37959,19 +37408,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+        <x:v>ECONOMIA</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>0920827276</x:v>
+        <x:v>0908973308</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>LOPEZ CHILA</x:v>
+        <x:v>FREIRE MORAN</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>ROBERTO DAVID</x:v>
+        <x:v>JORGE FABRICIO</x:v>
       </x:c>
       <x:c r="I13" s="4" t="str">
-        <x:v>rlopezch@ups.edu.ec</x:v>
+        <x:v>jfreirem@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
@@ -37988,19 +37437,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+        <x:v>BIOMEDICINA</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>0919280511</x:v>
+        <x:v>0912439486</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>LOZANO CASTILLO</x:v>
+        <x:v>GRUNAUER ESPINOZA</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>AURORA NELLY</x:v>
+        <x:v>CECILIA CATALINA</x:v>
       </x:c>
       <x:c r="I14" s="4" t="str">
-        <x:v>alozano@ups.edu.ec</x:v>
+        <x:v>cgrunauer@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
@@ -38017,19 +37466,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>INSTITUTO DE IDIOMAS</x:v>
+        <x:v>ELECTRICIDAD</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>0923038236</x:v>
+        <x:v>0301791893</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>MALDONADO CARRANZA</x:v>
+        <x:v>LATA GARCIA</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>MARIA GABRIELA</x:v>
+        <x:v>JUAN CARLOS</x:v>
       </x:c>
       <x:c r="I15" s="4" t="str">
-        <x:v>mmaldonadoc@ups.edu.ec</x:v>
+        <x:v>jlatag@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
@@ -38046,19 +37495,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>DERECHO</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>0911023406</x:v>
+        <x:v>0920827276</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>MOREIRA ARGUDO</x:v>
+        <x:v>LOPEZ CHILA</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>MARCOS FRANCISCO</x:v>
+        <x:v>ROBERTO DAVID</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>mmoreiraa@ups.edu.ec</x:v>
+        <x:v>rlopezch@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
@@ -38075,19 +37524,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>0912419611</x:v>
+        <x:v>0919280511</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>NEGRETE PEÑA</x:v>
+        <x:v>LOZANO CASTILLO</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>TEDDY JHENNSE</x:v>
+        <x:v>AURORA NELLY</x:v>
       </x:c>
       <x:c r="I17" s="4" t="str">
-        <x:v>tnegrete@ups.edu.ec</x:v>
+        <x:v>alozano@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
@@ -38104,19 +37553,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>INSTITUTO DE IDIOMAS</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
-        <x:v>0920160371</x:v>
+        <x:v>0923038236</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>PRECIADO MAILA</x:v>
+        <x:v>MALDONADO CARRANZA</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>OLGA LISET</x:v>
+        <x:v>MARIA GABRIELA</x:v>
       </x:c>
       <x:c r="I18" s="4" t="str">
-        <x:v>opreciado@ups.edu.ec</x:v>
+        <x:v>mmaldonadoc@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
@@ -38133,19 +37582,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>BIOTECNOLOGIA</x:v>
+        <x:v>DERECHO</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>0602420911</x:v>
+        <x:v>0911023406</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>PULGAR OLEAS</x:v>
+        <x:v>MOREIRA ARGUDO</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>NELLY LORENA</x:v>
+        <x:v>MARCOS FRANCISCO</x:v>
       </x:c>
       <x:c r="I19" s="4" t="str">
-        <x:v>npulgaro@ups.edu.ec</x:v>
+        <x:v>mmoreiraa@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -38162,19 +37611,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>MAESTRIA EN ANALITICA DE DATOS</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>0922799655</x:v>
+        <x:v>0912419611</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>QUIROZ MARTINEZ</x:v>
+        <x:v>NEGRETE PEÑA</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>MIGUEL ANGEL</x:v>
+        <x:v>TEDDY JHENNSE</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>mquiroz@ups.edu.ec</x:v>
+        <x:v>tnegrete@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
@@ -38191,19 +37640,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>DISEÑO MULTIMEDIA</x:v>
       </x:c>
       <x:c r="F21" s="8" t="str">
-        <x:v>0917494890</x:v>
+        <x:v>0926631573</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>RIVAS ORDOÑEZ</x:v>
+        <x:v>PORTUGAL GOROZABEL</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>VIVIANA MARIA</x:v>
+        <x:v>JONATAN ANDRES</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>vrivaso@ups.edu.ec</x:v>
+        <x:v>jportugal@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
@@ -38220,19 +37669,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F22" s="8" t="str">
-        <x:v>1206221572</x:v>
+        <x:v>0920160371</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>ROJAS LITARDO</x:v>
+        <x:v>PRECIADO MAILA</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>KENNEL JOSE</x:v>
+        <x:v>OLGA LISET</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>krojas@ups.edu.ec</x:v>
+        <x:v>opreciado@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
@@ -38249,19 +37698,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+        <x:v>BIOTECNOLOGIA</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>0909661472</x:v>
+        <x:v>0602420911</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>SALAZAR OJEDA</x:v>
+        <x:v>PULGAR OLEAS</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>EDGAR XAVIER</x:v>
+        <x:v>NELLY LORENA</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>esalazar@ups.edu.ec</x:v>
+        <x:v>npulgaro@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -38278,19 +37727,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>FISIOTERAPIA</x:v>
+        <x:v>MAESTRIA EN ANALITICA DE DATOS</x:v>
       </x:c>
       <x:c r="F24" s="8" t="str">
-        <x:v>1719094540</x:v>
+        <x:v>0922799655</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>SANCHEZ ZARSOSA</x:v>
+        <x:v>QUIROZ MARTINEZ</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>ANDREA LIZETH</x:v>
+        <x:v>MIGUEL ANGEL</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>asanchezz@ups.edu.ec</x:v>
+        <x:v>mquiroz@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
@@ -38310,16 +37759,16 @@
         <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F25" s="8" t="str">
-        <x:v>0928668508</x:v>
+        <x:v>0917494890</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>SANTANA CHUNGA</x:v>
+        <x:v>RIVAS ORDOÑEZ</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>SUSY SCHERING</x:v>
+        <x:v>VIVIANA MARIA</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>ssantana@ups.edu.ec</x:v>
+        <x:v>vrivaso@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -38336,19 +37785,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F26" s="8" t="str">
-        <x:v>0924194889</x:v>
+        <x:v>1206221572</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>SESME CAJO</x:v>
+        <x:v>ROJAS LITARDO</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>CINTHYA BEATRIZ</x:v>
+        <x:v>KENNEL JOSE</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>csesme@ups.edu.ec</x:v>
+        <x:v>krojas@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
@@ -38365,19 +37814,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>ELECTRICIDAD</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F27" s="8" t="str">
-        <x:v>0923481915</x:v>
+        <x:v>0909661472</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>SOLANO VILLEGAS</x:v>
+        <x:v>SALAZAR OJEDA</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>ERVIN GEOVANNY</x:v>
+        <x:v>EDGAR XAVIER</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>esolano@ups.edu.ec</x:v>
+        <x:v>esalazar@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
@@ -38394,19 +37843,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>FISIOTERAPIA</x:v>
       </x:c>
       <x:c r="F28" s="8" t="str">
-        <x:v>1104090756</x:v>
+        <x:v>1719094540</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>TORRES ROMERO</x:v>
+        <x:v>SANCHEZ ZARSOSA</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>ALEXANDER EMANUEL</x:v>
+        <x:v>ANDREA LIZETH</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>atorresr@ups.edu.ec</x:v>
+        <x:v>asanchezz@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
@@ -38423,19 +37872,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>INSTITUTO DE IDIOMAS</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>0919372524</x:v>
+        <x:v>0928668508</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>VASCO MUÑOZ</x:v>
+        <x:v>SANTANA CHUNGA</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>JESSICA ISABEL</x:v>
+        <x:v>SUSY SCHERING</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>jvasco@ups.edu.ec</x:v>
+        <x:v>ssantana@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
@@ -38452,19 +37901,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>0924287097</x:v>
+        <x:v>0924194889</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>VERA SANTISTEVAN</x:v>
+        <x:v>SESME CAJO</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>VICTOR PATRICIO</x:v>
+        <x:v>CINTHYA BEATRIZ</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>vvera@ups.edu.ec</x:v>
+        <x:v>csesme@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
@@ -38481,19 +37930,19 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
+        <x:v>ELECTRICIDAD</x:v>
       </x:c>
       <x:c r="F31" s="8" t="str">
-        <x:v>0910867407</x:v>
+        <x:v>0923481915</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>VITERI PALOMEQUE</x:v>
+        <x:v>SOLANO VILLEGAS</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>MARIA FERNANDA</x:v>
+        <x:v>ERVIN GEOVANNY</x:v>
       </x:c>
       <x:c r="I31" s="4" t="str">
-        <x:v>mviterip@ups.edu.ec</x:v>
+        <x:v>esolano@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="48" customHeight="1">
@@ -38510,18 +37959,134 @@
         <x:v>Aula D201</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="str">
+        <x:v>1104090756</x:v>
+      </x:c>
+      <x:c r="G32" s="4" t="str">
+        <x:v>TORRES ROMERO</x:v>
+      </x:c>
+      <x:c r="H32" s="4" t="str">
+        <x:v>ALEXANDER EMANUEL</x:v>
+      </x:c>
+      <x:c r="I32" s="4" t="str">
+        <x:v>atorresr@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="48" customHeight="1">
+      <x:c r="A33" s="9" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B33" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="str">
+        <x:v>FABIÁN LEONARDO CUESTA ASTUDILLO</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>Aula D201</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>INSTITUTO DE IDIOMAS</x:v>
+      </x:c>
+      <x:c r="F33" s="8" t="str">
+        <x:v>0919372524</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>VASCO MUÑOZ</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>JESSICA ISABEL</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>jvasco@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="A34" s="9" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="str">
+        <x:v>FABIÁN LEONARDO CUESTA ASTUDILLO</x:v>
+      </x:c>
+      <x:c r="D34" s="4" t="str">
+        <x:v>Aula D201</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
       </x:c>
-      <x:c r="F32" s="8" t="str">
+      <x:c r="F34" s="8" t="str">
+        <x:v>0924287097</x:v>
+      </x:c>
+      <x:c r="G34" s="4" t="str">
+        <x:v>VERA SANTISTEVAN</x:v>
+      </x:c>
+      <x:c r="H34" s="4" t="str">
+        <x:v>VICTOR PATRICIO</x:v>
+      </x:c>
+      <x:c r="I34" s="4" t="str">
+        <x:v>vvera@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="9" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B35" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="str">
+        <x:v>FABIÁN LEONARDO CUESTA ASTUDILLO</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>Aula D201</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
+        <x:v>ARQUITECTURA</x:v>
+      </x:c>
+      <x:c r="F35" s="8" t="str">
+        <x:v>0910867407</x:v>
+      </x:c>
+      <x:c r="G35" s="4" t="str">
+        <x:v>VITERI PALOMEQUE</x:v>
+      </x:c>
+      <x:c r="H35" s="4" t="str">
+        <x:v>MARIA FERNANDA</x:v>
+      </x:c>
+      <x:c r="I35" s="4" t="str">
+        <x:v>mviterip@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="48" customHeight="1">
+      <x:c r="A36" s="9" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B36" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C36" s="4" t="str">
+        <x:v>FABIÁN LEONARDO CUESTA ASTUDILLO</x:v>
+      </x:c>
+      <x:c r="D36" s="4" t="str">
+        <x:v>Aula D201</x:v>
+      </x:c>
+      <x:c r="E36" s="4" t="str">
+        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
+      </x:c>
+      <x:c r="F36" s="8" t="str">
         <x:v>0917375537</x:v>
       </x:c>
-      <x:c r="G32" s="4" t="str">
+      <x:c r="G36" s="4" t="str">
         <x:v>ZUÑIGA ALVARADO</x:v>
       </x:c>
-      <x:c r="H32" s="4" t="str">
+      <x:c r="H36" s="4" t="str">
         <x:v>MARIA ALEJANDRA</x:v>
       </x:c>
-      <x:c r="I32" s="4" t="str">
+      <x:c r="I36" s="4" t="str">
         <x:v>mzunigaa@ups.edu.ec</x:v>
       </x:c>
     </x:row>
@@ -38781,19 +38346,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>INGENIERIA CIVIL</x:v>
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F9" s="8" t="str">
-        <x:v>0930702444</x:v>
+        <x:v>0202336749</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
-        <x:v>CAMPOVERDE PEREZ</x:v>
+        <x:v>CAMACHO VARGAS</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>HECTOR ABEL</x:v>
+        <x:v>JONNATHAN LEONARDO</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
-        <x:v>hcampoverde@ups.edu.ec</x:v>
+        <x:v>jcamachov@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -38810,19 +38375,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>BIOQUIMICA Y FARMACIA</x:v>
+        <x:v>INGENIERIA CIVIL</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str">
-        <x:v>0931057756</x:v>
+        <x:v>0930702444</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
-        <x:v>CEDEÑO VINCES</x:v>
+        <x:v>CAMPOVERDE PEREZ</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>KEVIN GABRIEL</x:v>
+        <x:v>HECTOR ABEL</x:v>
       </x:c>
       <x:c r="I10" s="4" t="str">
-        <x:v>kcedeno@ups.edu.ec</x:v>
+        <x:v>hcampoverde@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
@@ -38839,19 +38404,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>INGENIERIA CIVIL</x:v>
+        <x:v>BIOQUIMICA Y FARMACIA</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>1204922544</x:v>
+        <x:v>0931057756</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>CHAVEZ OCAÑA</x:v>
+        <x:v>CEDEÑO VINCES</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>LINCON HUMBERTO</x:v>
+        <x:v>KEVIN GABRIEL</x:v>
       </x:c>
       <x:c r="I11" s="4" t="str">
-        <x:v>lchavez@ups.edu.ec</x:v>
+        <x:v>kcedeno@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
@@ -38868,19 +38433,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+        <x:v>INGENIERIA CIVIL</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>0503066284</x:v>
+        <x:v>1204922544</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>CHILIQUINGA GUANOPATIN</x:v>
+        <x:v>CHAVEZ OCAÑA</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>EDWIN OMAR</x:v>
+        <x:v>LINCON HUMBERTO</x:v>
       </x:c>
       <x:c r="I12" s="4" t="str">
-        <x:v>echiliquinga@ups.edu.ec</x:v>
+        <x:v>lchavez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
@@ -38897,19 +38462,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>ENFERMERIA</x:v>
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>1207725597</x:v>
+        <x:v>0503066284</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>DIAZ ARAUJO</x:v>
+        <x:v>CHILIQUINGA GUANOPATIN</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>PAULA JACQUELINE</x:v>
+        <x:v>EDWIN OMAR</x:v>
       </x:c>
       <x:c r="I13" s="4" t="str">
-        <x:v>pdiaz@ups.edu.ec</x:v>
+        <x:v>echiliquinga@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
@@ -38926,19 +38491,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>ENFERMERIA</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>0918581596</x:v>
+        <x:v>1207725597</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>FUENTES MIRANDA</x:v>
+        <x:v>DIAZ ARAUJO</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>RAFAEL FRANCISCO</x:v>
+        <x:v>PAULA JACQUELINE</x:v>
       </x:c>
       <x:c r="I14" s="4" t="str">
-        <x:v>rfuentes@ups.edu.ec</x:v>
+        <x:v>pdiaz@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
@@ -38955,19 +38520,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>MECATRONICA</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>0920256500</x:v>
+        <x:v>0918581596</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>GARCIA VASQUEZ</x:v>
+        <x:v>FUENTES MIRANDA</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>GABRIEL SANTIAGO</x:v>
+        <x:v>RAFAEL FRANCISCO</x:v>
       </x:c>
       <x:c r="I15" s="4" t="str">
-        <x:v>ggarciav@ups.edu.ec</x:v>
+        <x:v>rfuentes@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
@@ -38987,16 +38552,16 @@
         <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>1802792646</x:v>
+        <x:v>0920256500</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>GAVILANEZ GAMBOA</x:v>
+        <x:v>GARCIA VASQUEZ</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>TOMAS SANTIAGO</x:v>
+        <x:v>GABRIEL SANTIAGO</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>tgavilanez@ups.edu.ec</x:v>
+        <x:v>ggarciav@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
@@ -39013,19 +38578,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+        <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>0909736936</x:v>
+        <x:v>1802792646</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>IÑIGUEZ MAGALLANES</x:v>
+        <x:v>GAVILANEZ GAMBOA</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>HUGO FERNANDO</x:v>
+        <x:v>TOMAS SANTIAGO</x:v>
       </x:c>
       <x:c r="I17" s="4" t="str">
-        <x:v>hiniguez@ups.edu.ec</x:v>
+        <x:v>tgavilanez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
@@ -39042,19 +38607,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>MECATRONICA</x:v>
+        <x:v>PSICOLOGIA</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
-        <x:v>0909627432</x:v>
+        <x:v>0920200821</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>KUONQUI GAINZA</x:v>
+        <x:v>GUZÑAY VENTURA</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>FRANKLIN ILLICH</x:v>
+        <x:v>ANGEL MILTON</x:v>
       </x:c>
       <x:c r="I18" s="4" t="str">
-        <x:v>fkuonqui@ups.edu.ec</x:v>
+        <x:v>aguznay@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
@@ -39071,19 +38636,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>0923270136</x:v>
+        <x:v>0909736936</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>LARCO TORRES</x:v>
+        <x:v>IÑIGUEZ MAGALLANES</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>VICTOR DAVID</x:v>
+        <x:v>HUGO FERNANDO</x:v>
       </x:c>
       <x:c r="I19" s="4" t="str">
-        <x:v>vlarco@ups.edu.ec</x:v>
+        <x:v>hiniguez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -39100,19 +38665,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>INGENIERIA CIVIL</x:v>
+        <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>0704808625</x:v>
+        <x:v>0909627432</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>MACAS JARAMILLO</x:v>
+        <x:v>KUONQUI GAINZA</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>FABIAN ALBERTO</x:v>
+        <x:v>FRANKLIN ILLICH</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>fmacas@ups.edu.ec</x:v>
+        <x:v>fkuonqui@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
@@ -39129,19 +38694,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F21" s="8" t="str">
-        <x:v>1105738395</x:v>
+        <x:v>0923270136</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>MALDONADO ORTEGA</x:v>
+        <x:v>LARCO TORRES</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>JOSE LUIS</x:v>
+        <x:v>VICTOR DAVID</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>jmaldonadoo@ups.edu.ec</x:v>
+        <x:v>vlarco@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
@@ -39158,19 +38723,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>DIRECCION TECNICA DE PASTORAL</x:v>
+        <x:v>INGENIERIA CIVIL</x:v>
       </x:c>
       <x:c r="F22" s="8" t="str">
-        <x:v>0962943593</x:v>
+        <x:v>0704808625</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>MENDEZ REYES</x:v>
+        <x:v>MACAS JARAMILLO</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>JOHAN MANUEL</x:v>
+        <x:v>FABIAN ALBERTO</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>jmendezr@ups.edu.ec</x:v>
+        <x:v>fmacas@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
@@ -39187,19 +38752,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>0911169282</x:v>
+        <x:v>1105738395</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>RANGEL DONOSO</x:v>
+        <x:v>MALDONADO ORTEGA</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>FELIX ROBERTO</x:v>
+        <x:v>JOSE LUIS</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>frangel@ups.edu.ec</x:v>
+        <x:v>jmaldonadoo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -39216,19 +38781,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>MECATRONICA</x:v>
+        <x:v>DIRECCION TECNICA DE PASTORAL</x:v>
       </x:c>
       <x:c r="F24" s="8" t="str">
-        <x:v>0923848691</x:v>
+        <x:v>0962943593</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>REYES LOPEZ</x:v>
+        <x:v>MENDEZ REYES</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>CHRISTOPHER RUBEN</x:v>
+        <x:v>JOHAN MANUEL</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>creyesl@ups.edu.ec</x:v>
+        <x:v>jmendezr@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
@@ -39245,19 +38810,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F25" s="8" t="str">
-        <x:v>1315506590</x:v>
+        <x:v>0911169282</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>RUIZ FARFAN</x:v>
+        <x:v>RANGEL DONOSO</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>MARIA ALEJANDRA</x:v>
+        <x:v>FELIX ROBERTO</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>mruizf1@ups.edu.ec</x:v>
+        <x:v>frangel@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -39274,19 +38839,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F26" s="8" t="str">
-        <x:v>0966185225</x:v>
+        <x:v>0923848691</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>SANCHEZ ALMARAZ</x:v>
+        <x:v>REYES LOPEZ</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>FRANCISCO</x:v>
+        <x:v>CHRISTOPHER RUBEN</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>fsanchez@ups.edu.ec</x:v>
+        <x:v>creyesl@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
@@ -39303,19 +38868,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>ING. EN REDES INTELIGENTES Y CIBERSEGURIDAD</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F27" s="8" t="str">
-        <x:v>0914687165</x:v>
+        <x:v>1315506590</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>TINGO SOLEDISPA</x:v>
+        <x:v>RUIZ FARFAN</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>RAUL SEGUNDO</x:v>
+        <x:v>MARIA ALEJANDRA</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>rtingo@ups.edu.ec</x:v>
+        <x:v>mruizf1@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
@@ -39332,19 +38897,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>PSICOLOGIA</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F28" s="8" t="str">
-        <x:v>0912099355</x:v>
+        <x:v>0966185225</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>TORRES MEDINA</x:v>
+        <x:v>SANCHEZ ALMARAZ</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>CHRISTIAN JUAN</x:v>
+        <x:v>FRANCISCO</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>ctorres@ups.edu.ec</x:v>
+        <x:v>fsanchez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
@@ -39361,19 +38926,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+        <x:v>ING. EN REDES INTELIGENTES Y CIBERSEGURIDAD</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>1722909395</x:v>
+        <x:v>0914687165</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>TOTOY MONTERO</x:v>
+        <x:v>TINGO SOLEDISPA</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>PAUL HERNAN</x:v>
+        <x:v>RAUL SEGUNDO</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>ptotoy@ups.edu.ec</x:v>
+        <x:v>rtingo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
@@ -39390,19 +38955,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>PSICOLOGIA</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>0950594754</x:v>
+        <x:v>0912099355</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>TRIVIÑO BURBANO</x:v>
+        <x:v>TORRES MEDINA</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>MARIA VANESSA</x:v>
+        <x:v>CHRISTIAN JUAN</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>mtrivino@ups.edu.ec</x:v>
+        <x:v>ctorres@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
@@ -39419,19 +38984,19 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>BIOQUIMICA Y FARMACIA</x:v>
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F31" s="8" t="str">
-        <x:v>0202465365</x:v>
+        <x:v>1722909395</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>URREA CAMACHO</x:v>
+        <x:v>TOTOY MONTERO</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>KAREN JULISSA</x:v>
+        <x:v>PAUL HERNAN</x:v>
       </x:c>
       <x:c r="I31" s="4" t="str">
-        <x:v>kurrea@ups.edu.ec</x:v>
+        <x:v>ptotoy@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="48" customHeight="1">
@@ -39448,18 +39013,105 @@
         <x:v>Aula D202</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
+        <x:v>PSICOLOGIA CLINICA</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="str">
+        <x:v>0950594754</x:v>
+      </x:c>
+      <x:c r="G32" s="4" t="str">
+        <x:v>TRIVIÑO BURBANO</x:v>
+      </x:c>
+      <x:c r="H32" s="4" t="str">
+        <x:v>MARIA VANESSA</x:v>
+      </x:c>
+      <x:c r="I32" s="4" t="str">
+        <x:v>mtrivino@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="48" customHeight="1">
+      <x:c r="A33" s="9" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B33" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="str">
+        <x:v>ROMEL EDUARDO RODAS ORELLANA</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>Aula D202</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>BIOQUIMICA Y FARMACIA</x:v>
+      </x:c>
+      <x:c r="F33" s="8" t="str">
+        <x:v>0202465365</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>URREA CAMACHO</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>KAREN JULISSA</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>kurrea@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="A34" s="9" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="str">
+        <x:v>ROMEL EDUARDO RODAS ORELLANA</x:v>
+      </x:c>
+      <x:c r="D34" s="4" t="str">
+        <x:v>Aula D202</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="str">
+        <x:v>ARQUITECTURA</x:v>
+      </x:c>
+      <x:c r="F34" s="8" t="str">
+        <x:v>1705290128</x:v>
+      </x:c>
+      <x:c r="G34" s="4" t="str">
+        <x:v>VALLADARES CARRILLO</x:v>
+      </x:c>
+      <x:c r="H34" s="4" t="str">
+        <x:v>ALVARO MANUEL</x:v>
+      </x:c>
+      <x:c r="I34" s="4" t="str">
+        <x:v>avalladares@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="9" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B35" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="str">
+        <x:v>ROMEL EDUARDO RODAS ORELLANA</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>Aula D202</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
         <x:v>MECATRONICA</x:v>
       </x:c>
-      <x:c r="F32" s="8" t="str">
+      <x:c r="F35" s="8" t="str">
         <x:v>0801602160</x:v>
       </x:c>
-      <x:c r="G32" s="4" t="str">
+      <x:c r="G35" s="4" t="str">
         <x:v>VEGA URETA</x:v>
       </x:c>
-      <x:c r="H32" s="4" t="str">
+      <x:c r="H35" s="4" t="str">
         <x:v>NINO TELLO</x:v>
       </x:c>
-      <x:c r="I32" s="4" t="str">
+      <x:c r="I35" s="4" t="str">
         <x:v>nvega@ups.edu.ec</x:v>
       </x:c>
     </x:row>
@@ -39545,19 +39197,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
-        <x:v>EDUCACION INICIAL</x:v>
+        <x:v>BIOMEDICINA</x:v>
       </x:c>
       <x:c r="F3" s="8" t="str">
-        <x:v>0910750744</x:v>
+        <x:v>0912880028</x:v>
       </x:c>
       <x:c r="G3" s="4" t="str">
-        <x:v>ALENCASTRO CARRIEL</x:v>
+        <x:v>AGUILERA SARRIA</x:v>
       </x:c>
       <x:c r="H3" s="4" t="str">
-        <x:v>MONICA SANDRA</x:v>
+        <x:v>CARLOS JONATHAN</x:v>
       </x:c>
       <x:c r="I3" s="4" t="str">
-        <x:v>malencastro@ups.edu.ec</x:v>
+        <x:v>caguilera@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -39574,19 +39226,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+        <x:v>EDUCACION INICIAL</x:v>
       </x:c>
       <x:c r="F4" s="8" t="str">
-        <x:v>0909591208</x:v>
+        <x:v>0910750744</x:v>
       </x:c>
       <x:c r="G4" s="4" t="str">
-        <x:v>BALAS LEON</x:v>
+        <x:v>ALENCASTRO CARRIEL</x:v>
       </x:c>
       <x:c r="H4" s="4" t="str">
-        <x:v>JUAN EMILIO</x:v>
+        <x:v>MONICA SANDRA</x:v>
       </x:c>
       <x:c r="I4" s="4" t="str">
-        <x:v>jbalas@ups.edu.ec</x:v>
+        <x:v>malencastro@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
@@ -39603,19 +39255,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F5" s="8" t="str">
-        <x:v>0952645216</x:v>
+        <x:v>0909591208</x:v>
       </x:c>
       <x:c r="G5" s="4" t="str">
-        <x:v>BASANTES GARCIA</x:v>
+        <x:v>BALAS LEON</x:v>
       </x:c>
       <x:c r="H5" s="4" t="str">
-        <x:v>REBECA TAMARA</x:v>
+        <x:v>JUAN EMILIO</x:v>
       </x:c>
       <x:c r="I5" s="4" t="str">
-        <x:v>rbasantes@ups.edu.ec</x:v>
+        <x:v>jbalas@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
@@ -39632,19 +39284,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F6" s="8" t="str">
-        <x:v>0922618079</x:v>
+        <x:v>0952645216</x:v>
       </x:c>
       <x:c r="G6" s="4" t="str">
-        <x:v>CAAMAÑO GORDILLO</x:v>
+        <x:v>BASANTES GARCIA</x:v>
       </x:c>
       <x:c r="H6" s="4" t="str">
-        <x:v>LUIS DANIEL</x:v>
+        <x:v>REBECA TAMARA</x:v>
       </x:c>
       <x:c r="I6" s="4" t="str">
-        <x:v>lcaamano@ups.edu.ec</x:v>
+        <x:v>rbasantes@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
@@ -39661,19 +39313,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>TELECOMUNICACIONES</x:v>
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F7" s="8" t="str">
-        <x:v>1102293402</x:v>
+        <x:v>0922618079</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
-        <x:v>CARRION GORDILLO</x:v>
+        <x:v>CAAMAÑO GORDILLO</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>KLEVER FILIBERTO</x:v>
+        <x:v>LUIS DANIEL</x:v>
       </x:c>
       <x:c r="I7" s="4" t="str">
-        <x:v>kcarrion@ups.edu.ec</x:v>
+        <x:v>lcaamano@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
@@ -39690,19 +39342,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
-        <x:v>INSTITUTO DE IDIOMAS</x:v>
+        <x:v>TELECOMUNICACIONES</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str">
-        <x:v>0914861133</x:v>
+        <x:v>1102293402</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
-        <x:v>COBEÑA GUERRERO</x:v>
+        <x:v>CARRION GORDILLO</x:v>
       </x:c>
       <x:c r="H8" s="4" t="str">
-        <x:v>MIRIAN ELENA</x:v>
+        <x:v>KLEVER FILIBERTO</x:v>
       </x:c>
       <x:c r="I8" s="4" t="str">
-        <x:v>mcobena@ups.edu.ec</x:v>
+        <x:v>kcarrion@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
@@ -39719,19 +39371,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>DERECHO</x:v>
+        <x:v>INSTITUTO DE IDIOMAS</x:v>
       </x:c>
       <x:c r="F9" s="8" t="str">
-        <x:v>0924451461</x:v>
+        <x:v>0914861133</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
-        <x:v>DEL POZO VILLAMIL</x:v>
+        <x:v>COBEÑA GUERRERO</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>MARIA DE LOURDES</x:v>
+        <x:v>MIRIAN ELENA</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
-        <x:v>mdelpozo@ups.edu.ec</x:v>
+        <x:v>mcobena@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -39748,19 +39400,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>DERECHO</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str">
-        <x:v>0960030567</x:v>
+        <x:v>0924451461</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
-        <x:v>ESPINOSA GARCIA</x:v>
+        <x:v>DEL POZO VILLAMIL</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>MAYLEN</x:v>
+        <x:v>MARIA DE LOURDES</x:v>
       </x:c>
       <x:c r="I10" s="4" t="str">
-        <x:v>mespinosag@ups.edu.ec</x:v>
+        <x:v>mdelpozo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
@@ -39777,19 +39429,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>MAESTRIA EN GERENCIA TRIBUTARIA</x:v>
+        <x:v>DERECHO</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>0927011700</x:v>
+        <x:v>0926648155</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>ESPINOZA ROSERO</x:v>
+        <x:v>DIAZ VELEZ</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>GLORIA BELEN</x:v>
+        <x:v>CAROLINA ELIZABETH</x:v>
       </x:c>
       <x:c r="I11" s="4" t="str">
-        <x:v>gespinozar@ups.edu.ec</x:v>
+        <x:v>cdiazv@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
@@ -39806,19 +39458,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>EDUCACION INICIAL</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>0959611450</x:v>
+        <x:v>0960030567</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>GONZALEZ RIVERA</x:v>
+        <x:v>ESPINOSA GARCIA</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>PEDRO LUIS</x:v>
+        <x:v>MAYLEN</x:v>
       </x:c>
       <x:c r="I12" s="4" t="str">
-        <x:v>pgonzalezr@ups.edu.ec</x:v>
+        <x:v>mespinosag@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
@@ -39835,19 +39487,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+        <x:v>MAESTRIA EN GERENCIA TRIBUTARIA</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>0913523023</x:v>
+        <x:v>0927011700</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>HERRERA AVELLAN</x:v>
+        <x:v>ESPINOZA ROSERO</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>FRANCISCO JOSE</x:v>
+        <x:v>GLORIA BELEN</x:v>
       </x:c>
       <x:c r="I13" s="4" t="str">
-        <x:v>fherrera@ups.edu.ec</x:v>
+        <x:v>gespinozar@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
@@ -39864,19 +39516,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>EDUCACION INICIAL</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>0930941646</x:v>
+        <x:v>0959611450</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>IPIALES VASCONEZ</x:v>
+        <x:v>GONZALEZ RIVERA</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>MARLYS LISBETH</x:v>
+        <x:v>PEDRO LUIS</x:v>
       </x:c>
       <x:c r="I14" s="4" t="str">
-        <x:v>mipiales@ups.edu.ec</x:v>
+        <x:v>pgonzalezr@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
@@ -39893,19 +39545,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>DIRECCION TECNICA DE PASTORAL</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>1711743250</x:v>
+        <x:v>0913523023</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>IZA VILLACIS</x:v>
+        <x:v>HERRERA AVELLAN</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>VICTOR ADOLFO</x:v>
+        <x:v>FRANCISCO JOSE</x:v>
       </x:c>
       <x:c r="I15" s="4" t="str">
-        <x:v>viza@ups.edu.ec</x:v>
+        <x:v>fherrera@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
@@ -39922,19 +39574,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>1713338158</x:v>
+        <x:v>0930941646</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>JAIME CARRIEL</x:v>
+        <x:v>IPIALES VASCONEZ</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>JOSE ROBERTO</x:v>
+        <x:v>MARLYS LISBETH</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>jjaime@ups.edu.ec</x:v>
+        <x:v>mipiales@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
@@ -39951,19 +39603,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+        <x:v>DIRECCION TECNICA DE PASTORAL</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>0907881957</x:v>
+        <x:v>1711743250</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>JARA MOLINA</x:v>
+        <x:v>IZA VILLACIS</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>MIRIAM ROSARIO</x:v>
+        <x:v>VICTOR ADOLFO</x:v>
       </x:c>
       <x:c r="I17" s="4" t="str">
-        <x:v>mjaram@ups.edu.ec</x:v>
+        <x:v>viza@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
@@ -39980,19 +39632,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
-        <x:v>0930340112</x:v>
+        <x:v>1713338158</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>LARA MORALES</x:v>
+        <x:v>JAIME CARRIEL</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>CINDY JUDITH</x:v>
+        <x:v>JOSE ROBERTO</x:v>
       </x:c>
       <x:c r="I18" s="4" t="str">
-        <x:v>clara@ups.edu.ec</x:v>
+        <x:v>jjaime@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
@@ -40009,19 +39661,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>DIRECCION TECNICA DE VINCULACION CON LA SOCIEDAD</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>0910427962</x:v>
+        <x:v>0907881957</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>MARMOL CASTILLO</x:v>
+        <x:v>JARA MOLINA</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>MONICA CAROLINA</x:v>
+        <x:v>MIRIAM ROSARIO</x:v>
       </x:c>
       <x:c r="I19" s="4" t="str">
-        <x:v>mmarmol@ups.edu.ec</x:v>
+        <x:v>mjaram@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -40038,19 +39690,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>NEGOCIOS DIGITALES</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>0909237091</x:v>
+        <x:v>0930340112</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>MORENO DELGADO</x:v>
+        <x:v>LARA MORALES</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>JUAN PABLO</x:v>
+        <x:v>CINDY JUDITH</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>jmorenod@ups.edu.ec</x:v>
+        <x:v>clara@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
@@ -40067,19 +39719,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>DERECHO</x:v>
+        <x:v>DIRECCION TECNICA DE VINCULACION CON LA SOCIEDAD</x:v>
       </x:c>
       <x:c r="F21" s="8" t="str">
-        <x:v>0927079673</x:v>
+        <x:v>0910427962</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>NAVARRETE SANTANA</x:v>
+        <x:v>MARMOL CASTILLO</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>ALEX MICHAELL</x:v>
+        <x:v>MONICA CAROLINA</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>anavarretes@ups.edu.ec</x:v>
+        <x:v>mmarmol@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
@@ -40096,19 +39748,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>NEGOCIOS DIGITALES</x:v>
       </x:c>
       <x:c r="F22" s="8" t="str">
-        <x:v>0940441082</x:v>
+        <x:v>0909237091</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>PALMA DIAZ</x:v>
+        <x:v>MORENO DELGADO</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>BRYAN CARLOS</x:v>
+        <x:v>JUAN PABLO</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>bpalma@ups.edu.ec</x:v>
+        <x:v>jmorenod@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
@@ -40125,19 +39777,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
+        <x:v>DERECHO</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>0910390855</x:v>
+        <x:v>0927079673</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>PAREDES FLORIL</x:v>
+        <x:v>NAVARRETE SANTANA</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>PRISCILLA ROSSANA</x:v>
+        <x:v>ALEX MICHAELL</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>pparedes@ups.edu.ec</x:v>
+        <x:v>anavarretes@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -40154,19 +39806,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>TECNOLOGIA ELECTRICIDAD INDUSTRIAL</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F24" s="8" t="str">
-        <x:v>0930313614</x:v>
+        <x:v>0940441082</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>PEÑA MARISCAL</x:v>
+        <x:v>PALMA DIAZ</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>NILO ANDRES</x:v>
+        <x:v>BRYAN CARLOS</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>npena@ups.edu.ec</x:v>
+        <x:v>bpalma@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
@@ -40183,19 +39835,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
       </x:c>
       <x:c r="F25" s="8" t="str">
-        <x:v>0964920581</x:v>
+        <x:v>0910390855</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>PIÑA APONTE</x:v>
+        <x:v>PAREDES FLORIL</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>ENZO RAUL</x:v>
+        <x:v>PRISCILLA ROSSANA</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>epina@ups.edu.ec</x:v>
+        <x:v>pparedes@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -40212,19 +39864,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>ECONOMIA</x:v>
+        <x:v>TECNOLOGIA ELECTRICIDAD INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F26" s="8" t="str">
-        <x:v>0919240853</x:v>
+        <x:v>0930313614</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>POZO CARDOSO</x:v>
+        <x:v>PEÑA MARISCAL</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>SANTIAGO LEONARDO</x:v>
+        <x:v>NILO ANDRES</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>spozo@ups.edu.ec</x:v>
+        <x:v>npena@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
@@ -40241,19 +39893,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>INGENIERIA CIVIL</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F27" s="8" t="str">
-        <x:v>1205363326</x:v>
+        <x:v>0964920581</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>PROAÑO VISCARRA</x:v>
+        <x:v>PIÑA APONTE</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>KEVIN RICARDO</x:v>
+        <x:v>ENZO RAUL</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>kproano@ups.edu.ec</x:v>
+        <x:v>epina@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
@@ -40270,19 +39922,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>ECONOMIA</x:v>
       </x:c>
       <x:c r="F28" s="8" t="str">
-        <x:v>0917951048</x:v>
+        <x:v>0919240853</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>PUMA RODRIGUEZ</x:v>
+        <x:v>POZO CARDOSO</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>RUBEN ARMANDO</x:v>
+        <x:v>SANTIAGO LEONARDO</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>rpuma@ups.edu.ec</x:v>
+        <x:v>spozo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
@@ -40299,19 +39951,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>MECATRONICA</x:v>
+        <x:v>INGENIERIA CIVIL</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>0923348890</x:v>
+        <x:v>1205363326</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>RAMIREZ FARFAN</x:v>
+        <x:v>PROAÑO VISCARRA</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>ALBERTO SANTIAGO</x:v>
+        <x:v>KEVIN RICARDO</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>aramirezf@ups.edu.ec</x:v>
+        <x:v>kproano@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
@@ -40328,19 +39980,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>ELECTRICIDAD</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>0910972637</x:v>
+        <x:v>0917951048</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>SANTANA JARA</x:v>
+        <x:v>PUMA RODRIGUEZ</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>ROY FREDDY</x:v>
+        <x:v>RUBEN ARMANDO</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>rsantana@ups.edu.ec</x:v>
+        <x:v>rpuma@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
@@ -40357,19 +40009,19 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F31" s="8" t="str">
-        <x:v>0917242448</x:v>
+        <x:v>0923348890</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>TERAN ALVARADO</x:v>
+        <x:v>RAMIREZ FARFAN</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>ANA FABIOLA</x:v>
+        <x:v>ALBERTO SANTIAGO</x:v>
       </x:c>
       <x:c r="I31" s="4" t="str">
-        <x:v>ateran@ups.edu.ec</x:v>
+        <x:v>aramirezf@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="48" customHeight="1">
@@ -40386,18 +40038,105 @@
         <x:v>Aula D203</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="str">
+        <x:v>0914817010</x:v>
+      </x:c>
+      <x:c r="G32" s="4" t="str">
+        <x:v>RODRIGUEZ QUINTANA</x:v>
+      </x:c>
+      <x:c r="H32" s="4" t="str">
+        <x:v>ROMULO EDUARDO</x:v>
+      </x:c>
+      <x:c r="I32" s="4" t="str">
+        <x:v>rrodriguez@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="48" customHeight="1">
+      <x:c r="A33" s="9" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B33" s="9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="str">
+        <x:v>ELENA DEL ROCIO COYAGO CRUZ</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>Aula D203</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>ELECTRICIDAD</x:v>
+      </x:c>
+      <x:c r="F33" s="8" t="str">
+        <x:v>0910972637</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>SANTANA JARA</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>ROY FREDDY</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>rsantana@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="A34" s="9" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="str">
+        <x:v>ELENA DEL ROCIO COYAGO CRUZ</x:v>
+      </x:c>
+      <x:c r="D34" s="4" t="str">
+        <x:v>Aula D203</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="str">
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
+      </x:c>
+      <x:c r="F34" s="8" t="str">
+        <x:v>0917242448</x:v>
+      </x:c>
+      <x:c r="G34" s="4" t="str">
+        <x:v>TERAN ALVARADO</x:v>
+      </x:c>
+      <x:c r="H34" s="4" t="str">
+        <x:v>ANA FABIOLA</x:v>
+      </x:c>
+      <x:c r="I34" s="4" t="str">
+        <x:v>ateran@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="9" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B35" s="9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="str">
+        <x:v>ELENA DEL ROCIO COYAGO CRUZ</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>Aula D203</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
         <x:v>INSTITUTO DE IDIOMAS</x:v>
       </x:c>
-      <x:c r="F32" s="8" t="str">
+      <x:c r="F35" s="8" t="str">
         <x:v>0914394929</x:v>
       </x:c>
-      <x:c r="G32" s="4" t="str">
+      <x:c r="G35" s="4" t="str">
         <x:v>VINUEZA VASCONEZ</x:v>
       </x:c>
-      <x:c r="H32" s="4" t="str">
+      <x:c r="H35" s="4" t="str">
         <x:v>PATRICIA ALEXANDRA</x:v>
       </x:c>
-      <x:c r="I32" s="4" t="str">
+      <x:c r="I35" s="4" t="str">
         <x:v>pvinueza@ups.edu.ec</x:v>
       </x:c>
     </x:row>
@@ -40599,19 +40338,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
+        <x:v>DERECHO</x:v>
       </x:c>
       <x:c r="F7" s="8" t="str">
-        <x:v>0913868220</x:v>
+        <x:v>0930306477</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
-        <x:v>CHAVEZ PULLAS</x:v>
+        <x:v>BOHORQUEZ MORA</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>MARIA ALEXANDRA</x:v>
+        <x:v>OSCAR KEVIN</x:v>
       </x:c>
       <x:c r="I7" s="4" t="str">
-        <x:v>mchavez@ups.edu.ec</x:v>
+        <x:v>obohorquez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
@@ -40628,19 +40367,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
-        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
+        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str">
-        <x:v>0918835224</x:v>
+        <x:v>0913868220</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
-        <x:v>CUEVA ESTRADA</x:v>
+        <x:v>CHAVEZ PULLAS</x:v>
       </x:c>
       <x:c r="H8" s="4" t="str">
-        <x:v>JORGE MANUEL</x:v>
+        <x:v>MARIA ALEXANDRA</x:v>
       </x:c>
       <x:c r="I8" s="4" t="str">
-        <x:v>jcueva@ups.edu.ec</x:v>
+        <x:v>mchavez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
@@ -40657,19 +40396,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F9" s="8" t="str">
-        <x:v>0921267951</x:v>
+        <x:v>0918835224</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
-        <x:v>DURAN SOLORZANO</x:v>
+        <x:v>CUEVA ESTRADA</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>STEFANO ALEXANDER</x:v>
+        <x:v>JORGE MANUEL</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
-        <x:v>sduran@ups.edu.ec</x:v>
+        <x:v>jcueva@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -40686,19 +40425,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>MECATRONICA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str">
-        <x:v>0914335484</x:v>
+        <x:v>0921267951</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
-        <x:v>FARIÑO CEDEÑO</x:v>
+        <x:v>DURAN SOLORZANO</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>JORGE BLADIMIR</x:v>
+        <x:v>STEFANO ALEXANDER</x:v>
       </x:c>
       <x:c r="I10" s="4" t="str">
-        <x:v>jfarino@ups.edu.ec</x:v>
+        <x:v>sduran@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
@@ -40715,19 +40454,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>DISEÑO MULTIMEDIA</x:v>
+        <x:v>MECATRONICA</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>0919098681</x:v>
+        <x:v>0914335484</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>FIALLOS VARGAS</x:v>
+        <x:v>FARIÑO CEDEÑO</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>INGRID VERONICA</x:v>
+        <x:v>JORGE BLADIMIR</x:v>
       </x:c>
       <x:c r="I11" s="4" t="str">
-        <x:v>ifiallos@ups.edu.ec</x:v>
+        <x:v>jfarino@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
@@ -40744,19 +40483,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>DISEÑO MULTIMEDIA</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>0917208084</x:v>
+        <x:v>0919098681</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>FREIRE QUIROGA</x:v>
+        <x:v>FIALLOS VARGAS</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>DIEGO ROBERTO</x:v>
+        <x:v>INGRID VERONICA</x:v>
       </x:c>
       <x:c r="I12" s="4" t="str">
-        <x:v>dfreire@ups.edu.ec</x:v>
+        <x:v>ifiallos@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
@@ -40773,19 +40512,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>SEGURIDAD DE LA INFORMACION-LINEA</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>0920375177</x:v>
+        <x:v>0917208084</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>HUILCAPI SUBIA</x:v>
+        <x:v>FREIRE QUIROGA</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>DARIO FERNANDO</x:v>
+        <x:v>DIEGO ROBERTO</x:v>
       </x:c>
       <x:c r="I13" s="4" t="str">
-        <x:v>dhuilcapi@ups.edu.ec</x:v>
+        <x:v>dfreire@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
@@ -40802,19 +40541,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>BIOQUIMICA Y FARMACIA</x:v>
+        <x:v>SEGURIDAD DE LA INFORMACION-LINEA</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>1207482108</x:v>
+        <x:v>0920375177</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>JAIME CARVAJAL</x:v>
+        <x:v>HUILCAPI SUBIA</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>JAIRO JOEL</x:v>
+        <x:v>DARIO FERNANDO</x:v>
       </x:c>
       <x:c r="I14" s="4" t="str">
-        <x:v>jjaimec@ups.edu.ec</x:v>
+        <x:v>dhuilcapi@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
@@ -40831,19 +40570,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>VICERRECTORADO DE SEDE</x:v>
+        <x:v>BIOQUIMICA Y FARMACIA</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>0912234226</x:v>
+        <x:v>1207482108</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>LAM RODRIGUEZ</x:v>
+        <x:v>JAIME CARVAJAL</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>SUSANA ISABEL</x:v>
+        <x:v>JAIRO JOEL</x:v>
       </x:c>
       <x:c r="I15" s="4" t="str">
-        <x:v>slam@ups.edu.ec</x:v>
+        <x:v>jjaimec@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
@@ -40860,19 +40599,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>INSTITUTO DE IDIOMAS</x:v>
+        <x:v>VICERRECTORADO DE SEDE</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>0951974195</x:v>
+        <x:v>0912234226</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>LEON BRAVO</x:v>
+        <x:v>LAM RODRIGUEZ</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>GABRIELA MARGARITA</x:v>
+        <x:v>SUSANA ISABEL</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>gleonb@ups.edu.ec</x:v>
+        <x:v>slam@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
@@ -40889,19 +40628,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>INSTITUTO DE IDIOMAS</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>0706623923</x:v>
+        <x:v>0951974195</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>LOAYZA TORO</x:v>
+        <x:v>LEON BRAVO</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>MARIA ISABEL</x:v>
+        <x:v>GABRIELA MARGARITA</x:v>
       </x:c>
       <x:c r="I17" s="4" t="str">
-        <x:v>mloayzat@ups.edu.ec</x:v>
+        <x:v>gleonb@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
@@ -40918,19 +40657,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>TEOLOGIA MODALIDAD EN LINEA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
-        <x:v>0919514117</x:v>
+        <x:v>0706623923</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>LOOR SALAZAR</x:v>
+        <x:v>LOAYZA TORO</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>VERONICA KATIUSKA</x:v>
+        <x:v>MARIA ISABEL</x:v>
       </x:c>
       <x:c r="I18" s="4" t="str">
-        <x:v>vloor@ups.edu.ec</x:v>
+        <x:v>mloayzat@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
@@ -40947,19 +40686,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>TEOLOGIA MODALIDAD EN LINEA</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>0905056016</x:v>
+        <x:v>0919514117</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>MENDIETA VILLALBA</x:v>
+        <x:v>LOOR SALAZAR</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>NADIA MERCEDES</x:v>
+        <x:v>VERONICA KATIUSKA</x:v>
       </x:c>
       <x:c r="I19" s="4" t="str">
-        <x:v>nmendieta@ups.edu.ec</x:v>
+        <x:v>vloor@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -40976,19 +40715,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>0913608147</x:v>
+        <x:v>0905056016</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>MILLAN TRAVERSO</x:v>
+        <x:v>MENDIETA VILLALBA</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>MARCOS EFRAIN</x:v>
+        <x:v>NADIA MERCEDES</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>mmillan@ups.edu.ec</x:v>
+        <x:v>nmendieta@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
@@ -41005,19 +40744,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>INSTITUTO DE IDIOMAS</x:v>
+        <x:v>INGENIERIA AUTOMOTRIZ</x:v>
       </x:c>
       <x:c r="F21" s="8" t="str">
-        <x:v>0923940589</x:v>
+        <x:v>0913608147</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>MOREIRA MURILLO</x:v>
+        <x:v>MILLAN TRAVERSO</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>DIANA GUADALUPE</x:v>
+        <x:v>MARCOS EFRAIN</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>dmoreiram@ups.edu.ec</x:v>
+        <x:v>mmillan@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
@@ -41034,19 +40773,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>BIOTECNOLOGIA</x:v>
+        <x:v>INSTITUTO DE IDIOMAS</x:v>
       </x:c>
       <x:c r="F22" s="8" t="str">
-        <x:v>0927155226</x:v>
+        <x:v>0923940589</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>NARANJO MORAN</x:v>
+        <x:v>MOREIRA MURILLO</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>JAIME ALBERTO</x:v>
+        <x:v>DIANA GUADALUPE</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>jnaranjo@ups.edu.ec</x:v>
+        <x:v>dmoreiram@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
@@ -41063,19 +40802,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>DISEÑO MULTIMEDIA</x:v>
+        <x:v>BIOTECNOLOGIA</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>0927230631</x:v>
+        <x:v>0927155226</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>PAREDES ESTRELLA</x:v>
+        <x:v>NARANJO MORAN</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>GUILLERMO XAVIER</x:v>
+        <x:v>JAIME ALBERTO</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>gparedes@ups.edu.ec</x:v>
+        <x:v>jnaranjo@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -41092,19 +40831,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
+        <x:v>DISEÑO MULTIMEDIA</x:v>
       </x:c>
       <x:c r="F24" s="8" t="str">
-        <x:v>1757049075</x:v>
+        <x:v>0927230631</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>PRECIADO VELASQUEZ</x:v>
+        <x:v>PAREDES ESTRELLA</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>OSCAR EDUARDO</x:v>
+        <x:v>GUILLERMO XAVIER</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>opreciadov@ups.edu.ec</x:v>
+        <x:v>gparedes@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
@@ -41124,16 +40863,16 @@
         <x:v>ARQUITECTURA</x:v>
       </x:c>
       <x:c r="F25" s="8" t="str">
-        <x:v>0924613334</x:v>
+        <x:v>1757049075</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>REYES SANCHEZ</x:v>
+        <x:v>PRECIADO VELASQUEZ</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>JORGE ANDRES</x:v>
+        <x:v>OSCAR EDUARDO</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>jreyess@ups.edu.ec</x:v>
+        <x:v>opreciadov@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -41150,19 +40889,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>PEDAGOGIA DE LA ACTIVIDAD FISICA</x:v>
+        <x:v>ARQUITECTURA</x:v>
       </x:c>
       <x:c r="F26" s="8" t="str">
-        <x:v>0602162539</x:v>
+        <x:v>0924613334</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>ROMERO IBARRA</x:v>
+        <x:v>REYES SANCHEZ</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>FRANKLIN RUDIGER</x:v>
+        <x:v>JORGE ANDRES</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>fromero@ups.edu.ec</x:v>
+        <x:v>jreyess@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
@@ -41179,19 +40918,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>BIOMEDICINA</x:v>
+        <x:v>PEDAGOGIA DE LA ACTIVIDAD FISICA</x:v>
       </x:c>
       <x:c r="F27" s="8" t="str">
-        <x:v>1206442616</x:v>
+        <x:v>0602162539</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>ROMERO SANTISTEVAN</x:v>
+        <x:v>ROMERO IBARRA</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>DARIO XAVIER</x:v>
+        <x:v>FRANKLIN RUDIGER</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>dromeros@ups.edu.ec</x:v>
+        <x:v>fromero@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
@@ -41208,19 +40947,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>BIOMEDICINA</x:v>
       </x:c>
       <x:c r="F28" s="8" t="str">
-        <x:v>0912520475</x:v>
+        <x:v>1206442616</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>SAMANIEGO BRIONES</x:v>
+        <x:v>ROMERO SANTISTEVAN</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>PAOLA MERCEDES</x:v>
+        <x:v>DARIO XAVIER</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>psamaniego@ups.edu.ec</x:v>
+        <x:v>dromeros@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
@@ -41237,19 +40976,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>BIOMEDICINA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>0925582702</x:v>
+        <x:v>0912520475</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>SANTANA ZAMBRANO</x:v>
+        <x:v>SAMANIEGO BRIONES</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>CINDY MARIBEL</x:v>
+        <x:v>PAOLA MERCEDES</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>csantana@ups.edu.ec</x:v>
+        <x:v>psamaniego@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
@@ -41266,19 +41005,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>BIOMEDICINA</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>0909748287</x:v>
+        <x:v>0925582702</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>SUAREZ ESCOBAR</x:v>
+        <x:v>SANTANA ZAMBRANO</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>IVAN EDUARDO</x:v>
+        <x:v>CINDY MARIBEL</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>isuarez@ups.edu.ec</x:v>
+        <x:v>csantana@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
@@ -41295,19 +41034,19 @@
         <x:v>Aula D204</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>INGENIERIA CIVIL</x:v>
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F31" s="8" t="str">
-        <x:v>0925766461</x:v>
+        <x:v>0909748287</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>VALERO FAJARDO</x:v>
+        <x:v>SUAREZ ESCOBAR</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>CARLOS LUIS</x:v>
+        <x:v>IVAN EDUARDO</x:v>
       </x:c>
       <x:c r="I31" s="4" t="str">
-        <x:v>cvalero@ups.edu.ec</x:v>
+        <x:v>isuarez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="48" customHeight="1">
@@ -41327,16 +41066,103 @@
         <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F32" s="8" t="str">
+        <x:v>0914759576</x:v>
+      </x:c>
+      <x:c r="G32" s="4" t="str">
+        <x:v>TEJADA ESCOBAR</x:v>
+      </x:c>
+      <x:c r="H32" s="4" t="str">
+        <x:v>FREDDY JAVIER</x:v>
+      </x:c>
+      <x:c r="I32" s="4" t="str">
+        <x:v>ftejada@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="48" customHeight="1">
+      <x:c r="A33" s="9" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B33" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="str">
+        <x:v>SHEILA SERRANO VINCENTI</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>Aula D204</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>INGENIERIA CIVIL</x:v>
+      </x:c>
+      <x:c r="F33" s="8" t="str">
+        <x:v>0925766461</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>VALERO FAJARDO</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>CARLOS LUIS</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>cvalero@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="A34" s="9" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="str">
+        <x:v>SHEILA SERRANO VINCENTI</x:v>
+      </x:c>
+      <x:c r="D34" s="4" t="str">
+        <x:v>Aula D204</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="str">
+        <x:v>COMPUTACION</x:v>
+      </x:c>
+      <x:c r="F34" s="8" t="str">
         <x:v>0912511532</x:v>
       </x:c>
-      <x:c r="G32" s="4" t="str">
+      <x:c r="G34" s="4" t="str">
         <x:v>VALVERDE LANDIVAR</x:v>
       </x:c>
-      <x:c r="H32" s="4" t="str">
+      <x:c r="H34" s="4" t="str">
         <x:v>GALO ENRIQUE</x:v>
       </x:c>
-      <x:c r="I32" s="4" t="str">
+      <x:c r="I34" s="4" t="str">
         <x:v>gvalverde@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="9" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B35" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="str">
+        <x:v>SHEILA SERRANO VINCENTI</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>Aula D204</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
+        <x:v>DISEÑO MULTIMEDIA</x:v>
+      </x:c>
+      <x:c r="F35" s="8" t="str">
+        <x:v>0916155112</x:v>
+      </x:c>
+      <x:c r="G35" s="4" t="str">
+        <x:v>VELOZ ARCE</x:v>
+      </x:c>
+      <x:c r="H35" s="4" t="str">
+        <x:v>ALONSO EDUARDO</x:v>
+      </x:c>
+      <x:c r="I35" s="4" t="str">
+        <x:v>aveloz@ups.edu.ec</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -41537,19 +41363,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>DESARROLLO LOCAL - QUITO</x:v>
+        <x:v>TECNOLOGIA ELECTRICIDAD INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F7" s="8" t="str">
-        <x:v>0913750352</x:v>
+        <x:v>0911477776</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
-        <x:v>CASTRO MEDINA</x:v>
+        <x:v>CACERES GALAN</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>ANA JANETH</x:v>
+        <x:v>CESAR ANTONIO</x:v>
       </x:c>
       <x:c r="I7" s="4" t="str">
-        <x:v>acastro@ups.edu.ec</x:v>
+        <x:v>ccaceres@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
@@ -41566,19 +41392,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>DESARROLLO LOCAL - QUITO</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str">
-        <x:v>0930971593</x:v>
+        <x:v>0913750352</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
-        <x:v>CHAVEZ GONZALEZ</x:v>
+        <x:v>CASTRO MEDINA</x:v>
       </x:c>
       <x:c r="H8" s="4" t="str">
-        <x:v>KAROL LEONOR</x:v>
+        <x:v>ANA JANETH</x:v>
       </x:c>
       <x:c r="I8" s="4" t="str">
-        <x:v>kchavezg@ups.edu.ec</x:v>
+        <x:v>acastro@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
@@ -41598,16 +41424,16 @@
         <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F9" s="8" t="str">
-        <x:v>0918696303</x:v>
+        <x:v>0930971593</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
-        <x:v>CHEHAB ZAMBRANO</x:v>
+        <x:v>CHAVEZ GONZALEZ</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>JAMIL ADOLFO</x:v>
+        <x:v>KAROL LEONOR</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
-        <x:v>jchehab@ups.edu.ec</x:v>
+        <x:v>kchavezg@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -41624,19 +41450,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>INSTITUTO DE IDIOMAS</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str">
-        <x:v>0915453658</x:v>
+        <x:v>0918696303</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
-        <x:v>COLOMA PEÑAFIEL</x:v>
+        <x:v>CHEHAB ZAMBRANO</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>DAVID EMILIO</x:v>
+        <x:v>JAMIL ADOLFO</x:v>
       </x:c>
       <x:c r="I10" s="4" t="str">
-        <x:v>dcoloma@ups.edu.ec</x:v>
+        <x:v>jchehab@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
@@ -41653,19 +41479,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
+        <x:v>INSTITUTO DE IDIOMAS</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>0912186467</x:v>
+        <x:v>0915453658</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>DIAZ SOLIS</x:v>
+        <x:v>COLOMA PEÑAFIEL</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>GENARO ELICEO</x:v>
+        <x:v>DAVID EMILIO</x:v>
       </x:c>
       <x:c r="I11" s="4" t="str">
-        <x:v>gdiaz@ups.edu.ec</x:v>
+        <x:v>dcoloma@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
@@ -41682,19 +41508,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>COMUNICACION SOCIAL</x:v>
+        <x:v>ELECTRONICA Y AUTOMATIZACION</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>1202606404</x:v>
+        <x:v>0912186467</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>ESCOBAR TERAN</x:v>
+        <x:v>DIAZ SOLIS</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>SUSAN CATHERINE</x:v>
+        <x:v>GENARO ELICEO</x:v>
       </x:c>
       <x:c r="I12" s="4" t="str">
-        <x:v>sescobar@ups.edu.ec</x:v>
+        <x:v>gdiaz@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
@@ -41711,19 +41537,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>COMUNICACION SOCIAL</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>0918123605</x:v>
+        <x:v>1202606404</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>GARCIA PEREZ</x:v>
+        <x:v>ESCOBAR TERAN</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>ALEX GUILLERMO</x:v>
+        <x:v>SUSAN CATHERINE</x:v>
       </x:c>
       <x:c r="I13" s="4" t="str">
-        <x:v>agarciap@ups.edu.ec</x:v>
+        <x:v>sescobar@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
@@ -41740,19 +41566,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>0916525959</x:v>
+        <x:v>0918123605</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>GOMEZ PITA</x:v>
+        <x:v>GARCIA PEREZ</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>ARACELY JOSEFINA</x:v>
+        <x:v>ALEX GUILLERMO</x:v>
       </x:c>
       <x:c r="I14" s="4" t="str">
-        <x:v>agomez@ups.edu.ec</x:v>
+        <x:v>agarciap@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
@@ -41769,19 +41595,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>0104606777</x:v>
+        <x:v>0916525959</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>GOMEZ RIOS</x:v>
+        <x:v>GOMEZ PITA</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>MONICA DANIELA</x:v>
+        <x:v>ARACELY JOSEFINA</x:v>
       </x:c>
       <x:c r="I15" s="4" t="str">
-        <x:v>mgomezr@ups.edu.ec</x:v>
+        <x:v>agomez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
@@ -41798,19 +41624,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>INGENIERIA INDUSTRIAL</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>0911019529</x:v>
+        <x:v>0104606777</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>GONZALEZ VASQUEZ</x:v>
+        <x:v>GOMEZ RIOS</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>ANGEL EDUARDO</x:v>
+        <x:v>MONICA DANIELA</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>agonzalez@ups.edu.ec</x:v>
+        <x:v>mgomezr@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
@@ -41827,19 +41653,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>DIRECCION TECNICA DE PASTORAL</x:v>
+        <x:v>INGENIERIA INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>1715933972</x:v>
+        <x:v>0911019529</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>GUAJALA AGILA</x:v>
+        <x:v>GONZALEZ VASQUEZ</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>DIEGO DAVID</x:v>
+        <x:v>ANGEL EDUARDO</x:v>
       </x:c>
       <x:c r="I17" s="4" t="str">
-        <x:v>dguajala@ups.edu.ec</x:v>
+        <x:v>agonzalez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
@@ -41856,19 +41682,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>PSICOLOGIA CLINICA</x:v>
+        <x:v>DIRECCION TECNICA DE PASTORAL</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
-        <x:v>0930628284</x:v>
+        <x:v>1715933972</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>JATIVA MOYANO</x:v>
+        <x:v>GUAJALA AGILA</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>GABRIELA LISSETTE</x:v>
+        <x:v>DIEGO DAVID</x:v>
       </x:c>
       <x:c r="I18" s="4" t="str">
-        <x:v>gjativam@ups.edu.ec</x:v>
+        <x:v>dguajala@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
@@ -41885,19 +41711,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>BIOTECNOLOGIA</x:v>
+        <x:v>PSICOLOGIA CLINICA</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>0960450922</x:v>
+        <x:v>0930628284</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>LOPEZ ULLOA</x:v>
+        <x:v>JATIVA MOYANO</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>BRENDA PATRICIA</x:v>
+        <x:v>GABRIELA LISSETTE</x:v>
       </x:c>
       <x:c r="I19" s="4" t="str">
-        <x:v>blopez@ups.edu.ec</x:v>
+        <x:v>gjativam@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -41914,19 +41740,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>BIOTECNOLOGIA</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>0503202475</x:v>
+        <x:v>0960450922</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>MENA GALLEGOS</x:v>
+        <x:v>LOPEZ ULLOA</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>CYNTHIA LORENA</x:v>
+        <x:v>BRENDA PATRICIA</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>cmenag@ups.edu.ec</x:v>
+        <x:v>blopez@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
@@ -41943,19 +41769,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>COMPUTACION</x:v>
+        <x:v>ADMINISTRACION DE EMPRESAS</x:v>
       </x:c>
       <x:c r="F21" s="8" t="str">
-        <x:v>0909257800</x:v>
+        <x:v>0930054432</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>MORA SALTOS</x:v>
+        <x:v>MARTINEZ FIGUEROA</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>NELSON SALOMON</x:v>
+        <x:v>JUAN PABLO</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>nmora@ups.edu.ec</x:v>
+        <x:v>jmartinezf@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
@@ -41975,16 +41801,16 @@
         <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F22" s="8" t="str">
-        <x:v>0705777662</x:v>
+        <x:v>0503202475</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>RAMIREZ SANCHEZ</x:v>
+        <x:v>MENA GALLEGOS</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>KARINA MISHELLE</x:v>
+        <x:v>CYNTHIA LORENA</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>kramirezs@ups.edu.ec</x:v>
+        <x:v>cmenag@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
@@ -42001,19 +41827,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>EDUCACION INICIAL</x:v>
+        <x:v>COMPUTACION</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>0907787915</x:v>
+        <x:v>0909257800</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>RECALDE RAYMONDY</x:v>
+        <x:v>MORA SALTOS</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>RITA ELIZABETH</x:v>
+        <x:v>NELSON SALOMON</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>rrecalde@ups.edu.ec</x:v>
+        <x:v>nmora@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -42030,19 +41856,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>COMUNICACION SOCIAL</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F24" s="8" t="str">
-        <x:v>0914925904</x:v>
+        <x:v>0705777662</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>RODAS SOTO</x:v>
+        <x:v>RAMIREZ SANCHEZ</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>BETTY ISABEL</x:v>
+        <x:v>KARINA MISHELLE</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>brodas@ups.edu.ec</x:v>
+        <x:v>kramirezs@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
@@ -42059,19 +41885,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>MAESTRÍA EN SEGURIDAD, SALUD E HIGIENE INDUSTRIAL</x:v>
+        <x:v>EDUCACION INICIAL</x:v>
       </x:c>
       <x:c r="F25" s="8" t="str">
-        <x:v>0919958363</x:v>
+        <x:v>0907787915</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>ROJAS PARRAGA</x:v>
+        <x:v>RECALDE RAYMONDY</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>TANIA CATALINA</x:v>
+        <x:v>RITA ELIZABETH</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>trojas@ups.edu.ec</x:v>
+        <x:v>rrecalde@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -42088,19 +41914,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
+        <x:v>COMUNICACION SOCIAL</x:v>
       </x:c>
       <x:c r="F26" s="8" t="str">
-        <x:v>0918135690</x:v>
+        <x:v>0914925904</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>ROSALES VALENCIA</x:v>
+        <x:v>RODAS SOTO</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>JENNY ELIZABETH</x:v>
+        <x:v>BETTY ISABEL</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>jrosales@ups.edu.ec</x:v>
+        <x:v>brodas@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
@@ -42117,19 +41943,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
+        <x:v>MAESTRÍA EN SEGURIDAD, SALUD E HIGIENE INDUSTRIAL</x:v>
       </x:c>
       <x:c r="F27" s="8" t="str">
-        <x:v>0912805827</x:v>
+        <x:v>0919958363</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>SOTOMAYOR NAVARRO</x:v>
+        <x:v>ROJAS PARRAGA</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>MARIA CAROLINA</x:v>
+        <x:v>TANIA CATALINA</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>msotomayorn@ups.edu.ec</x:v>
+        <x:v>trojas@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
@@ -42146,19 +41972,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>ARQUITECTURA</x:v>
+        <x:v>CONTABILIDAD Y AUDITORIA</x:v>
       </x:c>
       <x:c r="F28" s="8" t="str">
-        <x:v>0926416298</x:v>
+        <x:v>0918135690</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>TRUJILLO MOLINA</x:v>
+        <x:v>ROSALES VALENCIA</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>ERICK SANTIAGO</x:v>
+        <x:v>JENNY ELIZABETH</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>etrujillom@ups.edu.ec</x:v>
+        <x:v>jrosales@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
@@ -42175,19 +42001,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>ARQUITECTURA</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>1204488900</x:v>
+        <x:v>0912805827</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>VALDIVIEZO GILCES</x:v>
+        <x:v>SOTOMAYOR NAVARRO</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>MARIA JOSE</x:v>
+        <x:v>MARIA CAROLINA</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>mvaldiviezo@ups.edu.ec</x:v>
+        <x:v>msotomayorn@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
@@ -42204,19 +42030,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>ECONOMIA</x:v>
+        <x:v>ODONTOLOGIA</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>0917770778</x:v>
+        <x:v>0924149081</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>VALLEJO LEON</x:v>
+        <x:v>SUASNAVAS MERINO</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>KARINA ROXANA</x:v>
+        <x:v>KATHERINE MELISSA</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>kvallejo@ups.edu.ec</x:v>
+        <x:v>ksuasnavas@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
@@ -42233,19 +42059,19 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>ODONTOLOGIA</x:v>
+        <x:v>ARQUITECTURA</x:v>
       </x:c>
       <x:c r="F31" s="8" t="str">
-        <x:v>0954979449</x:v>
+        <x:v>0926416298</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>YAROSSI MATA</x:v>
+        <x:v>TRUJILLO MOLINA</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>KATHERINA</x:v>
+        <x:v>ERICK SANTIAGO</x:v>
       </x:c>
       <x:c r="I31" s="4" t="str">
-        <x:v>kyarossi@ups.edu.ec</x:v>
+        <x:v>etrujillom@ups.edu.ec</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="48" customHeight="1">
@@ -42262,18 +42088,105 @@
         <x:v>Aula D205</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
+        <x:v>ODONTOLOGIA</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="str">
+        <x:v>1204488900</x:v>
+      </x:c>
+      <x:c r="G32" s="4" t="str">
+        <x:v>VALDIVIEZO GILCES</x:v>
+      </x:c>
+      <x:c r="H32" s="4" t="str">
+        <x:v>MARIA JOSE</x:v>
+      </x:c>
+      <x:c r="I32" s="4" t="str">
+        <x:v>mvaldiviezo@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="48" customHeight="1">
+      <x:c r="A33" s="9" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B33" s="9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="str">
+        <x:v>ALICIA MARIA CEDEÑO TELLO</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>Aula D205</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>ECONOMIA</x:v>
+      </x:c>
+      <x:c r="F33" s="8" t="str">
+        <x:v>0917770778</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>VALLEJO LEON</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>KARINA ROXANA</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>kvallejo@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="A34" s="9" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="str">
+        <x:v>ALICIA MARIA CEDEÑO TELLO</x:v>
+      </x:c>
+      <x:c r="D34" s="4" t="str">
+        <x:v>Aula D205</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="str">
+        <x:v>ODONTOLOGIA</x:v>
+      </x:c>
+      <x:c r="F34" s="8" t="str">
+        <x:v>0954979449</x:v>
+      </x:c>
+      <x:c r="G34" s="4" t="str">
+        <x:v>YAROSSI MATA</x:v>
+      </x:c>
+      <x:c r="H34" s="4" t="str">
+        <x:v>KATHERINA</x:v>
+      </x:c>
+      <x:c r="I34" s="4" t="str">
+        <x:v>kyarossi@ups.edu.ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="9" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B35" s="9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="str">
+        <x:v>ALICIA MARIA CEDEÑO TELLO</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>Aula D205</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
         <x:v>CONTABILIDAD Y AUDITORIA</x:v>
       </x:c>
-      <x:c r="F32" s="8" t="str">
+      <x:c r="F35" s="8" t="str">
         <x:v>0923726772</x:v>
       </x:c>
-      <x:c r="G32" s="4" t="str">
+      <x:c r="G35" s="4" t="str">
         <x:v>ZEA VILLACIS</x:v>
       </x:c>
-      <x:c r="H32" s="4" t="str">
+      <x:c r="H35" s="4" t="str">
         <x:v>NORMA MARGARITA</x:v>
       </x:c>
-      <x:c r="I32" s="4" t="str">
+      <x:c r="I35" s="4" t="str">
         <x:v>nzea@ups.edu.ec</x:v>
       </x:c>
     </x:row>
